--- a/docs/historical-mortgage-rates.xlsx
+++ b/docs/historical-mortgage-rates.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="39">
   <si>
     <t>Month</t>
   </si>
@@ -227,7 +227,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -243,6 +243,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -289,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -327,6 +333,9 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -340,18 +349,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -751,31 +749,24 @@
         <v>24</v>
       </c>
       <c r="B8" s="8">
-        <f>AVERAGE('Standard rates'!$B$2:$B$262)</f>
         <v>0.06794406130268199</v>
       </c>
       <c r="C8" s="8">
-        <f>AVERAGE('Standard rates'!$C$2:$C$262)</f>
-        <v>0.061274329501915706</v>
+        <v>0.06127432950191571</v>
       </c>
       <c r="D8" s="8">
-        <f>AVERAGE('Standard rates'!$D$2:$D$262)</f>
         <v>0.05998007662835249</v>
       </c>
       <c r="E8" s="8">
-        <f>AVERAGE('Standard rates'!$E$2:$E$262)</f>
         <v>0.06155938697318008</v>
       </c>
       <c r="F8" s="8">
-        <f>AVERAGE('Standard rates'!$F$2:$F$262)</f>
         <v>0.06295632183908045</v>
       </c>
       <c r="G8" s="8">
-        <f>AVERAGE('Standard rates'!$G$2:$G$262)</f>
         <v>0.06515249042145593</v>
       </c>
       <c r="H8" s="8">
-        <f>AVERAGE('Standard rates'!$H$2:$H$262)</f>
         <v>0.06661302681992337</v>
       </c>
     </row>
@@ -784,31 +775,24 @@
         <v>25</v>
       </c>
       <c r="B9" s="9">
-        <f>MAX('Standard rates'!$B$2:$B$262)</f>
         <v>0.1072</v>
       </c>
       <c r="C9" s="9">
-        <f>MAX('Standard rates'!$C$2:$C$262)</f>
         <v>0.0993</v>
       </c>
       <c r="D9" s="9">
-        <f>MAX('Standard rates'!$D$2:$D$262)</f>
         <v>0.099</v>
       </c>
       <c r="E9" s="9">
-        <f>MAX('Standard rates'!$E$2:$E$262)</f>
         <v>0.09630000000000001</v>
       </c>
       <c r="F9" s="9">
-        <f>MAX('Standard rates'!$F$2:$F$262)</f>
         <v>0.09609999999999999</v>
       </c>
       <c r="G9" s="9">
-        <f>MAX('Standard rates'!$G$2:$G$262)</f>
         <v>0.0956</v>
       </c>
       <c r="H9" s="9">
-        <f>MAX('Standard rates'!$H$2:$H$262)</f>
         <v>0.095</v>
       </c>
     </row>
@@ -817,31 +801,24 @@
         <v>26</v>
       </c>
       <c r="B10" s="9">
-        <f>MIN('Standard rates'!$B$2:$B$262)</f>
         <v>0.0447</v>
       </c>
       <c r="C10" s="9">
-        <f>MIN('Standard rates'!$C$2:$C$262)</f>
         <v>0.0374</v>
       </c>
       <c r="D10" s="9">
-        <f>MIN('Standard rates'!$D$2:$D$262)</f>
         <v>0.0317</v>
       </c>
       <c r="E10" s="9">
-        <f>MIN('Standard rates'!$E$2:$E$262)</f>
         <v>0.0346</v>
       </c>
       <c r="F10" s="9">
-        <f>MIN('Standard rates'!$F$2:$F$262)</f>
         <v>0.0333</v>
       </c>
       <c r="G10" s="9">
-        <f>MIN('Standard rates'!$G$2:$G$262)</f>
         <v>0.0369</v>
       </c>
       <c r="H10" s="9">
-        <f>MIN('Standard rates'!$H$2:$H$262)</f>
         <v>0.0377</v>
       </c>
     </row>
@@ -850,32 +827,25 @@
         <v>27</v>
       </c>
       <c r="B11" s="9">
-        <f>B9-B10</f>
         <v>0.0625</v>
       </c>
       <c r="C11" s="9">
-        <f>C9-C10</f>
         <v>0.0619</v>
       </c>
       <c r="D11" s="9">
-        <f>D9-D10</f>
         <v>0.0673</v>
       </c>
       <c r="E11" s="9">
-        <f>E9-E10</f>
         <v>0.06170000000000001</v>
       </c>
       <c r="F11" s="9">
-        <f>F9-F10</f>
-        <v>0.0628</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="G11" s="9">
-        <f>G9-G10</f>
         <v>0.0587</v>
       </c>
       <c r="H11" s="9">
-        <f>H9-H10</f>
-        <v>0.057300000000000004</v>
+        <v>0.0573</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -912,31 +882,24 @@
         <v>24</v>
       </c>
       <c r="B15" s="8">
-        <f>Workings!$C$19</f>
         <v>0.06309807512167666</v>
       </c>
       <c r="C15" s="8">
-        <f>Workings!$D$19</f>
         <v>0.05650144892407568</v>
       </c>
       <c r="D15" s="8">
-        <f>Workings!$E$19</f>
         <v>0.05469051977910503</v>
       </c>
       <c r="E15" s="8">
-        <f>Workings!$F$19</f>
         <v>0.05650726605777984</v>
       </c>
       <c r="F15" s="8">
-        <f>Workings!$G$19</f>
         <v>0.05775171170108443</v>
       </c>
       <c r="G15" s="8">
-        <f>Workings!$H$19</f>
         <v>0.06014645025178291</v>
       </c>
       <c r="H15" s="8">
-        <f>Workings!$I$19</f>
         <v>0.06182811846384758</v>
       </c>
     </row>
@@ -986,31 +949,24 @@
         <v>31</v>
       </c>
       <c r="B20" s="11">
-        <f>Workings!$K$19</f>
         <v>7</v>
       </c>
       <c r="C20" s="11">
-        <f>Workings!$L$19</f>
         <v>475</v>
       </c>
       <c r="D20" s="11">
-        <f>Workings!$M$19</f>
         <v>1429</v>
       </c>
       <c r="E20" s="11">
-        <f>Workings!$N$19</f>
         <v>74</v>
       </c>
       <c r="F20" s="11">
-        <f>Workings!$O$19</f>
         <v>112</v>
       </c>
       <c r="G20" s="11">
-        <f>Workings!$P$19</f>
         <v>29</v>
       </c>
       <c r="H20" s="11">
-        <f>Workings!$Q$19</f>
         <v>214</v>
       </c>
     </row>
@@ -1019,31 +975,24 @@
         <v>32</v>
       </c>
       <c r="B21" s="12">
-        <f>Workings!$K$20</f>
-        <v>0.0029914529914529917</v>
+        <v>0.002991452991452992</v>
       </c>
       <c r="C21" s="12">
-        <f>Workings!$L$20</f>
         <v>0.202991452991453</v>
       </c>
       <c r="D21" s="12">
-        <f>Workings!$M$20</f>
         <v>0.6106837606837607</v>
       </c>
       <c r="E21" s="12">
-        <f>Workings!$N$20</f>
         <v>0.03162393162393162</v>
       </c>
       <c r="F21" s="12">
-        <f>Workings!$O$20</f>
         <v>0.04786324786324787</v>
       </c>
       <c r="G21" s="12">
-        <f>Workings!$P$20</f>
-        <v>0.012393162393162393</v>
+        <v>0.01239316239316239</v>
       </c>
       <c r="H21" s="12">
-        <f>Workings!$Q$20</f>
         <v>0.09145299145299145</v>
       </c>
     </row>
@@ -1096,28 +1045,22 @@
         <v>35</v>
       </c>
       <c r="C26" s="8">
-        <f>AVERAGE('Special rates'!$B$2:$B$118)</f>
-        <v>0.050342735042735044</v>
+        <v>0.05034273504273504</v>
       </c>
       <c r="D26" s="8">
-        <f>AVERAGE('Special rates'!$C$2:$C$118)</f>
         <v>0.04601282051282051</v>
       </c>
       <c r="E26" s="8">
-        <f>AVERAGE('Special rates'!$D$2:$D$118)</f>
         <v>0.04713846153846154</v>
       </c>
       <c r="F26" s="8">
-        <f>AVERAGE('Special rates'!$E$2:$E$118)</f>
-        <v>0.049037606837606836</v>
+        <v>0.04903760683760684</v>
       </c>
       <c r="G26" s="8">
-        <f>AVERAGE('Special rates'!$F$2:$F$118)</f>
-        <v>0.051570940170940174</v>
+        <v>0.05157094017094017</v>
       </c>
       <c r="H26" s="8">
-        <f>AVERAGE('Special rates'!$G$2:$G$118)</f>
-        <v>0.052422222222222224</v>
+        <v>0.05242222222222222</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1128,27 +1071,21 @@
         <v>35</v>
       </c>
       <c r="C27" s="9">
-        <f>MAX('Special rates'!$B$2:$B$118)</f>
         <v>0.0738</v>
       </c>
       <c r="D27" s="9">
-        <f>MAX('Special rates'!$C$2:$C$118)</f>
         <v>0.073</v>
       </c>
       <c r="E27" s="9">
-        <f>MAX('Special rates'!$D$2:$D$118)</f>
         <v>0.0701</v>
       </c>
       <c r="F27" s="9">
-        <f>MAX('Special rates'!$E$2:$E$118)</f>
         <v>0.0679</v>
       </c>
       <c r="G27" s="9">
-        <f>MAX('Special rates'!$F$2:$F$118)</f>
         <v>0.067</v>
       </c>
       <c r="H27" s="9">
-        <f>MAX('Special rates'!$G$2:$G$118)</f>
         <v>0.0675</v>
       </c>
     </row>
@@ -1160,27 +1097,21 @@
         <v>35</v>
       </c>
       <c r="C28" s="9">
-        <f>MIN('Special rates'!$B$2:$B$118)</f>
-        <v>0.030899999999999997</v>
+        <v>0.0309</v>
       </c>
       <c r="D28" s="9">
-        <f>MIN('Special rates'!$C$2:$C$118)</f>
-        <v>0.022099999999999998</v>
+        <v>0.0221</v>
       </c>
       <c r="E28" s="9">
-        <f>MIN('Special rates'!$D$2:$D$118)</f>
         <v>0.0256</v>
       </c>
       <c r="F28" s="9">
-        <f>MIN('Special rates'!$E$2:$E$118)</f>
         <v>0.0273</v>
       </c>
       <c r="G28" s="9">
-        <f>MIN('Special rates'!$F$2:$F$118)</f>
         <v>0.0296</v>
       </c>
       <c r="H28" s="9">
-        <f>MIN('Special rates'!$G$2:$G$118)</f>
         <v>0.0301</v>
       </c>
     </row>
@@ -1192,27 +1123,21 @@
         <v>35</v>
       </c>
       <c r="C29" s="9">
-        <f>C27-C28</f>
         <v>0.04290000000000001</v>
       </c>
       <c r="D29" s="9">
-        <f>D27-D28</f>
         <v>0.0509</v>
       </c>
       <c r="E29" s="9">
-        <f>E27-E28</f>
         <v>0.0445</v>
       </c>
       <c r="F29" s="9">
-        <f>F27-F28</f>
         <v>0.0406</v>
       </c>
       <c r="G29" s="9">
-        <f>G27-G28</f>
         <v>0.0374</v>
       </c>
       <c r="H29" s="9">
-        <f>H27-H28</f>
         <v>0.0374</v>
       </c>
     </row>
@@ -1310,7 +1235,7 @@
       <c r="D2" s="16">
         <v>0.0764</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="17">
         <v>0.0761</v>
       </c>
       <c r="F2" s="16">
@@ -1322,9 +1247,8 @@
       <c r="H2" s="16">
         <v>0.0767</v>
       </c>
-      <c r="I2" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B2:H2),B2:H2,0)),"")</f>
-        <v>2 years</v>
+      <c r="I2" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1337,7 +1261,7 @@
       <c r="C3" s="16">
         <v>0.0765</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="17">
         <v>0.07629999999999999</v>
       </c>
       <c r="E3" s="16">
@@ -1352,9 +1276,8 @@
       <c r="H3" s="16">
         <v>0.0774</v>
       </c>
-      <c r="I3" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B3:H3),B3:H3,0)),"")</f>
-        <v>1 year</v>
+      <c r="I3" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1367,7 +1290,7 @@
       <c r="C4" s="16">
         <v>0.0791</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="17">
         <v>0.077</v>
       </c>
       <c r="E4" s="16">
@@ -1382,9 +1305,8 @@
       <c r="H4" s="16">
         <v>0.0794</v>
       </c>
-      <c r="I4" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B4:H4),B4:H4,0)),"")</f>
-        <v>1 year</v>
+      <c r="I4" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1397,7 +1319,7 @@
       <c r="C5" s="16">
         <v>0.0793</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="17">
         <v>0.0774</v>
       </c>
       <c r="E5" s="16">
@@ -1412,9 +1334,8 @@
       <c r="H5" s="16">
         <v>0.0799</v>
       </c>
-      <c r="I5" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B5:H5),B5:H5,0)),"")</f>
-        <v>1 year</v>
+      <c r="I5" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1430,7 +1351,7 @@
       <c r="D6" s="16">
         <v>0.0776</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="17">
         <v>0.07730000000000001</v>
       </c>
       <c r="F6" s="16">
@@ -1442,9 +1363,8 @@
       <c r="H6" s="16">
         <v>0.0776</v>
       </c>
-      <c r="I6" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B6:H6),B6:H6,0)),"")</f>
-        <v>2 years</v>
+      <c r="I6" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1466,15 +1386,14 @@
       <c r="F7" s="16">
         <v>0.07629999999999999</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="17">
         <v>0.0761</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="17">
         <v>0.0761</v>
       </c>
-      <c r="I7" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B7:H7),B7:H7,0)),"")</f>
-        <v>4 years</v>
+      <c r="I7" s="18" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1499,12 +1418,11 @@
       <c r="G8" s="16">
         <v>0.0757</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="17">
         <v>0.0747</v>
       </c>
-      <c r="I8" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B8:H8),B8:H8,0)),"")</f>
-        <v>5 years</v>
+      <c r="I8" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1529,12 +1447,11 @@
       <c r="G9" s="16">
         <v>0.07530000000000001</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="17">
         <v>0.0746</v>
       </c>
-      <c r="I9" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B9:H9),B9:H9,0)),"")</f>
-        <v>5 years</v>
+      <c r="I9" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1559,12 +1476,11 @@
       <c r="G10" s="16">
         <v>0.07480000000000001</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="17">
         <v>0.0746</v>
       </c>
-      <c r="I10" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B10:H10),B10:H10,0)),"")</f>
-        <v>5 years</v>
+      <c r="I10" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1589,12 +1505,11 @@
       <c r="G11" s="16">
         <v>0.0779</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="17">
         <v>0.07690000000000001</v>
       </c>
-      <c r="I11" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B11:H11),B11:H11,0)),"")</f>
-        <v>5 years</v>
+      <c r="I11" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1619,12 +1534,11 @@
       <c r="G12" s="16">
         <v>0.0809</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="17">
         <v>0.0793</v>
       </c>
-      <c r="I12" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B12:H12),B12:H12,0)),"")</f>
-        <v>5 years</v>
+      <c r="I12" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1649,12 +1563,11 @@
       <c r="G13" s="16">
         <v>0.0809</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="17">
         <v>0.0795</v>
       </c>
-      <c r="I13" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B13:H13),B13:H13,0)),"")</f>
-        <v>5 years</v>
+      <c r="I13" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1679,12 +1592,11 @@
       <c r="G14" s="16">
         <v>0.08</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="17">
         <v>0.0789</v>
       </c>
-      <c r="I14" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B14:H14),B14:H14,0)),"")</f>
-        <v>5 years</v>
+      <c r="I14" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1709,12 +1621,11 @@
       <c r="G15" s="16">
         <v>0.07870000000000001</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="17">
         <v>0.07679999999999999</v>
       </c>
-      <c r="I15" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B15:H15),B15:H15,0)),"")</f>
-        <v>5 years</v>
+      <c r="I15" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1739,12 +1650,11 @@
       <c r="G16" s="16">
         <v>0.07769999999999999</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="17">
         <v>0.07629999999999999</v>
       </c>
-      <c r="I16" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B16:H16),B16:H16,0)),"")</f>
-        <v>5 years</v>
+      <c r="I16" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1769,12 +1679,11 @@
       <c r="G17" s="16">
         <v>0.0765</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="17">
         <v>0.0761</v>
       </c>
-      <c r="I17" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B17:H17),B17:H17,0)),"")</f>
-        <v>5 years</v>
+      <c r="I17" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1799,12 +1708,11 @@
       <c r="G18" s="16">
         <v>0.0781</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="17">
         <v>0.07769999999999999</v>
       </c>
-      <c r="I18" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B18:H18),B18:H18,0)),"")</f>
-        <v>5 years</v>
+      <c r="I18" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1829,12 +1737,11 @@
       <c r="G19" s="16">
         <v>0.0789</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="17">
         <v>0.0784</v>
       </c>
-      <c r="I19" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B19:H19),B19:H19,0)),"")</f>
-        <v>5 years</v>
+      <c r="I19" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1859,12 +1766,11 @@
       <c r="G20" s="16">
         <v>0.08070000000000001</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="17">
         <v>0.0794</v>
       </c>
-      <c r="I20" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B20:H20),B20:H20,0)),"")</f>
-        <v>5 years</v>
+      <c r="I20" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1889,12 +1795,11 @@
       <c r="G21" s="16">
         <v>0.0795</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="17">
         <v>0.0786</v>
       </c>
-      <c r="I21" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B21:H21),B21:H21,0)),"")</f>
-        <v>5 years</v>
+      <c r="I21" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1919,12 +1824,11 @@
       <c r="G22" s="16">
         <v>0.0788</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="17">
         <v>0.07690000000000001</v>
       </c>
-      <c r="I22" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B22:H22),B22:H22,0)),"")</f>
-        <v>5 years</v>
+      <c r="I22" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1949,12 +1853,11 @@
       <c r="G23" s="16">
         <v>0.0789</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="17">
         <v>0.0775</v>
       </c>
-      <c r="I23" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B23:H23),B23:H23,0)),"")</f>
-        <v>5 years</v>
+      <c r="I23" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1979,12 +1882,11 @@
       <c r="G24" s="16">
         <v>0.0795</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="17">
         <v>0.0781</v>
       </c>
-      <c r="I24" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B24:H24),B24:H24,0)),"")</f>
-        <v>5 years</v>
+      <c r="I24" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -2009,12 +1911,11 @@
       <c r="G25" s="16">
         <v>0.07969999999999999</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="17">
         <v>0.0784</v>
       </c>
-      <c r="I25" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B25:H25),B25:H25,0)),"")</f>
-        <v>5 years</v>
+      <c r="I25" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -2039,12 +1940,11 @@
       <c r="G26" s="16">
         <v>0.0806</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="17">
         <v>0.0788</v>
       </c>
-      <c r="I26" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B26:H26),B26:H26,0)),"")</f>
-        <v>5 years</v>
+      <c r="I26" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -2069,12 +1969,11 @@
       <c r="G27" s="16">
         <v>0.08119999999999999</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="17">
         <v>0.07969999999999999</v>
       </c>
-      <c r="I27" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B27:H27),B27:H27,0)),"")</f>
-        <v>5 years</v>
+      <c r="I27" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -2099,12 +1998,11 @@
       <c r="G28" s="16">
         <v>0.08539999999999999</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="17">
         <v>0.0837</v>
       </c>
-      <c r="I28" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B28:H28),B28:H28,0)),"")</f>
-        <v>5 years</v>
+      <c r="I28" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -2129,12 +2027,11 @@
       <c r="G29" s="16">
         <v>0.08650000000000001</v>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="17">
         <v>0.0861</v>
       </c>
-      <c r="I29" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B29:H29),B29:H29,0)),"")</f>
-        <v>5 years</v>
+      <c r="I29" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -2159,12 +2056,11 @@
       <c r="G30" s="16">
         <v>0.0866</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="17">
         <v>0.0863</v>
       </c>
-      <c r="I30" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B30:H30),B30:H30,0)),"")</f>
-        <v>5 years</v>
+      <c r="I30" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -2189,12 +2085,11 @@
       <c r="G31" s="16">
         <v>0.0901</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.0892</v>
       </c>
-      <c r="I31" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B31:H31),B31:H31,0)),"")</f>
-        <v>5 years</v>
+      <c r="I31" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -2219,12 +2114,11 @@
       <c r="G32" s="16">
         <v>0.0898</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="17">
         <v>0.0891</v>
       </c>
-      <c r="I32" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B32:H32),B32:H32,0)),"")</f>
-        <v>5 years</v>
+      <c r="I32" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -2249,12 +2143,11 @@
       <c r="G33" s="16">
         <v>0.0898</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="17">
         <v>0.0891</v>
       </c>
-      <c r="I33" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B33:H33),B33:H33,0)),"")</f>
-        <v>5 years</v>
+      <c r="I33" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -2279,12 +2172,11 @@
       <c r="G34" s="16">
         <v>0.08929999999999999</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="17">
         <v>0.0863</v>
       </c>
-      <c r="I34" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B34:H34),B34:H34,0)),"")</f>
-        <v>5 years</v>
+      <c r="I34" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -2309,12 +2201,11 @@
       <c r="G35" s="16">
         <v>0.08929999999999999</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="17">
         <v>0.08779999999999999</v>
       </c>
-      <c r="I35" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B35:H35),B35:H35,0)),"")</f>
-        <v>5 years</v>
+      <c r="I35" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -2339,12 +2230,11 @@
       <c r="G36" s="16">
         <v>0.0902</v>
       </c>
-      <c r="H36" s="16">
+      <c r="H36" s="17">
         <v>0.0885</v>
       </c>
-      <c r="I36" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B36:H36),B36:H36,0)),"")</f>
-        <v>5 years</v>
+      <c r="I36" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -2369,12 +2259,11 @@
       <c r="G37" s="16">
         <v>0.09050000000000001</v>
       </c>
-      <c r="H37" s="16">
+      <c r="H37" s="17">
         <v>0.08929999999999999</v>
       </c>
-      <c r="I37" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B37:H37),B37:H37,0)),"")</f>
-        <v>5 years</v>
+      <c r="I37" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2399,12 +2288,11 @@
       <c r="G38" s="16">
         <v>0.09140000000000001</v>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="17">
         <v>0.08939999999999999</v>
       </c>
-      <c r="I38" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B38:H38),B38:H38,0)),"")</f>
-        <v>5 years</v>
+      <c r="I38" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2429,12 +2317,11 @@
       <c r="G39" s="16">
         <v>0.09210000000000002</v>
       </c>
-      <c r="H39" s="16">
+      <c r="H39" s="17">
         <v>0.09050000000000001</v>
       </c>
-      <c r="I39" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B39:H39),B39:H39,0)),"")</f>
-        <v>5 years</v>
+      <c r="I39" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2459,12 +2346,11 @@
       <c r="G40" s="16">
         <v>0.0935</v>
       </c>
-      <c r="H40" s="16">
+      <c r="H40" s="17">
         <v>0.09269999999999999</v>
       </c>
-      <c r="I40" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B40:H40),B40:H40,0)),"")</f>
-        <v>5 years</v>
+      <c r="I40" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2489,12 +2375,11 @@
       <c r="G41" s="16">
         <v>0.0956</v>
       </c>
-      <c r="H41" s="16">
+      <c r="H41" s="17">
         <v>0.095</v>
       </c>
-      <c r="I41" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B41:H41),B41:H41,0)),"")</f>
-        <v>5 years</v>
+      <c r="I41" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2516,15 +2401,14 @@
       <c r="F42" s="16">
         <v>0.0935</v>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="17">
         <v>0.09329999999999999</v>
       </c>
-      <c r="H42" s="16">
+      <c r="H42" s="17">
         <v>0.09329999999999999</v>
       </c>
-      <c r="I42" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B42:H42),B42:H42,0)),"")</f>
-        <v>4 years</v>
+      <c r="I42" s="18" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2543,7 +2427,7 @@
       <c r="E43" s="16">
         <v>0.092</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="17">
         <v>0.09119999999999999</v>
       </c>
       <c r="G43" s="16">
@@ -2552,9 +2436,8 @@
       <c r="H43" s="16">
         <v>0.09130000000000001</v>
       </c>
-      <c r="I43" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B43:H43),B43:H43,0)),"")</f>
-        <v>3 years</v>
+      <c r="I43" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2570,7 +2453,7 @@
       <c r="D44" s="16">
         <v>0.09300000000000001</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="17">
         <v>0.09029999999999999</v>
       </c>
       <c r="F44" s="16">
@@ -2582,9 +2465,8 @@
       <c r="H44" s="16">
         <v>0.09130000000000001</v>
       </c>
-      <c r="I44" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B44:H44),B44:H44,0)),"")</f>
-        <v>2 years</v>
+      <c r="I44" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2600,7 +2482,7 @@
       <c r="D45" s="16">
         <v>0.092</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="17">
         <v>0.08960000000000001</v>
       </c>
       <c r="F45" s="16">
@@ -2612,9 +2494,8 @@
       <c r="H45" s="16">
         <v>0.09130000000000001</v>
       </c>
-      <c r="I45" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B45:H45),B45:H45,0)),"")</f>
-        <v>2 years</v>
+      <c r="I45" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2630,7 +2511,7 @@
       <c r="D46" s="16">
         <v>0.08960000000000001</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="17">
         <v>0.0862</v>
       </c>
       <c r="F46" s="16">
@@ -2642,9 +2523,8 @@
       <c r="H46" s="16">
         <v>0.08929999999999999</v>
       </c>
-      <c r="I46" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B46:H46),B46:H46,0)),"")</f>
-        <v>2 years</v>
+      <c r="I46" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2657,7 +2537,7 @@
       <c r="C47" s="16">
         <v>0.08470000000000001</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="17">
         <v>0.08169999999999999</v>
       </c>
       <c r="E47" s="16">
@@ -2672,9 +2552,8 @@
       <c r="H47" s="16">
         <v>0.08740000000000001</v>
       </c>
-      <c r="I47" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B47:H47),B47:H47,0)),"")</f>
-        <v>1 year</v>
+      <c r="I47" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2687,7 +2566,7 @@
       <c r="C48" s="16">
         <v>0.0735</v>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="17">
         <v>0.0728</v>
       </c>
       <c r="E48" s="16">
@@ -2702,9 +2581,8 @@
       <c r="H48" s="16">
         <v>0.0793</v>
       </c>
-      <c r="I48" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B48:H48),B48:H48,0)),"")</f>
-        <v>1 year</v>
+      <c r="I48" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2717,7 +2595,7 @@
       <c r="C49" s="16">
         <v>0.06950000000000001</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="17">
         <v>0.0689</v>
       </c>
       <c r="E49" s="16">
@@ -2732,9 +2610,8 @@
       <c r="H49" s="16">
         <v>0.07539999999999999</v>
       </c>
-      <c r="I49" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B49:H49),B49:H49,0)),"")</f>
-        <v>1 year</v>
+      <c r="I49" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2747,7 +2624,7 @@
       <c r="C50" s="16">
         <v>0.0635</v>
       </c>
-      <c r="D50" s="16">
+      <c r="D50" s="17">
         <v>0.06150000000000001</v>
       </c>
       <c r="E50" s="16">
@@ -2762,9 +2639,8 @@
       <c r="H50" s="16">
         <v>0.06860000000000001</v>
       </c>
-      <c r="I50" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B50:H50),B50:H50,0)),"")</f>
-        <v>1 year</v>
+      <c r="I50" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2777,7 +2653,7 @@
       <c r="C51" s="16">
         <v>0.0587</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="17">
         <v>0.0578</v>
       </c>
       <c r="E51" s="16">
@@ -2792,9 +2668,8 @@
       <c r="H51" s="16">
         <v>0.0655</v>
       </c>
-      <c r="I51" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B51:H51),B51:H51,0)),"")</f>
-        <v>1 year</v>
+      <c r="I51" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2807,7 +2682,7 @@
       <c r="C52" s="16">
         <v>0.0578</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="17">
         <v>0.0576</v>
       </c>
       <c r="E52" s="16">
@@ -2822,9 +2697,8 @@
       <c r="H52" s="16">
         <v>0.07389999999999999</v>
       </c>
-      <c r="I52" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B52:H52),B52:H52,0)),"")</f>
-        <v>1 year</v>
+      <c r="I52" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2834,7 +2708,7 @@
       <c r="B53" s="16">
         <v>0.06370000000000001</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="17">
         <v>0.0572</v>
       </c>
       <c r="D53" s="16">
@@ -2852,9 +2726,8 @@
       <c r="H53" s="16">
         <v>0.07519999999999999</v>
       </c>
-      <c r="I53" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B53:H53),B53:H53,0)),"")</f>
-        <v>6 months</v>
+      <c r="I53" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2864,7 +2737,7 @@
       <c r="B54" s="16">
         <v>0.06370000000000001</v>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="17">
         <v>0.0553</v>
       </c>
       <c r="D54" s="16">
@@ -2882,9 +2755,8 @@
       <c r="H54" s="16">
         <v>0.07690000000000001</v>
       </c>
-      <c r="I54" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B54:H54),B54:H54,0)),"")</f>
-        <v>6 months</v>
+      <c r="I54" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2894,7 +2766,7 @@
       <c r="B55" s="16">
         <v>0.06370000000000001</v>
       </c>
-      <c r="C55" s="16">
+      <c r="C55" s="17">
         <v>0.0549</v>
       </c>
       <c r="D55" s="16">
@@ -2912,9 +2784,8 @@
       <c r="H55" s="16">
         <v>0.0795</v>
       </c>
-      <c r="I55" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B55:H55),B55:H55,0)),"")</f>
-        <v>6 months</v>
+      <c r="I55" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2924,7 +2795,7 @@
       <c r="B56" s="16">
         <v>0.06370000000000001</v>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="17">
         <v>0.0548</v>
       </c>
       <c r="D56" s="16">
@@ -2942,9 +2813,8 @@
       <c r="H56" s="16">
         <v>0.08</v>
       </c>
-      <c r="I56" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B56:H56),B56:H56,0)),"")</f>
-        <v>6 months</v>
+      <c r="I56" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2954,7 +2824,7 @@
       <c r="B57" s="16">
         <v>0.0633</v>
       </c>
-      <c r="C57" s="16">
+      <c r="C57" s="17">
         <v>0.0549</v>
       </c>
       <c r="D57" s="16">
@@ -2972,9 +2842,8 @@
       <c r="H57" s="16">
         <v>0.08310000000000001</v>
       </c>
-      <c r="I57" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B57:H57),B57:H57,0)),"")</f>
-        <v>6 months</v>
+      <c r="I57" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2984,7 +2853,7 @@
       <c r="B58" s="16">
         <v>0.0622</v>
       </c>
-      <c r="C58" s="16">
+      <c r="C58" s="17">
         <v>0.0547</v>
       </c>
       <c r="D58" s="16">
@@ -3002,9 +2871,8 @@
       <c r="H58" s="16">
         <v>0.0842</v>
       </c>
-      <c r="I58" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B58:H58),B58:H58,0)),"")</f>
-        <v>6 months</v>
+      <c r="I58" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -3014,7 +2882,7 @@
       <c r="B59" s="16">
         <v>0.06150000000000001</v>
       </c>
-      <c r="C59" s="16">
+      <c r="C59" s="17">
         <v>0.0566</v>
       </c>
       <c r="D59" s="16">
@@ -3032,9 +2900,8 @@
       <c r="H59" s="16">
         <v>0.0868</v>
       </c>
-      <c r="I59" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B59:H59),B59:H59,0)),"")</f>
-        <v>6 months</v>
+      <c r="I59" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -3044,7 +2911,7 @@
       <c r="B60" s="16">
         <v>0.0607</v>
       </c>
-      <c r="C60" s="16">
+      <c r="C60" s="17">
         <v>0.05769999999999999</v>
       </c>
       <c r="D60" s="16">
@@ -3062,9 +2929,8 @@
       <c r="H60" s="16">
         <v>0.0868</v>
       </c>
-      <c r="I60" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B60:H60),B60:H60,0)),"")</f>
-        <v>6 months</v>
+      <c r="I60" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -3074,7 +2940,7 @@
       <c r="B61" s="16">
         <v>0.0607</v>
       </c>
-      <c r="C61" s="16">
+      <c r="C61" s="17">
         <v>0.0581</v>
       </c>
       <c r="D61" s="16">
@@ -3092,9 +2958,8 @@
       <c r="H61" s="16">
         <v>0.0868</v>
       </c>
-      <c r="I61" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B61:H61),B61:H61,0)),"")</f>
-        <v>6 months</v>
+      <c r="I61" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -3104,7 +2969,7 @@
       <c r="B62" s="16">
         <v>0.0607</v>
       </c>
-      <c r="C62" s="16">
+      <c r="C62" s="17">
         <v>0.0581</v>
       </c>
       <c r="D62" s="16">
@@ -3122,9 +2987,8 @@
       <c r="H62" s="16">
         <v>0.08650000000000001</v>
       </c>
-      <c r="I62" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B62:H62),B62:H62,0)),"")</f>
-        <v>6 months</v>
+      <c r="I62" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -3134,7 +2998,7 @@
       <c r="B63" s="16">
         <v>0.05980000000000001</v>
       </c>
-      <c r="C63" s="16">
+      <c r="C63" s="17">
         <v>0.0582</v>
       </c>
       <c r="D63" s="16">
@@ -3152,9 +3016,8 @@
       <c r="H63" s="16">
         <v>0.0857</v>
       </c>
-      <c r="I63" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B63:H63),B63:H63,0)),"")</f>
-        <v>6 months</v>
+      <c r="I63" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -3164,7 +3027,7 @@
       <c r="B64" s="16">
         <v>0.05980000000000001</v>
       </c>
-      <c r="C64" s="16">
+      <c r="C64" s="17">
         <v>0.0582</v>
       </c>
       <c r="D64" s="16">
@@ -3182,9 +3045,8 @@
       <c r="H64" s="16">
         <v>0.08470000000000001</v>
       </c>
-      <c r="I64" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B64:H64),B64:H64,0)),"")</f>
-        <v>6 months</v>
+      <c r="I64" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -3194,7 +3056,7 @@
       <c r="B65" s="16">
         <v>0.05980000000000001</v>
       </c>
-      <c r="C65" s="16">
+      <c r="C65" s="17">
         <v>0.05769999999999999</v>
       </c>
       <c r="D65" s="16">
@@ -3212,9 +3074,8 @@
       <c r="H65" s="16">
         <v>0.0843</v>
       </c>
-      <c r="I65" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B65:H65),B65:H65,0)),"")</f>
-        <v>6 months</v>
+      <c r="I65" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -3224,7 +3085,7 @@
       <c r="B66" s="16">
         <v>0.05980000000000001</v>
       </c>
-      <c r="C66" s="16">
+      <c r="C66" s="17">
         <v>0.0584</v>
       </c>
       <c r="D66" s="16">
@@ -3242,9 +3103,8 @@
       <c r="H66" s="16">
         <v>0.08400000000000001</v>
       </c>
-      <c r="I66" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B66:H66),B66:H66,0)),"")</f>
-        <v>6 months</v>
+      <c r="I66" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -3254,7 +3114,7 @@
       <c r="B67" s="16">
         <v>0.0612</v>
       </c>
-      <c r="C67" s="16">
+      <c r="C67" s="17">
         <v>0.05980000000000001</v>
       </c>
       <c r="D67" s="16">
@@ -3272,9 +3132,8 @@
       <c r="H67" s="16">
         <v>0.083</v>
       </c>
-      <c r="I67" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B67:H67),B67:H67,0)),"")</f>
-        <v>6 months</v>
+      <c r="I67" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -3284,7 +3143,7 @@
       <c r="B68" s="16">
         <v>0.0612</v>
       </c>
-      <c r="C68" s="16">
+      <c r="C68" s="17">
         <v>0.06059999999999999</v>
       </c>
       <c r="D68" s="16">
@@ -3302,9 +3161,8 @@
       <c r="H68" s="16">
         <v>0.0775</v>
       </c>
-      <c r="I68" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B68:H68),B68:H68,0)),"")</f>
-        <v>6 months</v>
+      <c r="I68" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -3314,7 +3172,7 @@
       <c r="B69" s="16">
         <v>0.0635</v>
       </c>
-      <c r="C69" s="16">
+      <c r="C69" s="17">
         <v>0.0619</v>
       </c>
       <c r="D69" s="16">
@@ -3332,9 +3190,8 @@
       <c r="H69" s="16">
         <v>0.07719999999999999</v>
       </c>
-      <c r="I69" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B69:H69),B69:H69,0)),"")</f>
-        <v>6 months</v>
+      <c r="I69" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -3344,7 +3201,7 @@
       <c r="B70" s="16">
         <v>0.0634</v>
       </c>
-      <c r="C70" s="16">
+      <c r="C70" s="17">
         <v>0.0624</v>
       </c>
       <c r="D70" s="16">
@@ -3362,9 +3219,8 @@
       <c r="H70" s="16">
         <v>0.077</v>
       </c>
-      <c r="I70" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B70:H70),B70:H70,0)),"")</f>
-        <v>6 months</v>
+      <c r="I70" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -3374,7 +3230,7 @@
       <c r="B71" s="16">
         <v>0.0634</v>
       </c>
-      <c r="C71" s="16">
+      <c r="C71" s="17">
         <v>0.0624</v>
       </c>
       <c r="D71" s="16">
@@ -3392,9 +3248,8 @@
       <c r="H71" s="16">
         <v>0.077</v>
       </c>
-      <c r="I71" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B71:H71),B71:H71,0)),"")</f>
-        <v>6 months</v>
+      <c r="I71" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -3404,7 +3259,7 @@
       <c r="B72" s="16">
         <v>0.0634</v>
       </c>
-      <c r="C72" s="16">
+      <c r="C72" s="17">
         <v>0.0624</v>
       </c>
       <c r="D72" s="16">
@@ -3422,9 +3277,8 @@
       <c r="H72" s="16">
         <v>0.077</v>
       </c>
-      <c r="I72" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B72:H72),B72:H72,0)),"")</f>
-        <v>6 months</v>
+      <c r="I72" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3434,7 +3288,7 @@
       <c r="B73" s="16">
         <v>0.0634</v>
       </c>
-      <c r="C73" s="16">
+      <c r="C73" s="17">
         <v>0.0624</v>
       </c>
       <c r="D73" s="16">
@@ -3452,9 +3306,8 @@
       <c r="H73" s="16">
         <v>0.077</v>
       </c>
-      <c r="I73" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B73:H73),B73:H73,0)),"")</f>
-        <v>6 months</v>
+      <c r="I73" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -3464,7 +3317,7 @@
       <c r="B74" s="16">
         <v>0.0634</v>
       </c>
-      <c r="C74" s="16">
+      <c r="C74" s="17">
         <v>0.06269999999999999</v>
       </c>
       <c r="D74" s="16">
@@ -3482,9 +3335,8 @@
       <c r="H74" s="16">
         <v>0.077</v>
       </c>
-      <c r="I74" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B74:H74),B74:H74,0)),"")</f>
-        <v>6 months</v>
+      <c r="I74" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -3494,7 +3346,7 @@
       <c r="B75" s="16">
         <v>0.0634</v>
       </c>
-      <c r="C75" s="16">
+      <c r="C75" s="17">
         <v>0.062</v>
       </c>
       <c r="D75" s="16">
@@ -3512,16 +3364,15 @@
       <c r="H75" s="16">
         <v>0.077</v>
       </c>
-      <c r="I75" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B75:H75),B75:H75,0)),"")</f>
-        <v>6 months</v>
+      <c r="I75" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="15">
         <v>40633</v>
       </c>
-      <c r="B76" s="16">
+      <c r="B76" s="17">
         <v>0.0593</v>
       </c>
       <c r="C76" s="16">
@@ -3542,9 +3393,8 @@
       <c r="H76" s="16">
         <v>0.0765</v>
       </c>
-      <c r="I76" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B76:H76),B76:H76,0)),"")</f>
-        <v>Floating</v>
+      <c r="I76" s="18" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3554,7 +3404,7 @@
       <c r="B77" s="16">
         <v>0.05889999999999999</v>
       </c>
-      <c r="C77" s="16">
+      <c r="C77" s="17">
         <v>0.0583</v>
       </c>
       <c r="D77" s="16">
@@ -3572,9 +3422,8 @@
       <c r="H77" s="16">
         <v>0.0765</v>
       </c>
-      <c r="I77" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B77:H77),B77:H77,0)),"")</f>
-        <v>6 months</v>
+      <c r="I77" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3584,7 +3433,7 @@
       <c r="B78" s="16">
         <v>0.0587</v>
       </c>
-      <c r="C78" s="16">
+      <c r="C78" s="17">
         <v>0.0584</v>
       </c>
       <c r="D78" s="16">
@@ -3602,9 +3451,8 @@
       <c r="H78" s="16">
         <v>0.0765</v>
       </c>
-      <c r="I78" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B78:H78),B78:H78,0)),"")</f>
-        <v>6 months</v>
+      <c r="I78" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3614,7 +3462,7 @@
       <c r="B79" s="16">
         <v>0.0587</v>
       </c>
-      <c r="C79" s="16">
+      <c r="C79" s="17">
         <v>0.0584</v>
       </c>
       <c r="D79" s="16">
@@ -3632,9 +3480,8 @@
       <c r="H79" s="16">
         <v>0.0765</v>
       </c>
-      <c r="I79" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B79:H79),B79:H79,0)),"")</f>
-        <v>6 months</v>
+      <c r="I79" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3644,7 +3491,7 @@
       <c r="B80" s="16">
         <v>0.0587</v>
       </c>
-      <c r="C80" s="16">
+      <c r="C80" s="17">
         <v>0.0584</v>
       </c>
       <c r="D80" s="16">
@@ -3662,9 +3509,8 @@
       <c r="H80" s="16">
         <v>0.07629999999999999</v>
       </c>
-      <c r="I80" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B80:H80),B80:H80,0)),"")</f>
-        <v>6 months</v>
+      <c r="I80" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -3674,7 +3520,7 @@
       <c r="B81" s="16">
         <v>0.0587</v>
       </c>
-      <c r="C81" s="16">
+      <c r="C81" s="17">
         <v>0.05860000000000001</v>
       </c>
       <c r="D81" s="16">
@@ -3692,9 +3538,8 @@
       <c r="H81" s="16">
         <v>0.07629999999999999</v>
       </c>
-      <c r="I81" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B81:H81),B81:H81,0)),"")</f>
-        <v>6 months</v>
+      <c r="I81" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3704,7 +3549,7 @@
       <c r="B82" s="16">
         <v>0.0587</v>
       </c>
-      <c r="C82" s="16">
+      <c r="C82" s="17">
         <v>0.0585</v>
       </c>
       <c r="D82" s="16">
@@ -3722,9 +3567,8 @@
       <c r="H82" s="16">
         <v>0.07629999999999999</v>
       </c>
-      <c r="I82" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B82:H82),B82:H82,0)),"")</f>
-        <v>6 months</v>
+      <c r="I82" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3734,7 +3578,7 @@
       <c r="B83" s="16">
         <v>0.0585</v>
       </c>
-      <c r="C83" s="16">
+      <c r="C83" s="17">
         <v>0.0581</v>
       </c>
       <c r="D83" s="16">
@@ -3752,9 +3596,8 @@
       <c r="H83" s="16">
         <v>0.0756</v>
       </c>
-      <c r="I83" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B83:H83),B83:H83,0)),"")</f>
-        <v>6 months</v>
+      <c r="I83" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3764,7 +3607,7 @@
       <c r="B84" s="16">
         <v>0.0583</v>
       </c>
-      <c r="C84" s="16">
+      <c r="C84" s="17">
         <v>0.0567</v>
       </c>
       <c r="D84" s="16">
@@ -3782,9 +3625,8 @@
       <c r="H84" s="16">
         <v>0.0722</v>
       </c>
-      <c r="I84" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B84:H84),B84:H84,0)),"")</f>
-        <v>6 months</v>
+      <c r="I84" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -3794,7 +3636,7 @@
       <c r="B85" s="16">
         <v>0.05860000000000001</v>
       </c>
-      <c r="C85" s="16">
+      <c r="C85" s="17">
         <v>0.0572</v>
       </c>
       <c r="D85" s="16">
@@ -3812,9 +3654,8 @@
       <c r="H85" s="16">
         <v>0.0722</v>
       </c>
-      <c r="I85" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B85:H85),B85:H85,0)),"")</f>
-        <v>6 months</v>
+      <c r="I85" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -3824,7 +3665,7 @@
       <c r="B86" s="16">
         <v>0.05860000000000001</v>
       </c>
-      <c r="C86" s="16">
+      <c r="C86" s="17">
         <v>0.0566</v>
       </c>
       <c r="D86" s="16">
@@ -3842,9 +3683,8 @@
       <c r="H86" s="16">
         <v>0.07200000000000001</v>
       </c>
-      <c r="I86" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B86:H86),B86:H86,0)),"")</f>
-        <v>6 months</v>
+      <c r="I86" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3854,7 +3694,7 @@
       <c r="B87" s="16">
         <v>0.05860000000000001</v>
       </c>
-      <c r="C87" s="16">
+      <c r="C87" s="17">
         <v>0.0564</v>
       </c>
       <c r="D87" s="16">
@@ -3872,9 +3712,8 @@
       <c r="H87" s="16">
         <v>0.0693</v>
       </c>
-      <c r="I87" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B87:H87),B87:H87,0)),"")</f>
-        <v>6 months</v>
+      <c r="I87" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -3884,10 +3723,10 @@
       <c r="B88" s="16">
         <v>0.05860000000000001</v>
       </c>
-      <c r="C88" s="16">
+      <c r="C88" s="17">
         <v>0.0564</v>
       </c>
-      <c r="D88" s="16">
+      <c r="D88" s="17">
         <v>0.0564</v>
       </c>
       <c r="E88" s="16">
@@ -3902,9 +3741,8 @@
       <c r="H88" s="16">
         <v>0.06900000000000001</v>
       </c>
-      <c r="I88" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B88:H88),B88:H88,0)),"")</f>
-        <v>6 months</v>
+      <c r="I88" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -3917,7 +3755,7 @@
       <c r="C89" s="16">
         <v>0.0567</v>
       </c>
-      <c r="D89" s="16">
+      <c r="D89" s="17">
         <v>0.0564</v>
       </c>
       <c r="E89" s="16">
@@ -3932,9 +3770,8 @@
       <c r="H89" s="16">
         <v>0.06900000000000001</v>
       </c>
-      <c r="I89" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B89:H89),B89:H89,0)),"")</f>
-        <v>1 year</v>
+      <c r="I89" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -3947,7 +3784,7 @@
       <c r="C90" s="16">
         <v>0.05599999999999999</v>
       </c>
-      <c r="D90" s="16">
+      <c r="D90" s="17">
         <v>0.0529</v>
       </c>
       <c r="E90" s="16">
@@ -3962,9 +3799,8 @@
       <c r="H90" s="16">
         <v>0.06570000000000001</v>
       </c>
-      <c r="I90" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B90:H90),B90:H90,0)),"")</f>
-        <v>1 year</v>
+      <c r="I90" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -3977,7 +3813,7 @@
       <c r="C91" s="16">
         <v>0.0556</v>
       </c>
-      <c r="D91" s="16">
+      <c r="D91" s="17">
         <v>0.0529</v>
       </c>
       <c r="E91" s="16">
@@ -3992,9 +3828,8 @@
       <c r="H91" s="16">
         <v>0.06570000000000001</v>
       </c>
-      <c r="I91" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B91:H91),B91:H91,0)),"")</f>
-        <v>1 year</v>
+      <c r="I91" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -4007,7 +3842,7 @@
       <c r="C92" s="16">
         <v>0.0558</v>
       </c>
-      <c r="D92" s="16">
+      <c r="D92" s="17">
         <v>0.0537</v>
       </c>
       <c r="E92" s="16">
@@ -4022,9 +3857,8 @@
       <c r="H92" s="16">
         <v>0.06570000000000001</v>
       </c>
-      <c r="I92" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B92:H92),B92:H92,0)),"")</f>
-        <v>1 year</v>
+      <c r="I92" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -4037,7 +3871,7 @@
       <c r="C93" s="16">
         <v>0.0558</v>
       </c>
-      <c r="D93" s="16">
+      <c r="D93" s="17">
         <v>0.0539</v>
       </c>
       <c r="E93" s="16">
@@ -4052,9 +3886,8 @@
       <c r="H93" s="16">
         <v>0.0654</v>
       </c>
-      <c r="I93" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B93:H93),B93:H93,0)),"")</f>
-        <v>1 year</v>
+      <c r="I93" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -4067,7 +3900,7 @@
       <c r="C94" s="16">
         <v>0.0544</v>
       </c>
-      <c r="D94" s="16">
+      <c r="D94" s="17">
         <v>0.0537</v>
       </c>
       <c r="E94" s="16">
@@ -4082,9 +3915,8 @@
       <c r="H94" s="16">
         <v>0.0646</v>
       </c>
-      <c r="I94" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B94:H94),B94:H94,0)),"")</f>
-        <v>1 year</v>
+      <c r="I94" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -4097,7 +3929,7 @@
       <c r="C95" s="16">
         <v>0.0536</v>
       </c>
-      <c r="D95" s="16">
+      <c r="D95" s="17">
         <v>0.0528</v>
       </c>
       <c r="E95" s="16">
@@ -4112,9 +3944,8 @@
       <c r="H95" s="16">
         <v>0.0646</v>
       </c>
-      <c r="I95" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B95:H95),B95:H95,0)),"")</f>
-        <v>1 year</v>
+      <c r="I95" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -4124,10 +3955,10 @@
       <c r="B96" s="16">
         <v>0.0579</v>
       </c>
-      <c r="C96" s="16">
+      <c r="C96" s="17">
         <v>0.0529</v>
       </c>
-      <c r="D96" s="16">
+      <c r="D96" s="17">
         <v>0.0529</v>
       </c>
       <c r="E96" s="16">
@@ -4142,9 +3973,8 @@
       <c r="H96" s="16">
         <v>0.0646</v>
       </c>
-      <c r="I96" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B96:H96),B96:H96,0)),"")</f>
-        <v>6 months</v>
+      <c r="I96" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -4154,7 +3984,7 @@
       <c r="B97" s="16">
         <v>0.058</v>
       </c>
-      <c r="C97" s="16">
+      <c r="C97" s="17">
         <v>0.0538</v>
       </c>
       <c r="D97" s="16">
@@ -4172,9 +4002,8 @@
       <c r="H97" s="16">
         <v>0.0654</v>
       </c>
-      <c r="I97" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B97:H97),B97:H97,0)),"")</f>
-        <v>6 months</v>
+      <c r="I97" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -4187,7 +4016,7 @@
       <c r="C98" s="16">
         <v>0.0546</v>
       </c>
-      <c r="D98" s="16">
+      <c r="D98" s="17">
         <v>0.0539</v>
       </c>
       <c r="E98" s="16">
@@ -4202,9 +4031,8 @@
       <c r="H98" s="16">
         <v>0.06519999999999999</v>
       </c>
-      <c r="I98" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B98:H98),B98:H98,0)),"")</f>
-        <v>1 year</v>
+      <c r="I98" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -4217,7 +4045,7 @@
       <c r="C99" s="16">
         <v>0.0542</v>
       </c>
-      <c r="D99" s="16">
+      <c r="D99" s="17">
         <v>0.0538</v>
       </c>
       <c r="E99" s="16">
@@ -4232,9 +4060,8 @@
       <c r="H99" s="16">
         <v>0.0645</v>
       </c>
-      <c r="I99" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B99:H99),B99:H99,0)),"")</f>
-        <v>1 year</v>
+      <c r="I99" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -4247,7 +4074,7 @@
       <c r="C100" s="16">
         <v>0.0544</v>
       </c>
-      <c r="D100" s="16">
+      <c r="D100" s="17">
         <v>0.0537</v>
       </c>
       <c r="E100" s="16">
@@ -4262,9 +4089,8 @@
       <c r="H100" s="16">
         <v>0.06370000000000001</v>
       </c>
-      <c r="I100" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B100:H100),B100:H100,0)),"")</f>
-        <v>1 year</v>
+      <c r="I100" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -4277,7 +4103,7 @@
       <c r="C101" s="16">
         <v>0.0541</v>
       </c>
-      <c r="D101" s="16">
+      <c r="D101" s="17">
         <v>0.0528</v>
       </c>
       <c r="E101" s="16">
@@ -4292,9 +4118,8 @@
       <c r="H101" s="16">
         <v>0.0635</v>
       </c>
-      <c r="I101" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B101:H101),B101:H101,0)),"")</f>
-        <v>1 year</v>
+      <c r="I101" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -4307,7 +4132,7 @@
       <c r="C102" s="16">
         <v>0.0541</v>
       </c>
-      <c r="D102" s="16">
+      <c r="D102" s="17">
         <v>0.05309999999999999</v>
       </c>
       <c r="E102" s="16">
@@ -4322,9 +4147,8 @@
       <c r="H102" s="16">
         <v>0.0635</v>
       </c>
-      <c r="I102" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B102:H102),B102:H102,0)),"")</f>
-        <v>1 year</v>
+      <c r="I102" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -4337,7 +4161,7 @@
       <c r="C103" s="16">
         <v>0.0539</v>
       </c>
-      <c r="D103" s="16">
+      <c r="D103" s="17">
         <v>0.0526</v>
       </c>
       <c r="E103" s="16">
@@ -4352,9 +4176,8 @@
       <c r="H103" s="16">
         <v>0.0639</v>
       </c>
-      <c r="I103" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B103:H103),B103:H103,0)),"")</f>
-        <v>1 year</v>
+      <c r="I103" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -4367,7 +4190,7 @@
       <c r="C104" s="16">
         <v>0.0538</v>
       </c>
-      <c r="D104" s="16">
+      <c r="D104" s="17">
         <v>0.0527</v>
       </c>
       <c r="E104" s="16">
@@ -4382,9 +4205,8 @@
       <c r="H104" s="16">
         <v>0.0663</v>
       </c>
-      <c r="I104" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B104:H104),B104:H104,0)),"")</f>
-        <v>1 year</v>
+      <c r="I104" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -4397,7 +4219,7 @@
       <c r="C105" s="16">
         <v>0.05400000000000001</v>
       </c>
-      <c r="D105" s="16">
+      <c r="D105" s="17">
         <v>0.05309999999999999</v>
       </c>
       <c r="E105" s="16">
@@ -4412,9 +4234,8 @@
       <c r="H105" s="16">
         <v>0.0678</v>
       </c>
-      <c r="I105" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B105:H105),B105:H105,0)),"")</f>
-        <v>1 year</v>
+      <c r="I105" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -4427,7 +4248,7 @@
       <c r="C106" s="16">
         <v>0.0542</v>
       </c>
-      <c r="D106" s="16">
+      <c r="D106" s="17">
         <v>0.0537</v>
       </c>
       <c r="E106" s="16">
@@ -4442,9 +4263,8 @@
       <c r="H106" s="16">
         <v>0.0698</v>
       </c>
-      <c r="I106" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B106:H106),B106:H106,0)),"")</f>
-        <v>1 year</v>
+      <c r="I106" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -4457,7 +4277,7 @@
       <c r="C107" s="16">
         <v>0.0537</v>
       </c>
-      <c r="D107" s="16">
+      <c r="D107" s="17">
         <v>0.0532</v>
       </c>
       <c r="E107" s="16">
@@ -4472,9 +4292,8 @@
       <c r="H107" s="16">
         <v>0.0698</v>
       </c>
-      <c r="I107" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B107:H107),B107:H107,0)),"")</f>
-        <v>1 year</v>
+      <c r="I107" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -4487,7 +4306,7 @@
       <c r="C108" s="16">
         <v>0.0539</v>
       </c>
-      <c r="D108" s="16">
+      <c r="D108" s="17">
         <v>0.0534</v>
       </c>
       <c r="E108" s="16">
@@ -4502,9 +4321,8 @@
       <c r="H108" s="16">
         <v>0.0697</v>
       </c>
-      <c r="I108" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B108:H108),B108:H108,0)),"")</f>
-        <v>1 year</v>
+      <c r="I108" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -4514,7 +4332,7 @@
       <c r="B109" s="16">
         <v>0.0583</v>
       </c>
-      <c r="C109" s="16">
+      <c r="C109" s="17">
         <v>0.0542</v>
       </c>
       <c r="D109" s="16">
@@ -4532,9 +4350,8 @@
       <c r="H109" s="16">
         <v>0.0707</v>
       </c>
-      <c r="I109" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B109:H109),B109:H109,0)),"")</f>
-        <v>6 months</v>
+      <c r="I109" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -4544,7 +4361,7 @@
       <c r="B110" s="16">
         <v>0.0583</v>
       </c>
-      <c r="C110" s="16">
+      <c r="C110" s="17">
         <v>0.0542</v>
       </c>
       <c r="D110" s="16">
@@ -4562,9 +4379,8 @@
       <c r="H110" s="16">
         <v>0.0709</v>
       </c>
-      <c r="I110" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B110:H110),B110:H110,0)),"")</f>
-        <v>6 months</v>
+      <c r="I110" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -4574,7 +4390,7 @@
       <c r="B111" s="16">
         <v>0.0583</v>
       </c>
-      <c r="C111" s="16">
+      <c r="C111" s="17">
         <v>0.05429999999999999</v>
       </c>
       <c r="D111" s="16">
@@ -4592,9 +4408,8 @@
       <c r="H111" s="16">
         <v>0.0709</v>
       </c>
-      <c r="I111" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B111:H111),B111:H111,0)),"")</f>
-        <v>6 months</v>
+      <c r="I111" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -4604,7 +4419,7 @@
       <c r="B112" s="16">
         <v>0.0601</v>
       </c>
-      <c r="C112" s="16">
+      <c r="C112" s="17">
         <v>0.0554</v>
       </c>
       <c r="D112" s="16">
@@ -4622,9 +4437,8 @@
       <c r="H112" s="16">
         <v>0.07290000000000001</v>
       </c>
-      <c r="I112" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B112:H112),B112:H112,0)),"")</f>
-        <v>6 months</v>
+      <c r="I112" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -4634,7 +4448,7 @@
       <c r="B113" s="16">
         <v>0.0605</v>
       </c>
-      <c r="C113" s="16">
+      <c r="C113" s="17">
         <v>0.0559</v>
       </c>
       <c r="D113" s="16">
@@ -4652,9 +4466,8 @@
       <c r="H113" s="16">
         <v>0.07339999999999999</v>
       </c>
-      <c r="I113" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B113:H113),B113:H113,0)),"")</f>
-        <v>6 months</v>
+      <c r="I113" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -4664,7 +4477,7 @@
       <c r="B114" s="16">
         <v>0.06179999999999999</v>
       </c>
-      <c r="C114" s="16">
+      <c r="C114" s="17">
         <v>0.0572</v>
       </c>
       <c r="D114" s="16">
@@ -4682,9 +4495,8 @@
       <c r="H114" s="16">
         <v>0.0726</v>
       </c>
-      <c r="I114" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B114:H114),B114:H114,0)),"")</f>
-        <v>6 months</v>
+      <c r="I114" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -4694,7 +4506,7 @@
       <c r="B115" s="16">
         <v>0.0633</v>
       </c>
-      <c r="C115" s="16">
+      <c r="C115" s="17">
         <v>0.0582</v>
       </c>
       <c r="D115" s="16">
@@ -4712,9 +4524,8 @@
       <c r="H115" s="16">
         <v>0.0718</v>
       </c>
-      <c r="I115" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B115:H115),B115:H115,0)),"")</f>
-        <v>6 months</v>
+      <c r="I115" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -4724,7 +4535,7 @@
       <c r="B116" s="16">
         <v>0.06509999999999999</v>
       </c>
-      <c r="C116" s="16">
+      <c r="C116" s="17">
         <v>0.0591</v>
       </c>
       <c r="D116" s="16">
@@ -4742,9 +4553,8 @@
       <c r="H116" s="16">
         <v>0.0711</v>
       </c>
-      <c r="I116" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B116:H116),B116:H116,0)),"")</f>
-        <v>6 months</v>
+      <c r="I116" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -4754,7 +4564,7 @@
       <c r="B117" s="16">
         <v>0.06570000000000001</v>
       </c>
-      <c r="C117" s="16">
+      <c r="C117" s="17">
         <v>0.059</v>
       </c>
       <c r="D117" s="16">
@@ -4772,9 +4582,8 @@
       <c r="H117" s="16">
         <v>0.0711</v>
       </c>
-      <c r="I117" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B117:H117),B117:H117,0)),"")</f>
-        <v>6 months</v>
+      <c r="I117" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -4784,7 +4593,7 @@
       <c r="B118" s="16">
         <v>0.0659</v>
       </c>
-      <c r="C118" s="16">
+      <c r="C118" s="17">
         <v>0.0592</v>
       </c>
       <c r="D118" s="16">
@@ -4802,9 +4611,8 @@
       <c r="H118" s="16">
         <v>0.0712</v>
       </c>
-      <c r="I118" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B118:H118),B118:H118,0)),"")</f>
-        <v>6 months</v>
+      <c r="I118" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -4814,7 +4622,7 @@
       <c r="B119" s="16">
         <v>0.0659</v>
       </c>
-      <c r="C119" s="16">
+      <c r="C119" s="17">
         <v>0.0592</v>
       </c>
       <c r="D119" s="16">
@@ -4832,9 +4640,8 @@
       <c r="H119" s="16">
         <v>0.0709</v>
       </c>
-      <c r="I119" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B119:H119),B119:H119,0)),"")</f>
-        <v>6 months</v>
+      <c r="I119" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -4847,7 +4654,7 @@
       <c r="C120" s="16">
         <v>0.0591</v>
       </c>
-      <c r="D120" s="16">
+      <c r="D120" s="17">
         <v>0.05889999999999999</v>
       </c>
       <c r="E120" s="16">
@@ -4862,9 +4669,8 @@
       <c r="H120" s="16">
         <v>0.06849999999999999</v>
       </c>
-      <c r="I120" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B120:H120),B120:H120,0)),"")</f>
-        <v>1 year</v>
+      <c r="I120" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -4877,7 +4683,7 @@
       <c r="C121" s="16">
         <v>0.0591</v>
       </c>
-      <c r="D121" s="16">
+      <c r="D121" s="17">
         <v>0.0587</v>
       </c>
       <c r="E121" s="16">
@@ -4892,9 +4698,8 @@
       <c r="H121" s="16">
         <v>0.0683</v>
       </c>
-      <c r="I121" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B121:H121),B121:H121,0)),"")</f>
-        <v>1 year</v>
+      <c r="I121" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -4907,7 +4712,7 @@
       <c r="C122" s="16">
         <v>0.0591</v>
       </c>
-      <c r="D122" s="16">
+      <c r="D122" s="17">
         <v>0.0585</v>
       </c>
       <c r="E122" s="16">
@@ -4922,9 +4727,8 @@
       <c r="H122" s="16">
         <v>0.0674</v>
       </c>
-      <c r="I122" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B122:H122),B122:H122,0)),"")</f>
-        <v>1 year</v>
+      <c r="I122" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -4937,7 +4741,7 @@
       <c r="C123" s="16">
         <v>0.0588</v>
       </c>
-      <c r="D123" s="16">
+      <c r="D123" s="17">
         <v>0.0582</v>
       </c>
       <c r="E123" s="16">
@@ -4952,9 +4756,8 @@
       <c r="H123" s="16">
         <v>0.06519999999999999</v>
       </c>
-      <c r="I123" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B123:H123),B123:H123,0)),"")</f>
-        <v>1 year</v>
+      <c r="I123" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -4967,7 +4770,7 @@
       <c r="C124" s="16">
         <v>0.0588</v>
       </c>
-      <c r="D124" s="16">
+      <c r="D124" s="17">
         <v>0.0582</v>
       </c>
       <c r="E124" s="16">
@@ -4982,9 +4785,8 @@
       <c r="H124" s="16">
         <v>0.06509999999999999</v>
       </c>
-      <c r="I124" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B124:H124),B124:H124,0)),"")</f>
-        <v>1 year</v>
+      <c r="I124" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -4997,7 +4799,7 @@
       <c r="C125" s="16">
         <v>0.0584</v>
       </c>
-      <c r="D125" s="16">
+      <c r="D125" s="17">
         <v>0.0579</v>
       </c>
       <c r="E125" s="16">
@@ -5012,9 +4814,8 @@
       <c r="H125" s="16">
         <v>0.0643</v>
       </c>
-      <c r="I125" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B125:H125),B125:H125,0)),"")</f>
-        <v>1 year</v>
+      <c r="I125" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -5027,7 +4828,7 @@
       <c r="C126" s="16">
         <v>0.0576</v>
       </c>
-      <c r="D126" s="16">
+      <c r="D126" s="17">
         <v>0.0563</v>
       </c>
       <c r="E126" s="16">
@@ -5042,9 +4843,8 @@
       <c r="H126" s="16">
         <v>0.0619</v>
       </c>
-      <c r="I126" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B126:H126),B126:H126,0)),"")</f>
-        <v>1 year</v>
+      <c r="I126" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -5057,7 +4857,7 @@
       <c r="C127" s="16">
         <v>0.0567</v>
       </c>
-      <c r="D127" s="16">
+      <c r="D127" s="17">
         <v>0.0547</v>
       </c>
       <c r="E127" s="16">
@@ -5072,9 +4872,8 @@
       <c r="H127" s="16">
         <v>0.0612</v>
       </c>
-      <c r="I127" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B127:H127),B127:H127,0)),"")</f>
-        <v>1 year</v>
+      <c r="I127" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -5087,7 +4886,7 @@
       <c r="C128" s="16">
         <v>0.0554</v>
       </c>
-      <c r="D128" s="16">
+      <c r="D128" s="17">
         <v>0.0537</v>
       </c>
       <c r="E128" s="16">
@@ -5102,9 +4901,8 @@
       <c r="H128" s="16">
         <v>0.0608</v>
       </c>
-      <c r="I128" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B128:H128),B128:H128,0)),"")</f>
-        <v>1 year</v>
+      <c r="I128" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -5117,7 +4915,7 @@
       <c r="C129" s="16">
         <v>0.0546</v>
       </c>
-      <c r="D129" s="16">
+      <c r="D129" s="17">
         <v>0.0525</v>
       </c>
       <c r="E129" s="16">
@@ -5132,9 +4930,8 @@
       <c r="H129" s="16">
         <v>0.0601</v>
       </c>
-      <c r="I129" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B129:H129),B129:H129,0)),"")</f>
-        <v>1 year</v>
+      <c r="I129" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -5147,7 +4944,7 @@
       <c r="C130" s="16">
         <v>0.0535</v>
       </c>
-      <c r="D130" s="16">
+      <c r="D130" s="17">
         <v>0.05139999999999999</v>
       </c>
       <c r="E130" s="16">
@@ -5162,9 +4959,8 @@
       <c r="H130" s="16">
         <v>0.0584</v>
       </c>
-      <c r="I130" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B130:H130),B130:H130,0)),"")</f>
-        <v>1 year</v>
+      <c r="I130" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -5177,7 +4973,7 @@
       <c r="C131" s="16">
         <v>0.0529</v>
       </c>
-      <c r="D131" s="16">
+      <c r="D131" s="17">
         <v>0.0504</v>
       </c>
       <c r="E131" s="16">
@@ -5192,9 +4988,8 @@
       <c r="H131" s="16">
         <v>0.0572</v>
       </c>
-      <c r="I131" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B131:H131),B131:H131,0)),"")</f>
-        <v>1 year</v>
+      <c r="I131" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -5207,7 +5002,7 @@
       <c r="C132" s="16">
         <v>0.0529</v>
       </c>
-      <c r="D132" s="16">
+      <c r="D132" s="17">
         <v>0.0505</v>
       </c>
       <c r="E132" s="16">
@@ -5222,9 +5017,8 @@
       <c r="H132" s="16">
         <v>0.0572</v>
       </c>
-      <c r="I132" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B132:H132),B132:H132,0)),"")</f>
-        <v>1 year</v>
+      <c r="I132" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -5237,7 +5031,7 @@
       <c r="C133" s="16">
         <v>0.0527</v>
       </c>
-      <c r="D133" s="16">
+      <c r="D133" s="17">
         <v>0.0503</v>
       </c>
       <c r="E133" s="16">
@@ -5252,9 +5046,8 @@
       <c r="H133" s="16">
         <v>0.0576</v>
       </c>
-      <c r="I133" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B133:H133),B133:H133,0)),"")</f>
-        <v>1 year</v>
+      <c r="I133" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -5267,7 +5060,7 @@
       <c r="C134" s="16">
         <v>0.052</v>
       </c>
-      <c r="D134" s="16">
+      <c r="D134" s="17">
         <v>0.05</v>
       </c>
       <c r="E134" s="16">
@@ -5282,9 +5075,8 @@
       <c r="H134" s="16">
         <v>0.0576</v>
       </c>
-      <c r="I134" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B134:H134),B134:H134,0)),"")</f>
-        <v>1 year</v>
+      <c r="I134" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -5297,7 +5089,7 @@
       <c r="C135" s="16">
         <v>0.0516</v>
       </c>
-      <c r="D135" s="16">
+      <c r="D135" s="17">
         <v>0.0498</v>
       </c>
       <c r="E135" s="16">
@@ -5312,9 +5104,8 @@
       <c r="H135" s="16">
         <v>0.0576</v>
       </c>
-      <c r="I135" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B135:H135),B135:H135,0)),"")</f>
-        <v>1 year</v>
+      <c r="I135" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -5327,7 +5118,7 @@
       <c r="C136" s="16">
         <v>0.0513</v>
       </c>
-      <c r="D136" s="16">
+      <c r="D136" s="17">
         <v>0.04940000000000001</v>
       </c>
       <c r="E136" s="16">
@@ -5342,9 +5133,8 @@
       <c r="H136" s="16">
         <v>0.0566</v>
       </c>
-      <c r="I136" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B136:H136),B136:H136,0)),"")</f>
-        <v>1 year</v>
+      <c r="I136" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -5357,7 +5147,7 @@
       <c r="C137" s="16">
         <v>0.0512</v>
       </c>
-      <c r="D137" s="16">
+      <c r="D137" s="17">
         <v>0.0492</v>
       </c>
       <c r="E137" s="16">
@@ -5372,9 +5162,8 @@
       <c r="H137" s="16">
         <v>0.0565</v>
       </c>
-      <c r="I137" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B137:H137),B137:H137,0)),"")</f>
-        <v>1 year</v>
+      <c r="I137" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -5387,7 +5176,7 @@
       <c r="C138" s="16">
         <v>0.0508</v>
       </c>
-      <c r="D138" s="16">
+      <c r="D138" s="17">
         <v>0.0491</v>
       </c>
       <c r="E138" s="16">
@@ -5402,9 +5191,8 @@
       <c r="H138" s="16">
         <v>0.0562</v>
       </c>
-      <c r="I138" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B138:H138),B138:H138,0)),"")</f>
-        <v>1 year</v>
+      <c r="I138" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -5417,7 +5205,7 @@
       <c r="C139" s="16">
         <v>0.0508</v>
       </c>
-      <c r="D139" s="16">
+      <c r="D139" s="17">
         <v>0.0489</v>
       </c>
       <c r="E139" s="16">
@@ -5432,9 +5220,8 @@
       <c r="H139" s="16">
         <v>0.0562</v>
       </c>
-      <c r="I139" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B139:H139),B139:H139,0)),"")</f>
-        <v>1 year</v>
+      <c r="I139" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -5447,7 +5234,7 @@
       <c r="C140" s="16">
         <v>0.0508</v>
       </c>
-      <c r="D140" s="16">
+      <c r="D140" s="17">
         <v>0.0491</v>
       </c>
       <c r="E140" s="16">
@@ -5462,9 +5249,8 @@
       <c r="H140" s="16">
         <v>0.0562</v>
       </c>
-      <c r="I140" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B140:H140),B140:H140,0)),"")</f>
-        <v>1 year</v>
+      <c r="I140" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -5477,7 +5263,7 @@
       <c r="C141" s="16">
         <v>0.0508</v>
       </c>
-      <c r="D141" s="16">
+      <c r="D141" s="17">
         <v>0.0492</v>
       </c>
       <c r="E141" s="16">
@@ -5492,9 +5278,8 @@
       <c r="H141" s="16">
         <v>0.0562</v>
       </c>
-      <c r="I141" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B141:H141),B141:H141,0)),"")</f>
-        <v>1 year</v>
+      <c r="I141" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -5507,7 +5292,7 @@
       <c r="C142" s="16">
         <v>0.0508</v>
       </c>
-      <c r="D142" s="16">
+      <c r="D142" s="17">
         <v>0.049</v>
       </c>
       <c r="E142" s="16">
@@ -5522,9 +5307,8 @@
       <c r="H142" s="16">
         <v>0.0562</v>
       </c>
-      <c r="I142" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B142:H142),B142:H142,0)),"")</f>
-        <v>1 year</v>
+      <c r="I142" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -5537,7 +5321,7 @@
       <c r="C143" s="16">
         <v>0.0512</v>
       </c>
-      <c r="D143" s="16">
+      <c r="D143" s="17">
         <v>0.0493</v>
       </c>
       <c r="E143" s="16">
@@ -5552,9 +5336,8 @@
       <c r="H143" s="16">
         <v>0.0561</v>
       </c>
-      <c r="I143" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B143:H143),B143:H143,0)),"")</f>
-        <v>1 year</v>
+      <c r="I143" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -5567,7 +5350,7 @@
       <c r="C144" s="16">
         <v>0.0513</v>
       </c>
-      <c r="D144" s="16">
+      <c r="D144" s="17">
         <v>0.04940000000000001</v>
       </c>
       <c r="E144" s="16">
@@ -5582,9 +5365,8 @@
       <c r="H144" s="16">
         <v>0.0574</v>
       </c>
-      <c r="I144" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B144:H144),B144:H144,0)),"")</f>
-        <v>1 year</v>
+      <c r="I144" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -5597,7 +5379,7 @@
       <c r="C145" s="16">
         <v>0.05139999999999999</v>
       </c>
-      <c r="D145" s="16">
+      <c r="D145" s="17">
         <v>0.04940000000000001</v>
       </c>
       <c r="E145" s="16">
@@ -5612,9 +5394,8 @@
       <c r="H145" s="16">
         <v>0.059</v>
       </c>
-      <c r="I145" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B145:H145),B145:H145,0)),"")</f>
-        <v>1 year</v>
+      <c r="I145" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -5627,7 +5408,7 @@
       <c r="C146" s="16">
         <v>0.0508</v>
       </c>
-      <c r="D146" s="16">
+      <c r="D146" s="17">
         <v>0.0483</v>
       </c>
       <c r="E146" s="16">
@@ -5642,9 +5423,8 @@
       <c r="H146" s="16">
         <v>0.0587</v>
       </c>
-      <c r="I146" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B146:H146),B146:H146,0)),"")</f>
-        <v>1 year</v>
+      <c r="I146" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -5657,7 +5437,7 @@
       <c r="C147" s="16">
         <v>0.0508</v>
       </c>
-      <c r="D147" s="16">
+      <c r="D147" s="17">
         <v>0.0484</v>
       </c>
       <c r="E147" s="16">
@@ -5672,9 +5452,8 @@
       <c r="H147" s="16">
         <v>0.0579</v>
       </c>
-      <c r="I147" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B147:H147),B147:H147,0)),"")</f>
-        <v>1 year</v>
+      <c r="I147" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -5687,7 +5466,7 @@
       <c r="C148" s="16">
         <v>0.05110000000000001</v>
       </c>
-      <c r="D148" s="16">
+      <c r="D148" s="17">
         <v>0.0488</v>
       </c>
       <c r="E148" s="16">
@@ -5702,9 +5481,8 @@
       <c r="H148" s="16">
         <v>0.0593</v>
       </c>
-      <c r="I148" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B148:H148),B148:H148,0)),"")</f>
-        <v>1 year</v>
+      <c r="I148" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -5717,7 +5495,7 @@
       <c r="C149" s="16">
         <v>0.05110000000000001</v>
       </c>
-      <c r="D149" s="16">
+      <c r="D149" s="17">
         <v>0.0487</v>
       </c>
       <c r="E149" s="16">
@@ -5732,9 +5510,8 @@
       <c r="H149" s="16">
         <v>0.0593</v>
       </c>
-      <c r="I149" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B149:H149),B149:H149,0)),"")</f>
-        <v>1 year</v>
+      <c r="I149" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -5747,7 +5524,7 @@
       <c r="C150" s="16">
         <v>0.05110000000000001</v>
       </c>
-      <c r="D150" s="16">
+      <c r="D150" s="17">
         <v>0.0487</v>
       </c>
       <c r="E150" s="16">
@@ -5762,9 +5539,8 @@
       <c r="H150" s="16">
         <v>0.0597</v>
       </c>
-      <c r="I150" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B150:H150),B150:H150,0)),"")</f>
-        <v>1 year</v>
+      <c r="I150" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -5777,7 +5553,7 @@
       <c r="C151" s="16">
         <v>0.05110000000000001</v>
       </c>
-      <c r="D151" s="16">
+      <c r="D151" s="17">
         <v>0.0487</v>
       </c>
       <c r="E151" s="16">
@@ -5792,9 +5568,8 @@
       <c r="H151" s="16">
         <v>0.0597</v>
       </c>
-      <c r="I151" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B151:H151),B151:H151,0)),"")</f>
-        <v>1 year</v>
+      <c r="I151" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -5807,7 +5582,7 @@
       <c r="C152" s="16">
         <v>0.05110000000000001</v>
       </c>
-      <c r="D152" s="16">
+      <c r="D152" s="17">
         <v>0.049</v>
       </c>
       <c r="E152" s="16">
@@ -5822,9 +5597,8 @@
       <c r="H152" s="16">
         <v>0.05980000000000001</v>
       </c>
-      <c r="I152" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B152:H152),B152:H152,0)),"")</f>
-        <v>1 year</v>
+      <c r="I152" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -5837,7 +5611,7 @@
       <c r="C153" s="16">
         <v>0.051</v>
       </c>
-      <c r="D153" s="16">
+      <c r="D153" s="17">
         <v>0.0489</v>
       </c>
       <c r="E153" s="16">
@@ -5852,9 +5626,8 @@
       <c r="H153" s="16">
         <v>0.0595</v>
       </c>
-      <c r="I153" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B153:H153),B153:H153,0)),"")</f>
-        <v>1 year</v>
+      <c r="I153" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -5867,7 +5640,7 @@
       <c r="C154" s="16">
         <v>0.051</v>
       </c>
-      <c r="D154" s="16">
+      <c r="D154" s="17">
         <v>0.049</v>
       </c>
       <c r="E154" s="16">
@@ -5882,9 +5655,8 @@
       <c r="H154" s="16">
         <v>0.0595</v>
       </c>
-      <c r="I154" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B154:H154),B154:H154,0)),"")</f>
-        <v>1 year</v>
+      <c r="I154" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -5897,7 +5669,7 @@
       <c r="C155" s="16">
         <v>0.051</v>
       </c>
-      <c r="D155" s="16">
+      <c r="D155" s="17">
         <v>0.049</v>
       </c>
       <c r="E155" s="16">
@@ -5912,9 +5684,8 @@
       <c r="H155" s="16">
         <v>0.0592</v>
       </c>
-      <c r="I155" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B155:H155),B155:H155,0)),"")</f>
-        <v>1 year</v>
+      <c r="I155" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -5927,7 +5698,7 @@
       <c r="C156" s="16">
         <v>0.051</v>
       </c>
-      <c r="D156" s="16">
+      <c r="D156" s="17">
         <v>0.0489</v>
       </c>
       <c r="E156" s="16">
@@ -5942,9 +5713,8 @@
       <c r="H156" s="16">
         <v>0.0592</v>
       </c>
-      <c r="I156" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B156:H156),B156:H156,0)),"")</f>
-        <v>1 year</v>
+      <c r="I156" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -5957,7 +5727,7 @@
       <c r="C157" s="16">
         <v>0.051</v>
       </c>
-      <c r="D157" s="16">
+      <c r="D157" s="17">
         <v>0.0488</v>
       </c>
       <c r="E157" s="16">
@@ -5972,9 +5742,8 @@
       <c r="H157" s="16">
         <v>0.0591</v>
       </c>
-      <c r="I157" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B157:H157),B157:H157,0)),"")</f>
-        <v>1 year</v>
+      <c r="I157" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -5987,7 +5756,7 @@
       <c r="C158" s="16">
         <v>0.051</v>
       </c>
-      <c r="D158" s="16">
+      <c r="D158" s="17">
         <v>0.0488</v>
       </c>
       <c r="E158" s="16">
@@ -6002,9 +5771,8 @@
       <c r="H158" s="16">
         <v>0.0591</v>
       </c>
-      <c r="I158" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B158:H158),B158:H158,0)),"")</f>
-        <v>1 year</v>
+      <c r="I158" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -6017,7 +5785,7 @@
       <c r="C159" s="16">
         <v>0.051</v>
       </c>
-      <c r="D159" s="16">
+      <c r="D159" s="17">
         <v>0.0486</v>
       </c>
       <c r="E159" s="16">
@@ -6032,9 +5800,8 @@
       <c r="H159" s="16">
         <v>0.0591</v>
       </c>
-      <c r="I159" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B159:H159),B159:H159,0)),"")</f>
-        <v>1 year</v>
+      <c r="I159" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -6047,7 +5814,7 @@
       <c r="C160" s="16">
         <v>0.0513</v>
       </c>
-      <c r="D160" s="16">
+      <c r="D160" s="17">
         <v>0.0487</v>
       </c>
       <c r="E160" s="16">
@@ -6062,9 +5829,8 @@
       <c r="H160" s="16">
         <v>0.0593</v>
       </c>
-      <c r="I160" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B160:H160),B160:H160,0)),"")</f>
-        <v>1 year</v>
+      <c r="I160" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -6077,7 +5843,7 @@
       <c r="C161" s="16">
         <v>0.0513</v>
       </c>
-      <c r="D161" s="16">
+      <c r="D161" s="17">
         <v>0.0486</v>
       </c>
       <c r="E161" s="16">
@@ -6092,9 +5858,8 @@
       <c r="H161" s="16">
         <v>0.059</v>
       </c>
-      <c r="I161" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B161:H161),B161:H161,0)),"")</f>
-        <v>1 year</v>
+      <c r="I161" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -6107,7 +5872,7 @@
       <c r="C162" s="16">
         <v>0.0513</v>
       </c>
-      <c r="D162" s="16">
+      <c r="D162" s="17">
         <v>0.0484</v>
       </c>
       <c r="E162" s="16">
@@ -6122,9 +5887,8 @@
       <c r="H162" s="16">
         <v>0.059</v>
       </c>
-      <c r="I162" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B162:H162),B162:H162,0)),"")</f>
-        <v>1 year</v>
+      <c r="I162" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -6137,7 +5901,7 @@
       <c r="C163" s="16">
         <v>0.05139999999999999</v>
       </c>
-      <c r="D163" s="16">
+      <c r="D163" s="17">
         <v>0.0486</v>
       </c>
       <c r="E163" s="16">
@@ -6152,9 +5916,8 @@
       <c r="H163" s="16">
         <v>0.05889999999999999</v>
       </c>
-      <c r="I163" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B163:H163),B163:H163,0)),"")</f>
-        <v>1 year</v>
+      <c r="I163" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -6167,7 +5930,7 @@
       <c r="C164" s="16">
         <v>0.05139999999999999</v>
       </c>
-      <c r="D164" s="16">
+      <c r="D164" s="17">
         <v>0.0483</v>
       </c>
       <c r="E164" s="16">
@@ -6182,9 +5945,8 @@
       <c r="H164" s="16">
         <v>0.05860000000000001</v>
       </c>
-      <c r="I164" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B164:H164),B164:H164,0)),"")</f>
-        <v>1 year</v>
+      <c r="I164" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -6197,7 +5959,7 @@
       <c r="C165" s="16">
         <v>0.05139999999999999</v>
       </c>
-      <c r="D165" s="16">
+      <c r="D165" s="17">
         <v>0.0481</v>
       </c>
       <c r="E165" s="16">
@@ -6212,9 +5974,8 @@
       <c r="H165" s="16">
         <v>0.058</v>
       </c>
-      <c r="I165" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B165:H165),B165:H165,0)),"")</f>
-        <v>1 year</v>
+      <c r="I165" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -6227,7 +5988,7 @@
       <c r="C166" s="16">
         <v>0.0509</v>
       </c>
-      <c r="D166" s="16">
+      <c r="D166" s="17">
         <v>0.0478</v>
       </c>
       <c r="E166" s="16">
@@ -6242,9 +6003,8 @@
       <c r="H166" s="16">
         <v>0.0556</v>
       </c>
-      <c r="I166" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B166:H166),B166:H166,0)),"")</f>
-        <v>1 year</v>
+      <c r="I166" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -6257,7 +6017,7 @@
       <c r="C167" s="16">
         <v>0.0507</v>
       </c>
-      <c r="D167" s="16">
+      <c r="D167" s="17">
         <v>0.04769999999999999</v>
       </c>
       <c r="E167" s="16">
@@ -6272,9 +6032,8 @@
       <c r="H167" s="16">
         <v>0.0551</v>
       </c>
-      <c r="I167" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B167:H167),B167:H167,0)),"")</f>
-        <v>1 year</v>
+      <c r="I167" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -6287,7 +6046,7 @@
       <c r="C168" s="16">
         <v>0.0504</v>
       </c>
-      <c r="D168" s="16">
+      <c r="D168" s="17">
         <v>0.0472</v>
       </c>
       <c r="E168" s="16">
@@ -6302,9 +6061,8 @@
       <c r="H168" s="16">
         <v>0.0551</v>
       </c>
-      <c r="I168" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B168:H168),B168:H168,0)),"")</f>
-        <v>1 year</v>
+      <c r="I168" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -6317,7 +6075,7 @@
       <c r="C169" s="16">
         <v>0.051</v>
       </c>
-      <c r="D169" s="16">
+      <c r="D169" s="17">
         <v>0.0475</v>
       </c>
       <c r="E169" s="16">
@@ -6332,9 +6090,8 @@
       <c r="H169" s="16">
         <v>0.0558</v>
       </c>
-      <c r="I169" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B169:H169),B169:H169,0)),"")</f>
-        <v>1 year</v>
+      <c r="I169" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -6347,7 +6104,7 @@
       <c r="C170" s="16">
         <v>0.051</v>
       </c>
-      <c r="D170" s="16">
+      <c r="D170" s="17">
         <v>0.0475</v>
       </c>
       <c r="E170" s="16">
@@ -6362,9 +6119,8 @@
       <c r="H170" s="16">
         <v>0.0558</v>
       </c>
-      <c r="I170" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B170:H170),B170:H170,0)),"")</f>
-        <v>1 year</v>
+      <c r="I170" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -6377,7 +6133,7 @@
       <c r="C171" s="16">
         <v>0.0509</v>
       </c>
-      <c r="D171" s="16">
+      <c r="D171" s="17">
         <v>0.0474</v>
       </c>
       <c r="E171" s="16">
@@ -6392,9 +6148,8 @@
       <c r="H171" s="16">
         <v>0.0556</v>
       </c>
-      <c r="I171" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B171:H171),B171:H171,0)),"")</f>
-        <v>1 year</v>
+      <c r="I171" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -6407,7 +6162,7 @@
       <c r="C172" s="16">
         <v>0.0508</v>
       </c>
-      <c r="D172" s="16">
+      <c r="D172" s="17">
         <v>0.047</v>
       </c>
       <c r="E172" s="16">
@@ -6422,9 +6177,8 @@
       <c r="H172" s="16">
         <v>0.0544</v>
       </c>
-      <c r="I172" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B172:H172),B172:H172,0)),"")</f>
-        <v>1 year</v>
+      <c r="I172" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -6437,7 +6191,7 @@
       <c r="C173" s="16">
         <v>0.0508</v>
       </c>
-      <c r="D173" s="16">
+      <c r="D173" s="17">
         <v>0.047</v>
       </c>
       <c r="E173" s="16">
@@ -6452,9 +6206,8 @@
       <c r="H173" s="16">
         <v>0.0518</v>
       </c>
-      <c r="I173" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B173:H173),B173:H173,0)),"")</f>
-        <v>1 year</v>
+      <c r="I173" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -6467,7 +6220,7 @@
       <c r="C174" s="16">
         <v>0.0508</v>
       </c>
-      <c r="D174" s="16">
+      <c r="D174" s="17">
         <v>0.0464</v>
       </c>
       <c r="E174" s="16">
@@ -6482,9 +6235,8 @@
       <c r="H174" s="16">
         <v>0.0504</v>
       </c>
-      <c r="I174" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B174:H174),B174:H174,0)),"")</f>
-        <v>1 year</v>
+      <c r="I174" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -6497,7 +6249,7 @@
       <c r="C175" s="16">
         <v>0.05019999999999999</v>
       </c>
-      <c r="D175" s="16">
+      <c r="D175" s="17">
         <v>0.0461</v>
       </c>
       <c r="E175" s="16">
@@ -6512,9 +6264,8 @@
       <c r="H175" s="16">
         <v>0.0504</v>
       </c>
-      <c r="I175" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B175:H175),B175:H175,0)),"")</f>
-        <v>1 year</v>
+      <c r="I175" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -6527,7 +6278,7 @@
       <c r="C176" s="16">
         <v>0.05</v>
       </c>
-      <c r="D176" s="16">
+      <c r="D176" s="17">
         <v>0.046</v>
       </c>
       <c r="E176" s="16">
@@ -6542,9 +6293,8 @@
       <c r="H176" s="16">
         <v>0.0504</v>
       </c>
-      <c r="I176" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B176:H176),B176:H176,0)),"")</f>
-        <v>1 year</v>
+      <c r="I176" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -6557,7 +6307,7 @@
       <c r="C177" s="16">
         <v>0.049</v>
       </c>
-      <c r="D177" s="16">
+      <c r="D177" s="17">
         <v>0.0451</v>
       </c>
       <c r="E177" s="16">
@@ -6572,9 +6322,8 @@
       <c r="H177" s="16">
         <v>0.0503</v>
       </c>
-      <c r="I177" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B177:H177),B177:H177,0)),"")</f>
-        <v>1 year</v>
+      <c r="I177" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -6587,7 +6336,7 @@
       <c r="C178" s="16">
         <v>0.0486</v>
       </c>
-      <c r="D178" s="16">
+      <c r="D178" s="17">
         <v>0.0443</v>
       </c>
       <c r="E178" s="16">
@@ -6602,9 +6351,8 @@
       <c r="H178" s="16">
         <v>0.0495</v>
       </c>
-      <c r="I178" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B178:H178),B178:H178,0)),"")</f>
-        <v>1 year</v>
+      <c r="I178" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -6617,7 +6365,7 @@
       <c r="C179" s="16">
         <v>0.0472</v>
       </c>
-      <c r="D179" s="16">
+      <c r="D179" s="17">
         <v>0.0435</v>
       </c>
       <c r="E179" s="16">
@@ -6632,9 +6380,8 @@
       <c r="H179" s="16">
         <v>0.0486</v>
       </c>
-      <c r="I179" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B179:H179),B179:H179,0)),"")</f>
-        <v>1 year</v>
+      <c r="I179" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -6647,7 +6394,7 @@
       <c r="C180" s="16">
         <v>0.0466</v>
       </c>
-      <c r="D180" s="16">
+      <c r="D180" s="17">
         <v>0.0433</v>
       </c>
       <c r="E180" s="16">
@@ -6662,9 +6409,8 @@
       <c r="H180" s="16">
         <v>0.049</v>
       </c>
-      <c r="I180" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B180:H180),B180:H180,0)),"")</f>
-        <v>1 year</v>
+      <c r="I180" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -6677,7 +6423,7 @@
       <c r="C181" s="16">
         <v>0.0466</v>
       </c>
-      <c r="D181" s="16">
+      <c r="D181" s="17">
         <v>0.0432</v>
       </c>
       <c r="E181" s="16">
@@ -6692,9 +6438,8 @@
       <c r="H181" s="16">
         <v>0.0491</v>
       </c>
-      <c r="I181" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B181:H181),B181:H181,0)),"")</f>
-        <v>1 year</v>
+      <c r="I181" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -6707,7 +6452,7 @@
       <c r="C182" s="16">
         <v>0.0466</v>
       </c>
-      <c r="D182" s="16">
+      <c r="D182" s="17">
         <v>0.0432</v>
       </c>
       <c r="E182" s="16">
@@ -6722,9 +6467,8 @@
       <c r="H182" s="16">
         <v>0.0491</v>
       </c>
-      <c r="I182" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B182:H182),B182:H182,0)),"")</f>
-        <v>1 year</v>
+      <c r="I182" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -6737,7 +6481,7 @@
       <c r="C183" s="16">
         <v>0.0466</v>
       </c>
-      <c r="D183" s="16">
+      <c r="D183" s="17">
         <v>0.0432</v>
       </c>
       <c r="E183" s="16">
@@ -6752,9 +6496,8 @@
       <c r="H183" s="16">
         <v>0.0491</v>
       </c>
-      <c r="I183" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B183:H183),B183:H183,0)),"")</f>
-        <v>1 year</v>
+      <c r="I183" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -6767,7 +6510,7 @@
       <c r="C184" s="16">
         <v>0.046</v>
       </c>
-      <c r="D184" s="16">
+      <c r="D184" s="17">
         <v>0.04</v>
       </c>
       <c r="E184" s="16">
@@ -6782,9 +6525,8 @@
       <c r="H184" s="16">
         <v>0.0475</v>
       </c>
-      <c r="I184" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B184:H184),B184:H184,0)),"")</f>
-        <v>1 year</v>
+      <c r="I184" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -6797,7 +6539,7 @@
       <c r="C185" s="16">
         <v>0.0452</v>
       </c>
-      <c r="D185" s="16">
+      <c r="D185" s="17">
         <v>0.0397</v>
       </c>
       <c r="E185" s="16">
@@ -6812,9 +6554,8 @@
       <c r="H185" s="16">
         <v>0.0475</v>
       </c>
-      <c r="I185" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B185:H185),B185:H185,0)),"")</f>
-        <v>1 year</v>
+      <c r="I185" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -6827,7 +6568,7 @@
       <c r="C186" s="16">
         <v>0.0435</v>
       </c>
-      <c r="D186" s="16">
+      <c r="D186" s="17">
         <v>0.0381</v>
       </c>
       <c r="E186" s="16">
@@ -6842,9 +6583,8 @@
       <c r="H186" s="16">
         <v>0.04480000000000001</v>
       </c>
-      <c r="I186" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B186:H186),B186:H186,0)),"")</f>
-        <v>1 year</v>
+      <c r="I186" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -6857,7 +6597,7 @@
       <c r="C187" s="16">
         <v>0.0414</v>
       </c>
-      <c r="D187" s="16">
+      <c r="D187" s="17">
         <v>0.0365</v>
       </c>
       <c r="E187" s="16">
@@ -6872,9 +6612,8 @@
       <c r="H187" s="16">
         <v>0.0412</v>
       </c>
-      <c r="I187" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B187:H187),B187:H187,0)),"")</f>
-        <v>1 year</v>
+      <c r="I187" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -6887,7 +6626,7 @@
       <c r="C188" s="16">
         <v>0.0404</v>
       </c>
-      <c r="D188" s="16">
+      <c r="D188" s="17">
         <v>0.0355</v>
       </c>
       <c r="E188" s="16">
@@ -6902,9 +6641,8 @@
       <c r="H188" s="16">
         <v>0.0398</v>
       </c>
-      <c r="I188" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B188:H188),B188:H188,0)),"")</f>
-        <v>1 year</v>
+      <c r="I188" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -6917,7 +6655,7 @@
       <c r="C189" s="16">
         <v>0.0401</v>
       </c>
-      <c r="D189" s="16">
+      <c r="D189" s="17">
         <v>0.0353</v>
       </c>
       <c r="E189" s="16">
@@ -6932,9 +6670,8 @@
       <c r="H189" s="16">
         <v>0.0397</v>
       </c>
-      <c r="I189" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B189:H189),B189:H189,0)),"")</f>
-        <v>1 year</v>
+      <c r="I189" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -6947,7 +6684,7 @@
       <c r="C190" s="16">
         <v>0.0397</v>
       </c>
-      <c r="D190" s="16">
+      <c r="D190" s="17">
         <v>0.0346</v>
       </c>
       <c r="E190" s="16">
@@ -6962,9 +6699,8 @@
       <c r="H190" s="16">
         <v>0.0385</v>
       </c>
-      <c r="I190" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B190:H190),B190:H190,0)),"")</f>
-        <v>1 year</v>
+      <c r="I190" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -6977,7 +6713,7 @@
       <c r="C191" s="16">
         <v>0.0392</v>
       </c>
-      <c r="D191" s="16">
+      <c r="D191" s="17">
         <v>0.0336</v>
       </c>
       <c r="E191" s="16">
@@ -6992,9 +6728,8 @@
       <c r="H191" s="16">
         <v>0.0378</v>
       </c>
-      <c r="I191" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B191:H191),B191:H191,0)),"")</f>
-        <v>1 year</v>
+      <c r="I191" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -7007,13 +6742,13 @@
       <c r="C192" s="16">
         <v>0.039</v>
       </c>
-      <c r="D192" s="16">
+      <c r="D192" s="17">
         <v>0.0334</v>
       </c>
       <c r="E192" s="16">
         <v>0.0351</v>
       </c>
-      <c r="F192" s="16">
+      <c r="F192" s="17">
         <v>0.0334</v>
       </c>
       <c r="G192" s="16">
@@ -7022,9 +6757,8 @@
       <c r="H192" s="16">
         <v>0.0378</v>
       </c>
-      <c r="I192" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B192:H192),B192:H192,0)),"")</f>
-        <v>1 year</v>
+      <c r="I192" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -7037,13 +6771,13 @@
       <c r="C193" s="16">
         <v>0.039</v>
       </c>
-      <c r="D193" s="16">
+      <c r="D193" s="17">
         <v>0.0334</v>
       </c>
       <c r="E193" s="16">
         <v>0.0351</v>
       </c>
-      <c r="F193" s="16">
+      <c r="F193" s="17">
         <v>0.0334</v>
       </c>
       <c r="G193" s="16">
@@ -7052,9 +6786,8 @@
       <c r="H193" s="16">
         <v>0.0378</v>
       </c>
-      <c r="I193" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B193:H193),B193:H193,0)),"")</f>
-        <v>1 year</v>
+      <c r="I193" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -7067,7 +6800,7 @@
       <c r="C194" s="16">
         <v>0.0388</v>
       </c>
-      <c r="D194" s="16">
+      <c r="D194" s="17">
         <v>0.0326</v>
       </c>
       <c r="E194" s="16">
@@ -7082,9 +6815,8 @@
       <c r="H194" s="16">
         <v>0.0378</v>
       </c>
-      <c r="I194" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B194:H194),B194:H194,0)),"")</f>
-        <v>1 year</v>
+      <c r="I194" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -7097,7 +6829,7 @@
       <c r="C195" s="16">
         <v>0.0388</v>
       </c>
-      <c r="D195" s="16">
+      <c r="D195" s="17">
         <v>0.03240000000000001</v>
       </c>
       <c r="E195" s="16">
@@ -7112,9 +6844,8 @@
       <c r="H195" s="16">
         <v>0.0377</v>
       </c>
-      <c r="I195" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B195:H195),B195:H195,0)),"")</f>
-        <v>1 year</v>
+      <c r="I195" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -7127,7 +6858,7 @@
       <c r="C196" s="16">
         <v>0.0388</v>
       </c>
-      <c r="D196" s="16">
+      <c r="D196" s="17">
         <v>0.03240000000000001</v>
       </c>
       <c r="E196" s="16">
@@ -7142,9 +6873,8 @@
       <c r="H196" s="16">
         <v>0.0378</v>
       </c>
-      <c r="I196" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B196:H196),B196:H196,0)),"")</f>
-        <v>1 year</v>
+      <c r="I196" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -7157,7 +6887,7 @@
       <c r="C197" s="16">
         <v>0.0386</v>
       </c>
-      <c r="D197" s="16">
+      <c r="D197" s="17">
         <v>0.0323</v>
       </c>
       <c r="E197" s="16">
@@ -7172,9 +6902,8 @@
       <c r="H197" s="16">
         <v>0.0389</v>
       </c>
-      <c r="I197" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B197:H197),B197:H197,0)),"")</f>
-        <v>1 year</v>
+      <c r="I197" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -7187,7 +6916,7 @@
       <c r="C198" s="16">
         <v>0.0385</v>
       </c>
-      <c r="D198" s="16">
+      <c r="D198" s="17">
         <v>0.032</v>
       </c>
       <c r="E198" s="16">
@@ -7202,9 +6931,8 @@
       <c r="H198" s="16">
         <v>0.04019999999999999</v>
       </c>
-      <c r="I198" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B198:H198),B198:H198,0)),"")</f>
-        <v>1 year</v>
+      <c r="I198" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -7217,7 +6945,7 @@
       <c r="C199" s="16">
         <v>0.0374</v>
       </c>
-      <c r="D199" s="16">
+      <c r="D199" s="17">
         <v>0.0317</v>
       </c>
       <c r="E199" s="16">
@@ -7232,9 +6960,8 @@
       <c r="H199" s="16">
         <v>0.04219999999999999</v>
       </c>
-      <c r="I199" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B199:H199),B199:H199,0)),"")</f>
-        <v>1 year</v>
+      <c r="I199" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -7247,7 +6974,7 @@
       <c r="C200" s="16">
         <v>0.0382</v>
       </c>
-      <c r="D200" s="16">
+      <c r="D200" s="17">
         <v>0.0339</v>
       </c>
       <c r="E200" s="16">
@@ -7262,9 +6989,8 @@
       <c r="H200" s="16">
         <v>0.0442</v>
       </c>
-      <c r="I200" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B200:H200),B200:H200,0)),"")</f>
-        <v>1 year</v>
+      <c r="I200" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -7277,7 +7003,7 @@
       <c r="C201" s="16">
         <v>0.0383</v>
       </c>
-      <c r="D201" s="16">
+      <c r="D201" s="17">
         <v>0.0337</v>
       </c>
       <c r="E201" s="16">
@@ -7292,9 +7018,8 @@
       <c r="H201" s="16">
         <v>0.0444</v>
       </c>
-      <c r="I201" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B201:H201),B201:H201,0)),"")</f>
-        <v>1 year</v>
+      <c r="I201" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -7307,7 +7032,7 @@
       <c r="C202" s="16">
         <v>0.039</v>
       </c>
-      <c r="D202" s="16">
+      <c r="D202" s="17">
         <v>0.0354</v>
       </c>
       <c r="E202" s="16">
@@ -7322,9 +7047,8 @@
       <c r="H202" s="16">
         <v>0.04650000000000001</v>
       </c>
-      <c r="I202" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B202:H202),B202:H202,0)),"")</f>
-        <v>1 year</v>
+      <c r="I202" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -7337,7 +7061,7 @@
       <c r="C203" s="16">
         <v>0.0417</v>
       </c>
-      <c r="D203" s="16">
+      <c r="D203" s="17">
         <v>0.0382</v>
       </c>
       <c r="E203" s="16">
@@ -7352,9 +7076,8 @@
       <c r="H203" s="16">
         <v>0.0496</v>
       </c>
-      <c r="I203" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B203:H203),B203:H203,0)),"")</f>
-        <v>1 year</v>
+      <c r="I203" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -7367,7 +7090,7 @@
       <c r="C204" s="16">
         <v>0.0445</v>
       </c>
-      <c r="D204" s="16">
+      <c r="D204" s="17">
         <v>0.0412</v>
       </c>
       <c r="E204" s="16">
@@ -7382,9 +7105,8 @@
       <c r="H204" s="16">
         <v>0.0536</v>
       </c>
-      <c r="I204" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B204:H204),B204:H204,0)),"")</f>
-        <v>1 year</v>
+      <c r="I204" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -7397,7 +7119,7 @@
       <c r="C205" s="16">
         <v>0.04480000000000001</v>
       </c>
-      <c r="D205" s="16">
+      <c r="D205" s="17">
         <v>0.042</v>
       </c>
       <c r="E205" s="16">
@@ -7412,9 +7134,8 @@
       <c r="H205" s="16">
         <v>0.0542</v>
       </c>
-      <c r="I205" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B205:H205),B205:H205,0)),"")</f>
-        <v>1 year</v>
+      <c r="I205" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -7427,7 +7148,7 @@
       <c r="C206" s="16">
         <v>0.0446</v>
       </c>
-      <c r="D206" s="16">
+      <c r="D206" s="17">
         <v>0.0418</v>
       </c>
       <c r="E206" s="16">
@@ -7442,9 +7163,8 @@
       <c r="H206" s="16">
         <v>0.0542</v>
       </c>
-      <c r="I206" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B206:H206),B206:H206,0)),"")</f>
-        <v>1 year</v>
+      <c r="I206" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -7457,7 +7177,7 @@
       <c r="C207" s="16">
         <v>0.045</v>
       </c>
-      <c r="D207" s="16">
+      <c r="D207" s="17">
         <v>0.0426</v>
       </c>
       <c r="E207" s="16">
@@ -7472,9 +7192,8 @@
       <c r="H207" s="16">
         <v>0.0547</v>
       </c>
-      <c r="I207" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B207:H207),B207:H207,0)),"")</f>
-        <v>1 year</v>
+      <c r="I207" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -7487,7 +7206,7 @@
       <c r="C208" s="16">
         <v>0.047</v>
       </c>
-      <c r="D208" s="16">
+      <c r="D208" s="17">
         <v>0.0449</v>
       </c>
       <c r="E208" s="16">
@@ -7502,9 +7221,8 @@
       <c r="H208" s="16">
         <v>0.05690000000000001</v>
       </c>
-      <c r="I208" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B208:H208),B208:H208,0)),"")</f>
-        <v>1 year</v>
+      <c r="I208" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="209" spans="1:9">
@@ -7517,7 +7235,7 @@
       <c r="C209" s="16">
         <v>0.04940000000000001</v>
       </c>
-      <c r="D209" s="16">
+      <c r="D209" s="17">
         <v>0.0487</v>
       </c>
       <c r="E209" s="16">
@@ -7532,9 +7250,8 @@
       <c r="H209" s="16">
         <v>0.0635</v>
       </c>
-      <c r="I209" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B209:H209),B209:H209,0)),"")</f>
-        <v>1 year</v>
+      <c r="I209" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:9">
@@ -7547,7 +7264,7 @@
       <c r="C210" s="16">
         <v>0.0504</v>
       </c>
-      <c r="D210" s="16">
+      <c r="D210" s="17">
         <v>0.0496</v>
       </c>
       <c r="E210" s="16">
@@ -7562,9 +7279,8 @@
       <c r="H210" s="16">
         <v>0.06419999999999999</v>
       </c>
-      <c r="I210" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B210:H210),B210:H210,0)),"")</f>
-        <v>1 year</v>
+      <c r="I210" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:9">
@@ -7574,7 +7290,7 @@
       <c r="B211" s="16">
         <v>0.05889999999999999</v>
       </c>
-      <c r="C211" s="16">
+      <c r="C211" s="17">
         <v>0.0552</v>
       </c>
       <c r="D211" s="16">
@@ -7592,9 +7308,8 @@
       <c r="H211" s="16">
         <v>0.0677</v>
       </c>
-      <c r="I211" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B211:H211),B211:H211,0)),"")</f>
-        <v>6 months</v>
+      <c r="I211" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:9">
@@ -7604,10 +7319,10 @@
       <c r="B212" s="16">
         <v>0.0622</v>
       </c>
-      <c r="C212" s="16">
+      <c r="C212" s="17">
         <v>0.0565</v>
       </c>
-      <c r="D212" s="16">
+      <c r="D212" s="17">
         <v>0.0565</v>
       </c>
       <c r="E212" s="16">
@@ -7622,9 +7337,8 @@
       <c r="H212" s="16">
         <v>0.06759999999999999</v>
       </c>
-      <c r="I212" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B212:H212),B212:H212,0)),"")</f>
-        <v>6 months</v>
+      <c r="I212" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:9">
@@ -7637,7 +7351,7 @@
       <c r="C213" s="16">
         <v>0.0556</v>
       </c>
-      <c r="D213" s="16">
+      <c r="D213" s="17">
         <v>0.0548</v>
       </c>
       <c r="E213" s="16">
@@ -7652,9 +7366,8 @@
       <c r="H213" s="16">
         <v>0.0644</v>
       </c>
-      <c r="I213" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B213:H213),B213:H213,0)),"")</f>
-        <v>1 year</v>
+      <c r="I213" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:9">
@@ -7664,7 +7377,7 @@
       <c r="B214" s="16">
         <v>0.0665</v>
       </c>
-      <c r="C214" s="16">
+      <c r="C214" s="17">
         <v>0.0571</v>
       </c>
       <c r="D214" s="16">
@@ -7682,9 +7395,8 @@
       <c r="H214" s="16">
         <v>0.0644</v>
       </c>
-      <c r="I214" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B214:H214),B214:H214,0)),"")</f>
-        <v>6 months</v>
+      <c r="I214" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:9">
@@ -7694,7 +7406,7 @@
       <c r="B215" s="16">
         <v>0.0699</v>
       </c>
-      <c r="C215" s="16">
+      <c r="C215" s="17">
         <v>0.0616</v>
       </c>
       <c r="D215" s="16">
@@ -7712,9 +7424,8 @@
       <c r="H215" s="16">
         <v>0.06900000000000001</v>
       </c>
-      <c r="I215" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B215:H215),B215:H215,0)),"")</f>
-        <v>6 months</v>
+      <c r="I215" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:9">
@@ -7724,7 +7435,7 @@
       <c r="B216" s="16">
         <v>0.0733</v>
       </c>
-      <c r="C216" s="16">
+      <c r="C216" s="17">
         <v>0.0643</v>
       </c>
       <c r="D216" s="16">
@@ -7742,9 +7453,8 @@
       <c r="H216" s="16">
         <v>0.0694</v>
       </c>
-      <c r="I216" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B216:H216),B216:H216,0)),"")</f>
-        <v>6 months</v>
+      <c r="I216" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:9">
@@ -7757,7 +7467,7 @@
       <c r="C217" s="16">
         <v>0.06849999999999999</v>
       </c>
-      <c r="D217" s="16">
+      <c r="D217" s="17">
         <v>0.0682</v>
       </c>
       <c r="E217" s="16">
@@ -7772,9 +7482,8 @@
       <c r="H217" s="16">
         <v>0.0732</v>
       </c>
-      <c r="I217" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B217:H217),B217:H217,0)),"")</f>
-        <v>1 year</v>
+      <c r="I217" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="218" spans="1:9">
@@ -7787,7 +7496,7 @@
       <c r="C218" s="16">
         <v>0.0688</v>
       </c>
-      <c r="D218" s="16">
+      <c r="D218" s="17">
         <v>0.06860000000000001</v>
       </c>
       <c r="E218" s="16">
@@ -7802,9 +7511,8 @@
       <c r="H218" s="16">
         <v>0.0725</v>
       </c>
-      <c r="I218" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B218:H218),B218:H218,0)),"")</f>
-        <v>1 year</v>
+      <c r="I218" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:9">
@@ -7817,7 +7525,7 @@
       <c r="C219" s="16">
         <v>0.0693</v>
       </c>
-      <c r="D219" s="16">
+      <c r="D219" s="17">
         <v>0.06909999999999999</v>
       </c>
       <c r="E219" s="16">
@@ -7832,9 +7540,8 @@
       <c r="H219" s="16">
         <v>0.07049999999999999</v>
       </c>
-      <c r="I219" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B219:H219),B219:H219,0)),"")</f>
-        <v>1 year</v>
+      <c r="I219" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:9">
@@ -7853,7 +7560,7 @@
       <c r="E220" s="16">
         <v>0.0703</v>
       </c>
-      <c r="F220" s="16">
+      <c r="F220" s="17">
         <v>0.0694</v>
       </c>
       <c r="G220" s="16">
@@ -7862,9 +7569,8 @@
       <c r="H220" s="16">
         <v>0.0701</v>
       </c>
-      <c r="I220" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B220:H220),B220:H220,0)),"")</f>
-        <v>3 years</v>
+      <c r="I220" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -7883,7 +7589,7 @@
       <c r="E221" s="16">
         <v>0.0707</v>
       </c>
-      <c r="F221" s="16">
+      <c r="F221" s="17">
         <v>0.0678</v>
       </c>
       <c r="G221" s="16">
@@ -7892,9 +7598,8 @@
       <c r="H221" s="16">
         <v>0.0687</v>
       </c>
-      <c r="I221" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B221:H221),B221:H221,0)),"")</f>
-        <v>3 years</v>
+      <c r="I221" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -7913,7 +7618,7 @@
       <c r="E222" s="16">
         <v>0.07099999999999999</v>
       </c>
-      <c r="F222" s="16">
+      <c r="F222" s="17">
         <v>0.0665</v>
       </c>
       <c r="G222" s="16">
@@ -7922,9 +7627,8 @@
       <c r="H222" s="16">
         <v>0.0678</v>
       </c>
-      <c r="I222" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B222:H222),B222:H222,0)),"")</f>
-        <v>3 years</v>
+      <c r="I222" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -7943,7 +7647,7 @@
       <c r="E223" s="16">
         <v>0.07150000000000001</v>
       </c>
-      <c r="F223" s="16">
+      <c r="F223" s="17">
         <v>0.067</v>
       </c>
       <c r="G223" s="16">
@@ -7952,9 +7656,8 @@
       <c r="H223" s="16">
         <v>0.0678</v>
       </c>
-      <c r="I223" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B223:H223),B223:H223,0)),"")</f>
-        <v>3 years</v>
+      <c r="I223" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:9">
@@ -7979,12 +7682,11 @@
       <c r="G224" s="16">
         <v>0.06849999999999999</v>
       </c>
-      <c r="H224" s="16">
+      <c r="H224" s="17">
         <v>0.0679</v>
       </c>
-      <c r="I224" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B224:H224),B224:H224,0)),"")</f>
-        <v>5 years</v>
+      <c r="I224" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="225" spans="1:9">
@@ -8003,7 +7705,7 @@
       <c r="E225" s="16">
         <v>0.0742</v>
       </c>
-      <c r="F225" s="16">
+      <c r="F225" s="17">
         <v>0.0692</v>
       </c>
       <c r="G225" s="16">
@@ -8012,9 +7714,8 @@
       <c r="H225" s="16">
         <v>0.06950000000000001</v>
       </c>
-      <c r="I225" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B225:H225),B225:H225,0)),"")</f>
-        <v>3 years</v>
+      <c r="I225" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:9">
@@ -8039,12 +7740,11 @@
       <c r="G226" s="16">
         <v>0.0707</v>
       </c>
-      <c r="H226" s="16">
+      <c r="H226" s="17">
         <v>0.0702</v>
       </c>
-      <c r="I226" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B226:H226),B226:H226,0)),"")</f>
-        <v>5 years</v>
+      <c r="I226" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="227" spans="1:9">
@@ -8069,12 +7769,11 @@
       <c r="G227" s="16">
         <v>0.0722</v>
       </c>
-      <c r="H227" s="16">
+      <c r="H227" s="17">
         <v>0.07190000000000001</v>
       </c>
-      <c r="I227" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B227:H227),B227:H227,0)),"")</f>
-        <v>5 years</v>
+      <c r="I227" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="228" spans="1:9">
@@ -8099,12 +7798,11 @@
       <c r="G228" s="16">
         <v>0.0723</v>
       </c>
-      <c r="H228" s="16">
+      <c r="H228" s="17">
         <v>0.07200000000000001</v>
       </c>
-      <c r="I228" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B228:H228),B228:H228,0)),"")</f>
-        <v>5 years</v>
+      <c r="I228" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="229" spans="1:9">
@@ -8129,12 +7827,11 @@
       <c r="G229" s="16">
         <v>0.0723</v>
       </c>
-      <c r="H229" s="16">
+      <c r="H229" s="17">
         <v>0.07200000000000001</v>
       </c>
-      <c r="I229" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B229:H229),B229:H229,0)),"")</f>
-        <v>5 years</v>
+      <c r="I229" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="230" spans="1:9">
@@ -8159,12 +7856,11 @@
       <c r="G230" s="16">
         <v>0.0718</v>
       </c>
-      <c r="H230" s="16">
+      <c r="H230" s="17">
         <v>0.0713</v>
       </c>
-      <c r="I230" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B230:H230),B230:H230,0)),"")</f>
-        <v>5 years</v>
+      <c r="I230" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="231" spans="1:9">
@@ -8189,12 +7885,11 @@
       <c r="G231" s="16">
         <v>0.07150000000000001</v>
       </c>
-      <c r="H231" s="16">
+      <c r="H231" s="17">
         <v>0.07099999999999999</v>
       </c>
-      <c r="I231" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B231:H231),B231:H231,0)),"")</f>
-        <v>5 years</v>
+      <c r="I231" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="232" spans="1:9">
@@ -8213,18 +7908,17 @@
       <c r="E232" s="16">
         <v>0.07400000000000001</v>
       </c>
-      <c r="F232" s="16">
+      <c r="F232" s="17">
         <v>0.07049999999999999</v>
       </c>
       <c r="G232" s="16">
         <v>0.0707</v>
       </c>
-      <c r="H232" s="16">
+      <c r="H232" s="17">
         <v>0.07049999999999999</v>
       </c>
-      <c r="I232" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B232:H232),B232:H232,0)),"")</f>
-        <v>3 years</v>
+      <c r="I232" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:9">
@@ -8249,12 +7943,11 @@
       <c r="G233" s="16">
         <v>0.0703</v>
       </c>
-      <c r="H233" s="16">
+      <c r="H233" s="17">
         <v>0.0699</v>
       </c>
-      <c r="I233" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B233:H233),B233:H233,0)),"")</f>
-        <v>5 years</v>
+      <c r="I233" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="234" spans="1:9">
@@ -8273,7 +7966,7 @@
       <c r="E234" s="16">
         <v>0.0736</v>
       </c>
-      <c r="F234" s="16">
+      <c r="F234" s="17">
         <v>0.0696</v>
       </c>
       <c r="G234" s="16">
@@ -8282,9 +7975,8 @@
       <c r="H234" s="16">
         <v>0.0698</v>
       </c>
-      <c r="I234" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B234:H234),B234:H234,0)),"")</f>
-        <v>3 years</v>
+      <c r="I234" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -8309,12 +8001,11 @@
       <c r="G235" s="16">
         <v>0.0699</v>
       </c>
-      <c r="H235" s="16">
+      <c r="H235" s="17">
         <v>0.0698</v>
       </c>
-      <c r="I235" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B235:H235),B235:H235,0)),"")</f>
-        <v>5 years</v>
+      <c r="I235" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="236" spans="1:9">
@@ -8339,12 +8030,11 @@
       <c r="G236" s="16">
         <v>0.0684</v>
       </c>
-      <c r="H236" s="16">
+      <c r="H236" s="17">
         <v>0.0679</v>
       </c>
-      <c r="I236" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B236:H236),B236:H236,0)),"")</f>
-        <v>5 years</v>
+      <c r="I236" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="237" spans="1:9">
@@ -8369,12 +8059,11 @@
       <c r="G237" s="16">
         <v>0.06309999999999999</v>
       </c>
-      <c r="H237" s="16">
+      <c r="H237" s="17">
         <v>0.063</v>
       </c>
-      <c r="I237" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B237:H237),B237:H237,0)),"")</f>
-        <v>5 years</v>
+      <c r="I237" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="238" spans="1:9">
@@ -8396,15 +8085,14 @@
       <c r="F238" s="16">
         <v>0.06269999999999999</v>
       </c>
-      <c r="G238" s="16">
+      <c r="G238" s="17">
         <v>0.06150000000000001</v>
       </c>
-      <c r="H238" s="16">
+      <c r="H238" s="17">
         <v>0.06150000000000001</v>
       </c>
-      <c r="I238" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B238:H238),B238:H238,0)),"")</f>
-        <v>4 years</v>
+      <c r="I238" s="18" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -8426,15 +8114,14 @@
       <c r="F239" s="16">
         <v>0.0611</v>
       </c>
-      <c r="G239" s="16">
+      <c r="G239" s="17">
         <v>0.061</v>
       </c>
-      <c r="H239" s="16">
+      <c r="H239" s="17">
         <v>0.061</v>
       </c>
-      <c r="I239" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B239:H239),B239:H239,0)),"")</f>
-        <v>4 years</v>
+      <c r="I239" s="18" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -8453,18 +8140,17 @@
       <c r="E240" s="16">
         <v>0.06269999999999999</v>
       </c>
-      <c r="F240" s="16">
+      <c r="F240" s="17">
         <v>0.061</v>
       </c>
-      <c r="G240" s="16">
+      <c r="G240" s="17">
         <v>0.061</v>
       </c>
-      <c r="H240" s="16">
+      <c r="H240" s="17">
         <v>0.061</v>
       </c>
-      <c r="I240" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B240:H240),B240:H240,0)),"")</f>
-        <v>3 years</v>
+      <c r="I240" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -8483,7 +8169,7 @@
       <c r="E241" s="16">
         <v>0.0612</v>
       </c>
-      <c r="F241" s="16">
+      <c r="F241" s="17">
         <v>0.0605</v>
       </c>
       <c r="G241" s="16">
@@ -8492,9 +8178,8 @@
       <c r="H241" s="16">
         <v>0.06150000000000001</v>
       </c>
-      <c r="I241" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B241:H241),B241:H241,0)),"")</f>
-        <v>3 years</v>
+      <c r="I241" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -8510,7 +8195,7 @@
       <c r="D242" s="16">
         <v>0.06150000000000001</v>
       </c>
-      <c r="E242" s="16">
+      <c r="E242" s="17">
         <v>0.0603</v>
       </c>
       <c r="F242" s="16">
@@ -8522,9 +8207,8 @@
       <c r="H242" s="16">
         <v>0.0619</v>
       </c>
-      <c r="I242" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B242:H242),B242:H242,0)),"")</f>
-        <v>2 years</v>
+      <c r="I242" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -8540,7 +8224,7 @@
       <c r="D243" s="16">
         <v>0.0587</v>
       </c>
-      <c r="E243" s="16">
+      <c r="E243" s="17">
         <v>0.0572</v>
       </c>
       <c r="F243" s="16">
@@ -8552,9 +8236,8 @@
       <c r="H243" s="16">
         <v>0.0612</v>
       </c>
-      <c r="I243" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B243:H243),B243:H243,0)),"")</f>
-        <v>2 years</v>
+      <c r="I243" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -8570,7 +8253,7 @@
       <c r="D244" s="16">
         <v>0.0588</v>
       </c>
-      <c r="E244" s="16">
+      <c r="E244" s="17">
         <v>0.0573</v>
       </c>
       <c r="F244" s="16">
@@ -8582,9 +8265,8 @@
       <c r="H244" s="16">
         <v>0.0611</v>
       </c>
-      <c r="I244" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B244:H244),B244:H244,0)),"")</f>
-        <v>2 years</v>
+      <c r="I244" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="245" spans="1:9">
@@ -8600,7 +8282,7 @@
       <c r="D245" s="16">
         <v>0.0568</v>
       </c>
-      <c r="E245" s="16">
+      <c r="E245" s="17">
         <v>0.0566</v>
       </c>
       <c r="F245" s="16">
@@ -8612,9 +8294,8 @@
       <c r="H245" s="16">
         <v>0.061</v>
       </c>
-      <c r="I245" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B245:H245),B245:H245,0)),"")</f>
-        <v>2 years</v>
+      <c r="I245" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="246" spans="1:9">
@@ -8630,7 +8311,7 @@
       <c r="D246" s="16">
         <v>0.0564</v>
       </c>
-      <c r="E246" s="16">
+      <c r="E246" s="17">
         <v>0.0563</v>
       </c>
       <c r="F246" s="16">
@@ -8642,9 +8323,8 @@
       <c r="H246" s="16">
         <v>0.0607</v>
       </c>
-      <c r="I246" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B246:H246),B246:H246,0)),"")</f>
-        <v>2 years</v>
+      <c r="I246" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="247" spans="1:9">
@@ -8657,7 +8337,7 @@
       <c r="C247" s="16">
         <v>0.0585</v>
       </c>
-      <c r="D247" s="16">
+      <c r="D247" s="17">
         <v>0.0556</v>
       </c>
       <c r="E247" s="16">
@@ -8672,9 +8352,8 @@
       <c r="H247" s="16">
         <v>0.06</v>
       </c>
-      <c r="I247" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B247:H247),B247:H247,0)),"")</f>
-        <v>1 year</v>
+      <c r="I247" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="248" spans="1:9">
@@ -8687,7 +8366,7 @@
       <c r="C248" s="16">
         <v>0.0584</v>
       </c>
-      <c r="D248" s="16">
+      <c r="D248" s="17">
         <v>0.0553</v>
       </c>
       <c r="E248" s="16">
@@ -8702,9 +8381,8 @@
       <c r="H248" s="16">
         <v>0.06</v>
       </c>
-      <c r="I248" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B248:H248),B248:H248,0)),"")</f>
-        <v>1 year</v>
+      <c r="I248" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="249" spans="1:9">
@@ -8717,7 +8395,7 @@
       <c r="C249" s="16">
         <v>0.0568</v>
       </c>
-      <c r="D249" s="16">
+      <c r="D249" s="17">
         <v>0.05400000000000001</v>
       </c>
       <c r="E249" s="16">
@@ -8732,9 +8410,8 @@
       <c r="H249" s="16">
         <v>0.05889999999999999</v>
       </c>
-      <c r="I249" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B249:H249),B249:H249,0)),"")</f>
-        <v>1 year</v>
+      <c r="I249" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="250" spans="1:9">
@@ -8747,7 +8424,7 @@
       <c r="C250" s="16">
         <v>0.0566</v>
       </c>
-      <c r="D250" s="16">
+      <c r="D250" s="17">
         <v>0.0537</v>
       </c>
       <c r="E250" s="16">
@@ -8762,9 +8439,8 @@
       <c r="H250" s="16">
         <v>0.05889999999999999</v>
       </c>
-      <c r="I250" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B250:H250),B250:H250,0)),"")</f>
-        <v>1 year</v>
+      <c r="I250" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="251" spans="1:9">
@@ -8777,7 +8453,7 @@
       <c r="C251" s="16">
         <v>0.0544</v>
       </c>
-      <c r="D251" s="16">
+      <c r="D251" s="17">
         <v>0.051</v>
       </c>
       <c r="E251" s="16">
@@ -8792,9 +8468,8 @@
       <c r="H251" s="16">
         <v>0.0556</v>
       </c>
-      <c r="I251" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B251:H251),B251:H251,0)),"")</f>
-        <v>1 year</v>
+      <c r="I251" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="252" spans="1:9">
@@ -8807,7 +8482,7 @@
       <c r="C252" s="16">
         <v>0.0542</v>
       </c>
-      <c r="D252" s="16">
+      <c r="D252" s="17">
         <v>0.051</v>
       </c>
       <c r="E252" s="16">
@@ -8822,9 +8497,8 @@
       <c r="H252" s="16">
         <v>0.0556</v>
       </c>
-      <c r="I252" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B252:H252),B252:H252,0)),"")</f>
-        <v>1 year</v>
+      <c r="I252" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="253" spans="1:9">
@@ -8837,7 +8511,7 @@
       <c r="C253" s="16">
         <v>0.0535</v>
       </c>
-      <c r="D253" s="16">
+      <c r="D253" s="17">
         <v>0.0512</v>
       </c>
       <c r="E253" s="16">
@@ -8852,9 +8526,8 @@
       <c r="H253" s="16">
         <v>0.05769999999999999</v>
       </c>
-      <c r="I253" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B253:H253),B253:H253,0)),"")</f>
-        <v>1 year</v>
+      <c r="I253" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="254" spans="1:9">
@@ -8867,7 +8540,7 @@
       <c r="C254" s="16">
         <v>0.0532</v>
       </c>
-      <c r="D254" s="16">
+      <c r="D254" s="17">
         <v>0.0513</v>
       </c>
       <c r="E254" s="16">
@@ -8882,9 +8555,8 @@
       <c r="H254" s="16">
         <v>0.0584</v>
       </c>
-      <c r="I254" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B254:H254),B254:H254,0)),"")</f>
-        <v>1 year</v>
+      <c r="I254" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -8897,7 +8569,7 @@
       <c r="C255" s="16">
         <v>0.05230000000000001</v>
       </c>
-      <c r="D255" s="16">
+      <c r="D255" s="17">
         <v>0.0513</v>
       </c>
       <c r="E255" s="16">
@@ -8912,9 +8584,8 @@
       <c r="H255" s="16">
         <v>0.0596</v>
       </c>
-      <c r="I255" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B255:H255),B255:H255,0)),"")</f>
-        <v>1 year</v>
+      <c r="I255" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="256" spans="1:9">
@@ -8927,7 +8598,7 @@
       <c r="C256" s="16">
         <v>0.052</v>
       </c>
-      <c r="D256" s="16">
+      <c r="D256" s="17">
         <v>0.0519</v>
       </c>
       <c r="E256" s="16">
@@ -8942,9 +8613,8 @@
       <c r="H256" s="16">
         <v>0.06179999999999999</v>
       </c>
-      <c r="I256" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B256:H256),B256:H256,0)),"")</f>
-        <v>1 year</v>
+      <c r="I256" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -8954,7 +8624,7 @@
       <c r="B257" s="16">
         <v>0.0611</v>
       </c>
-      <c r="C257" s="16">
+      <c r="C257" s="17">
         <v>0.05139999999999999</v>
       </c>
       <c r="D257" s="16">
@@ -8972,9 +8642,8 @@
       <c r="H257" s="16">
         <v>0.0619</v>
       </c>
-      <c r="I257" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B257:H257),B257:H257,0)),"")</f>
-        <v>6 months</v>
+      <c r="I257" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="258" spans="1:9">
@@ -8984,7 +8653,7 @@
       <c r="B258" s="16">
         <v>0.06150000000000001</v>
       </c>
-      <c r="C258" s="16">
+      <c r="C258" s="17">
         <v>0.0515</v>
       </c>
       <c r="D258" s="16">
@@ -9002,9 +8671,8 @@
       <c r="H258" s="16">
         <v>0.0624</v>
       </c>
-      <c r="I258" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B258:H258),B258:H258,0)),"")</f>
-        <v>6 months</v>
+      <c r="I258" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="259" spans="1:9">
@@ -9014,7 +8682,7 @@
       <c r="B259" s="16">
         <v>0.06150000000000001</v>
       </c>
-      <c r="C259" s="16">
+      <c r="C259" s="17">
         <v>0.052</v>
       </c>
       <c r="D259" s="16">
@@ -9032,9 +8700,8 @@
       <c r="H259" s="16">
         <v>0.0617</v>
       </c>
-      <c r="I259" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B259:H259),B259:H259,0)),"")</f>
-        <v>6 months</v>
+      <c r="I259" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="260" spans="1:9">
@@ -9044,7 +8711,7 @@
       <c r="B260" s="16">
         <v>0.06320000000000001</v>
       </c>
-      <c r="C260" s="16">
+      <c r="C260" s="17">
         <v>0.0525</v>
       </c>
       <c r="D260" s="16">
@@ -9062,9 +8729,8 @@
       <c r="H260" s="16">
         <v>0.0613</v>
       </c>
-      <c r="I260" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B260:H260),B260:H260,0)),"")</f>
-        <v>6 months</v>
+      <c r="I260" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="261" spans="1:9">
@@ -9074,7 +8740,7 @@
       <c r="B261" s="16">
         <v>0.0626</v>
       </c>
-      <c r="C261" s="16">
+      <c r="C261" s="17">
         <v>0.0529</v>
       </c>
       <c r="D261" s="16">
@@ -9092,9 +8758,8 @@
       <c r="H261" s="16">
         <v>0.0613</v>
       </c>
-      <c r="I261" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B261:H261),B261:H261,0)),"")</f>
-        <v>6 months</v>
+      <c r="I261" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="262" spans="1:9">
@@ -9104,7 +8769,7 @@
       <c r="B262" s="16">
         <v>0.0643</v>
       </c>
-      <c r="C262" s="16">
+      <c r="C262" s="17">
         <v>0.0533</v>
       </c>
       <c r="D262" s="16">
@@ -9122,18 +8787,12 @@
       <c r="H262" s="16">
         <v>0.062</v>
       </c>
-      <c r="I262" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$H$1,MATCH(MIN(B262:H262),B262:H262,0)),"")</f>
-        <v>6 months</v>
+      <c r="I262" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I262"/>
-  <conditionalFormatting sqref="B2:H262">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(B2&lt;&gt;"",B2=MIN($B2:$H2))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -9185,7 +8844,7 @@
       <c r="B2" s="16">
         <v>0.0482</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="17">
         <v>0.04480000000000001</v>
       </c>
       <c r="D2" s="16">
@@ -9200,9 +8859,8 @@
       <c r="G2" s="16">
         <v>0.0558</v>
       </c>
-      <c r="H2" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B2:G2),B2:G2,0)),"")</f>
-        <v>1 year</v>
+      <c r="H2" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -9212,7 +8870,7 @@
       <c r="B3" s="16">
         <v>0.049</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="17">
         <v>0.045</v>
       </c>
       <c r="D3" s="16">
@@ -9227,9 +8885,8 @@
       <c r="G3" s="16">
         <v>0.0562</v>
       </c>
-      <c r="H3" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B3:G3),B3:G3,0)),"")</f>
-        <v>1 year</v>
+      <c r="H3" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -9239,7 +8896,7 @@
       <c r="B4" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="17">
         <v>0.0457</v>
       </c>
       <c r="D4" s="16">
@@ -9254,9 +8911,8 @@
       <c r="G4" s="16">
         <v>0.057</v>
       </c>
-      <c r="H4" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B4:G4),B4:G4,0)),"")</f>
-        <v>1 year</v>
+      <c r="H4" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -9266,7 +8922,7 @@
       <c r="B5" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="17">
         <v>0.04559999999999999</v>
       </c>
       <c r="D5" s="16">
@@ -9281,9 +8937,8 @@
       <c r="G5" s="16">
         <v>0.0571</v>
       </c>
-      <c r="H5" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B5:G5),B5:G5,0)),"")</f>
-        <v>1 year</v>
+      <c r="H5" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -9293,7 +8948,7 @@
       <c r="B6" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="17">
         <v>0.04559999999999999</v>
       </c>
       <c r="D6" s="16">
@@ -9308,9 +8963,8 @@
       <c r="G6" s="16">
         <v>0.0573</v>
       </c>
-      <c r="H6" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B6:G6),B6:G6,0)),"")</f>
-        <v>1 year</v>
+      <c r="H6" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -9320,7 +8974,7 @@
       <c r="B7" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="17">
         <v>0.04559999999999999</v>
       </c>
       <c r="D7" s="16">
@@ -9335,9 +8989,8 @@
       <c r="G7" s="16">
         <v>0.0573</v>
       </c>
-      <c r="H7" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B7:G7),B7:G7,0)),"")</f>
-        <v>1 year</v>
+      <c r="H7" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -9347,7 +9000,7 @@
       <c r="B8" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="17">
         <v>0.0454</v>
       </c>
       <c r="D8" s="16">
@@ -9362,9 +9015,8 @@
       <c r="G8" s="16">
         <v>0.0576</v>
       </c>
-      <c r="H8" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B8:G8),B8:G8,0)),"")</f>
-        <v>1 year</v>
+      <c r="H8" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -9374,7 +9026,7 @@
       <c r="B9" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="17">
         <v>0.0454</v>
       </c>
       <c r="D9" s="16">
@@ -9389,9 +9041,8 @@
       <c r="G9" s="16">
         <v>0.0573</v>
       </c>
-      <c r="H9" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B9:G9),B9:G9,0)),"")</f>
-        <v>1 year</v>
+      <c r="H9" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -9401,7 +9052,7 @@
       <c r="B10" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="17">
         <v>0.0452</v>
       </c>
       <c r="D10" s="16">
@@ -9416,9 +9067,8 @@
       <c r="G10" s="16">
         <v>0.0571</v>
       </c>
-      <c r="H10" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B10:G10),B10:G10,0)),"")</f>
-        <v>1 year</v>
+      <c r="H10" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -9428,7 +9078,7 @@
       <c r="B11" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="17">
         <v>0.0454</v>
       </c>
       <c r="D11" s="16">
@@ -9443,9 +9093,8 @@
       <c r="G11" s="16">
         <v>0.0571</v>
       </c>
-      <c r="H11" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B11:G11),B11:G11,0)),"")</f>
-        <v>1 year</v>
+      <c r="H11" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -9455,7 +9104,7 @@
       <c r="B12" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="17">
         <v>0.0452</v>
       </c>
       <c r="D12" s="16">
@@ -9470,9 +9119,8 @@
       <c r="G12" s="16">
         <v>0.0567</v>
       </c>
-      <c r="H12" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B12:G12),B12:G12,0)),"")</f>
-        <v>1 year</v>
+      <c r="H12" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -9482,7 +9130,7 @@
       <c r="B13" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="17">
         <v>0.0452</v>
       </c>
       <c r="D13" s="16">
@@ -9497,9 +9145,8 @@
       <c r="G13" s="16">
         <v>0.0564</v>
       </c>
-      <c r="H13" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B13:G13),B13:G13,0)),"")</f>
-        <v>1 year</v>
+      <c r="H13" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -9509,7 +9156,7 @@
       <c r="B14" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="17">
         <v>0.0449</v>
       </c>
       <c r="D14" s="16">
@@ -9524,9 +9171,8 @@
       <c r="G14" s="16">
         <v>0.0564</v>
       </c>
-      <c r="H14" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B14:G14),B14:G14,0)),"")</f>
-        <v>1 year</v>
+      <c r="H14" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -9536,7 +9182,7 @@
       <c r="B15" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="17">
         <v>0.0437</v>
       </c>
       <c r="D15" s="16">
@@ -9551,9 +9197,8 @@
       <c r="G15" s="16">
         <v>0.0561</v>
       </c>
-      <c r="H15" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B15:G15),B15:G15,0)),"")</f>
-        <v>1 year</v>
+      <c r="H15" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -9563,7 +9208,7 @@
       <c r="B16" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="17">
         <v>0.0437</v>
       </c>
       <c r="D16" s="16">
@@ -9578,9 +9223,8 @@
       <c r="G16" s="16">
         <v>0.0561</v>
       </c>
-      <c r="H16" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B16:G16),B16:G16,0)),"")</f>
-        <v>1 year</v>
+      <c r="H16" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -9590,7 +9234,7 @@
       <c r="B17" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="17">
         <v>0.0434</v>
       </c>
       <c r="D17" s="16">
@@ -9605,9 +9249,8 @@
       <c r="G17" s="16">
         <v>0.0561</v>
       </c>
-      <c r="H17" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B17:G17),B17:G17,0)),"")</f>
-        <v>1 year</v>
+      <c r="H17" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -9617,7 +9260,7 @@
       <c r="B18" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="17">
         <v>0.0434</v>
       </c>
       <c r="D18" s="16">
@@ -9632,9 +9275,8 @@
       <c r="G18" s="16">
         <v>0.0561</v>
       </c>
-      <c r="H18" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B18:G18),B18:G18,0)),"")</f>
-        <v>1 year</v>
+      <c r="H18" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -9644,7 +9286,7 @@
       <c r="B19" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="17">
         <v>0.043</v>
       </c>
       <c r="D19" s="16">
@@ -9659,9 +9301,8 @@
       <c r="G19" s="16">
         <v>0.0561</v>
       </c>
-      <c r="H19" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B19:G19),B19:G19,0)),"")</f>
-        <v>1 year</v>
+      <c r="H19" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -9671,7 +9312,7 @@
       <c r="B20" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="17">
         <v>0.0425</v>
       </c>
       <c r="D20" s="16">
@@ -9686,9 +9327,8 @@
       <c r="G20" s="16">
         <v>0.0561</v>
       </c>
-      <c r="H20" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B20:G20),B20:G20,0)),"")</f>
-        <v>1 year</v>
+      <c r="H20" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -9698,7 +9338,7 @@
       <c r="B21" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="17">
         <v>0.0423</v>
       </c>
       <c r="D21" s="16">
@@ -9713,9 +9353,8 @@
       <c r="G21" s="16">
         <v>0.0546</v>
       </c>
-      <c r="H21" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B21:G21),B21:G21,0)),"")</f>
-        <v>1 year</v>
+      <c r="H21" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -9725,7 +9364,7 @@
       <c r="B22" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="17">
         <v>0.0416</v>
       </c>
       <c r="D22" s="16">
@@ -9740,9 +9379,8 @@
       <c r="G22" s="16">
         <v>0.0499</v>
       </c>
-      <c r="H22" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B22:G22),B22:G22,0)),"")</f>
-        <v>1 year</v>
+      <c r="H22" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -9752,7 +9390,7 @@
       <c r="B23" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="17">
         <v>0.0414</v>
       </c>
       <c r="D23" s="16">
@@ -9767,9 +9405,8 @@
       <c r="G23" s="16">
         <v>0.0499</v>
       </c>
-      <c r="H23" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B23:G23),B23:G23,0)),"")</f>
-        <v>1 year</v>
+      <c r="H23" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -9779,7 +9416,7 @@
       <c r="B24" s="16">
         <v>0.0493</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="17">
         <v>0.04</v>
       </c>
       <c r="D24" s="16">
@@ -9794,9 +9431,8 @@
       <c r="G24" s="16">
         <v>0.0499</v>
       </c>
-      <c r="H24" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B24:G24),B24:G24,0)),"")</f>
-        <v>1 year</v>
+      <c r="H24" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -9806,7 +9442,7 @@
       <c r="B25" s="16">
         <v>0.0495</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="17">
         <v>0.0409</v>
       </c>
       <c r="D25" s="16">
@@ -9821,9 +9457,8 @@
       <c r="G25" s="16">
         <v>0.0507</v>
       </c>
-      <c r="H25" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B25:G25),B25:G25,0)),"")</f>
-        <v>1 year</v>
+      <c r="H25" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -9833,7 +9468,7 @@
       <c r="B26" s="16">
         <v>0.0495</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="17">
         <v>0.0406</v>
       </c>
       <c r="D26" s="16">
@@ -9848,9 +9483,8 @@
       <c r="G26" s="16">
         <v>0.0507</v>
       </c>
-      <c r="H26" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B26:G26),B26:G26,0)),"")</f>
-        <v>1 year</v>
+      <c r="H26" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -9860,7 +9494,7 @@
       <c r="B27" s="16">
         <v>0.0495</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="17">
         <v>0.0403</v>
       </c>
       <c r="D27" s="16">
@@ -9875,9 +9509,8 @@
       <c r="G27" s="16">
         <v>0.0507</v>
       </c>
-      <c r="H27" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B27:G27),B27:G27,0)),"")</f>
-        <v>1 year</v>
+      <c r="H27" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -9890,7 +9523,7 @@
       <c r="C28" s="16">
         <v>0.0405</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="17">
         <v>0.0399</v>
       </c>
       <c r="E28" s="16">
@@ -9902,9 +9535,8 @@
       <c r="G28" s="16">
         <v>0.0507</v>
       </c>
-      <c r="H28" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B28:G28),B28:G28,0)),"")</f>
-        <v>2 years</v>
+      <c r="H28" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -9917,7 +9549,7 @@
       <c r="C29" s="16">
         <v>0.0404</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="17">
         <v>0.0392</v>
       </c>
       <c r="E29" s="16">
@@ -9929,9 +9561,8 @@
       <c r="G29" s="16">
         <v>0.0459</v>
       </c>
-      <c r="H29" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B29:G29),B29:G29,0)),"")</f>
-        <v>2 years</v>
+      <c r="H29" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -9941,10 +9572,10 @@
       <c r="B30" s="16">
         <v>0.0495</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="17">
         <v>0.0392</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="17">
         <v>0.0392</v>
       </c>
       <c r="E30" s="16">
@@ -9956,9 +9587,8 @@
       <c r="G30" s="16">
         <v>0.0446</v>
       </c>
-      <c r="H30" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B30:G30),B30:G30,0)),"")</f>
-        <v>1 year</v>
+      <c r="H30" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -9971,7 +9601,7 @@
       <c r="C31" s="16">
         <v>0.0388</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.0384</v>
       </c>
       <c r="E31" s="16">
@@ -9983,9 +9613,8 @@
       <c r="G31" s="16">
         <v>0.0446</v>
       </c>
-      <c r="H31" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B31:G31),B31:G31,0)),"")</f>
-        <v>2 years</v>
+      <c r="H31" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -9998,7 +9627,7 @@
       <c r="C32" s="16">
         <v>0.0386</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>0.0379</v>
       </c>
       <c r="E32" s="16">
@@ -10010,9 +9639,8 @@
       <c r="G32" s="16">
         <v>0.0446</v>
       </c>
-      <c r="H32" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B32:G32),B32:G32,0)),"")</f>
-        <v>2 years</v>
+      <c r="H32" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -10022,10 +9650,10 @@
       <c r="B33" s="16">
         <v>0.0437</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="17">
         <v>0.0366</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="17">
         <v>0.0366</v>
       </c>
       <c r="E33" s="16">
@@ -10037,9 +9665,8 @@
       <c r="G33" s="16">
         <v>0.0438</v>
       </c>
-      <c r="H33" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B33:G33),B33:G33,0)),"")</f>
-        <v>1 year</v>
+      <c r="H33" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -10052,7 +9679,7 @@
       <c r="C34" s="16">
         <v>0.0352</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="17">
         <v>0.0344</v>
       </c>
       <c r="E34" s="16">
@@ -10064,9 +9691,8 @@
       <c r="G34" s="16">
         <v>0.0416</v>
       </c>
-      <c r="H34" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B34:G34),B34:G34,0)),"")</f>
-        <v>2 years</v>
+      <c r="H34" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -10079,7 +9705,7 @@
       <c r="C35" s="16">
         <v>0.0349</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="17">
         <v>0.034</v>
       </c>
       <c r="E35" s="16">
@@ -10091,9 +9717,8 @@
       <c r="G35" s="16">
         <v>0.0421</v>
       </c>
-      <c r="H35" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B35:G35),B35:G35,0)),"")</f>
-        <v>2 years</v>
+      <c r="H35" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -10103,7 +9728,7 @@
       <c r="B36" s="16">
         <v>0.04</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="17">
         <v>0.0341</v>
       </c>
       <c r="D36" s="16">
@@ -10118,9 +9743,8 @@
       <c r="G36" s="16">
         <v>0.0415</v>
       </c>
-      <c r="H36" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B36:G36),B36:G36,0)),"")</f>
-        <v>1 year</v>
+      <c r="H36" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -10130,7 +9754,7 @@
       <c r="B37" s="16">
         <v>0.04</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="17">
         <v>0.0338</v>
       </c>
       <c r="D37" s="16">
@@ -10145,9 +9769,8 @@
       <c r="G37" s="16">
         <v>0.04190000000000001</v>
       </c>
-      <c r="H37" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B37:G37),B37:G37,0)),"")</f>
-        <v>1 year</v>
+      <c r="H37" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -10157,7 +9780,7 @@
       <c r="B38" s="16">
         <v>0.04</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="17">
         <v>0.0337</v>
       </c>
       <c r="D38" s="16">
@@ -10172,9 +9795,8 @@
       <c r="G38" s="16">
         <v>0.04190000000000001</v>
       </c>
-      <c r="H38" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B38:G38),B38:G38,0)),"")</f>
-        <v>1 year</v>
+      <c r="H38" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -10184,7 +9806,7 @@
       <c r="B39" s="16">
         <v>0.04</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="17">
         <v>0.0336</v>
       </c>
       <c r="D39" s="16">
@@ -10199,9 +9821,8 @@
       <c r="G39" s="16">
         <v>0.0416</v>
       </c>
-      <c r="H39" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B39:G39),B39:G39,0)),"")</f>
-        <v>1 year</v>
+      <c r="H39" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -10211,7 +9832,7 @@
       <c r="B40" s="16">
         <v>0.0392</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="17">
         <v>0.0308</v>
       </c>
       <c r="D40" s="16">
@@ -10226,9 +9847,8 @@
       <c r="G40" s="16">
         <v>0.0386</v>
       </c>
-      <c r="H40" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B40:G40),B40:G40,0)),"")</f>
-        <v>1 year</v>
+      <c r="H40" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -10238,7 +9858,7 @@
       <c r="B41" s="16">
         <v>0.0392</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="17">
         <v>0.0307</v>
       </c>
       <c r="D41" s="16">
@@ -10253,9 +9873,8 @@
       <c r="G41" s="16">
         <v>0.0386</v>
       </c>
-      <c r="H41" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B41:G41),B41:G41,0)),"")</f>
-        <v>1 year</v>
+      <c r="H41" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -10265,7 +9884,7 @@
       <c r="B42" s="16">
         <v>0.0378</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="17">
         <v>0.028</v>
       </c>
       <c r="D42" s="16">
@@ -10280,9 +9899,8 @@
       <c r="G42" s="16">
         <v>0.0353</v>
       </c>
-      <c r="H42" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B42:G42),B42:G42,0)),"")</f>
-        <v>1 year</v>
+      <c r="H42" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -10292,7 +9910,7 @@
       <c r="B43" s="16">
         <v>0.035</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="17">
         <v>0.0267</v>
       </c>
       <c r="D43" s="16">
@@ -10307,9 +9925,8 @@
       <c r="G43" s="16">
         <v>0.0313</v>
       </c>
-      <c r="H43" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B43:G43),B43:G43,0)),"")</f>
-        <v>1 year</v>
+      <c r="H43" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -10319,7 +9936,7 @@
       <c r="B44" s="16">
         <v>0.0339</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="17">
         <v>0.0257</v>
       </c>
       <c r="D44" s="16">
@@ -10334,9 +9951,8 @@
       <c r="G44" s="16">
         <v>0.0307</v>
       </c>
-      <c r="H44" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B44:G44),B44:G44,0)),"")</f>
-        <v>1 year</v>
+      <c r="H44" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -10346,7 +9962,7 @@
       <c r="B45" s="16">
         <v>0.0337</v>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="17">
         <v>0.0256</v>
       </c>
       <c r="D45" s="16">
@@ -10361,9 +9977,8 @@
       <c r="G45" s="16">
         <v>0.0307</v>
       </c>
-      <c r="H45" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B45:G45),B45:G45,0)),"")</f>
-        <v>1 year</v>
+      <c r="H45" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -10373,7 +9988,7 @@
       <c r="B46" s="16">
         <v>0.0337</v>
       </c>
-      <c r="C46" s="16">
+      <c r="C46" s="17">
         <v>0.0256</v>
       </c>
       <c r="D46" s="16">
@@ -10388,9 +10003,8 @@
       <c r="G46" s="16">
         <v>0.0307</v>
       </c>
-      <c r="H46" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B46:G46),B46:G46,0)),"")</f>
-        <v>1 year</v>
+      <c r="H46" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -10400,7 +10014,7 @@
       <c r="B47" s="16">
         <v>0.03240000000000001</v>
       </c>
-      <c r="C47" s="16">
+      <c r="C47" s="17">
         <v>0.0253</v>
       </c>
       <c r="D47" s="16">
@@ -10415,9 +10029,8 @@
       <c r="G47" s="16">
         <v>0.0304</v>
       </c>
-      <c r="H47" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B47:G47),B47:G47,0)),"")</f>
-        <v>1 year</v>
+      <c r="H47" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -10427,7 +10040,7 @@
       <c r="B48" s="16">
         <v>0.03240000000000001</v>
       </c>
-      <c r="C48" s="16">
+      <c r="C48" s="17">
         <v>0.0253</v>
       </c>
       <c r="D48" s="16">
@@ -10442,9 +10055,8 @@
       <c r="G48" s="16">
         <v>0.0304</v>
       </c>
-      <c r="H48" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B48:G48),B48:G48,0)),"")</f>
-        <v>1 year</v>
+      <c r="H48" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -10454,7 +10066,7 @@
       <c r="B49" s="16">
         <v>0.03240000000000001</v>
       </c>
-      <c r="C49" s="16">
+      <c r="C49" s="17">
         <v>0.0253</v>
       </c>
       <c r="D49" s="16">
@@ -10469,9 +10081,8 @@
       <c r="G49" s="16">
         <v>0.0304</v>
       </c>
-      <c r="H49" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B49:G49),B49:G49,0)),"")</f>
-        <v>1 year</v>
+      <c r="H49" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -10481,7 +10092,7 @@
       <c r="B50" s="16">
         <v>0.03240000000000001</v>
       </c>
-      <c r="C50" s="16">
+      <c r="C50" s="17">
         <v>0.0237</v>
       </c>
       <c r="D50" s="16">
@@ -10496,9 +10107,8 @@
       <c r="G50" s="16">
         <v>0.0304</v>
       </c>
-      <c r="H50" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B50:G50),B50:G50,0)),"")</f>
-        <v>1 year</v>
+      <c r="H50" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -10508,7 +10118,7 @@
       <c r="B51" s="16">
         <v>0.03240000000000001</v>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="17">
         <v>0.0229</v>
       </c>
       <c r="D51" s="16">
@@ -10523,9 +10133,8 @@
       <c r="G51" s="16">
         <v>0.0301</v>
       </c>
-      <c r="H51" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B51:G51),B51:G51,0)),"")</f>
-        <v>1 year</v>
+      <c r="H51" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -10535,7 +10144,7 @@
       <c r="B52" s="16">
         <v>0.03240000000000001</v>
       </c>
-      <c r="C52" s="16">
+      <c r="C52" s="17">
         <v>0.0229</v>
       </c>
       <c r="D52" s="16">
@@ -10550,9 +10159,8 @@
       <c r="G52" s="16">
         <v>0.0301</v>
       </c>
-      <c r="H52" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B52:G52),B52:G52,0)),"")</f>
-        <v>1 year</v>
+      <c r="H52" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -10562,7 +10170,7 @@
       <c r="B53" s="16">
         <v>0.03240000000000001</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="17">
         <v>0.0231</v>
       </c>
       <c r="D53" s="16">
@@ -10577,9 +10185,8 @@
       <c r="G53" s="16">
         <v>0.0313</v>
       </c>
-      <c r="H53" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B53:G53),B53:G53,0)),"")</f>
-        <v>1 year</v>
+      <c r="H53" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -10589,7 +10196,7 @@
       <c r="B54" s="16">
         <v>0.03240000000000001</v>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="17">
         <v>0.0227</v>
       </c>
       <c r="D54" s="16">
@@ -10604,9 +10211,8 @@
       <c r="G54" s="16">
         <v>0.0333</v>
       </c>
-      <c r="H54" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B54:G54),B54:G54,0)),"")</f>
-        <v>1 year</v>
+      <c r="H54" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -10616,7 +10222,7 @@
       <c r="B55" s="16">
         <v>0.0309</v>
       </c>
-      <c r="C55" s="16">
+      <c r="C55" s="17">
         <v>0.0221</v>
       </c>
       <c r="D55" s="16">
@@ -10631,9 +10237,8 @@
       <c r="G55" s="16">
         <v>0.0357</v>
       </c>
-      <c r="H55" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B55:G55),B55:G55,0)),"")</f>
-        <v>1 year</v>
+      <c r="H55" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -10643,7 +10248,7 @@
       <c r="B56" s="16">
         <v>0.0316</v>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="17">
         <v>0.0248</v>
       </c>
       <c r="D56" s="16">
@@ -10658,9 +10263,8 @@
       <c r="G56" s="16">
         <v>0.0383</v>
       </c>
-      <c r="H56" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B56:G56),B56:G56,0)),"")</f>
-        <v>1 year</v>
+      <c r="H56" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -10670,7 +10274,7 @@
       <c r="B57" s="16">
         <v>0.0316</v>
       </c>
-      <c r="C57" s="16">
+      <c r="C57" s="17">
         <v>0.0249</v>
       </c>
       <c r="D57" s="16">
@@ -10685,9 +10289,8 @@
       <c r="G57" s="16">
         <v>0.0383</v>
       </c>
-      <c r="H57" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B57:G57),B57:G57,0)),"")</f>
-        <v>1 year</v>
+      <c r="H57" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -10697,7 +10300,7 @@
       <c r="B58" s="16">
         <v>0.0322</v>
       </c>
-      <c r="C58" s="16">
+      <c r="C58" s="17">
         <v>0.0272</v>
       </c>
       <c r="D58" s="16">
@@ -10712,9 +10315,8 @@
       <c r="G58" s="16">
         <v>0.0403</v>
       </c>
-      <c r="H58" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B58:G58),B58:G58,0)),"")</f>
-        <v>1 year</v>
+      <c r="H58" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -10724,7 +10326,7 @@
       <c r="B59" s="16">
         <v>0.036</v>
       </c>
-      <c r="C59" s="16">
+      <c r="C59" s="17">
         <v>0.0316</v>
       </c>
       <c r="D59" s="16">
@@ -10739,9 +10341,8 @@
       <c r="G59" s="16">
         <v>0.0443</v>
       </c>
-      <c r="H59" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B59:G59),B59:G59,0)),"")</f>
-        <v>1 year</v>
+      <c r="H59" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -10751,7 +10352,7 @@
       <c r="B60" s="16">
         <v>0.0386</v>
       </c>
-      <c r="C60" s="16">
+      <c r="C60" s="17">
         <v>0.0354</v>
       </c>
       <c r="D60" s="16">
@@ -10766,9 +10367,8 @@
       <c r="G60" s="16">
         <v>0.0491</v>
       </c>
-      <c r="H60" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B60:G60),B60:G60,0)),"")</f>
-        <v>1 year</v>
+      <c r="H60" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -10778,7 +10378,7 @@
       <c r="B61" s="16">
         <v>0.0386</v>
       </c>
-      <c r="C61" s="16">
+      <c r="C61" s="17">
         <v>0.0359</v>
       </c>
       <c r="D61" s="16">
@@ -10793,9 +10393,8 @@
       <c r="G61" s="16">
         <v>0.04940000000000001</v>
       </c>
-      <c r="H61" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B61:G61),B61:G61,0)),"")</f>
-        <v>1 year</v>
+      <c r="H61" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -10805,7 +10404,7 @@
       <c r="B62" s="16">
         <v>0.0386</v>
       </c>
-      <c r="C62" s="16">
+      <c r="C62" s="17">
         <v>0.0357</v>
       </c>
       <c r="D62" s="16">
@@ -10820,9 +10419,8 @@
       <c r="G62" s="16">
         <v>0.04940000000000001</v>
       </c>
-      <c r="H62" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B62:G62),B62:G62,0)),"")</f>
-        <v>1 year</v>
+      <c r="H62" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -10832,7 +10430,7 @@
       <c r="B63" s="16">
         <v>0.0396</v>
       </c>
-      <c r="C63" s="16">
+      <c r="C63" s="17">
         <v>0.0371</v>
       </c>
       <c r="D63" s="16">
@@ -10847,9 +10445,8 @@
       <c r="G63" s="16">
         <v>0.0501</v>
       </c>
-      <c r="H63" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B63:G63),B63:G63,0)),"")</f>
-        <v>1 year</v>
+      <c r="H63" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -10859,7 +10456,7 @@
       <c r="B64" s="16">
         <v>0.0413</v>
       </c>
-      <c r="C64" s="16">
+      <c r="C64" s="17">
         <v>0.0393</v>
       </c>
       <c r="D64" s="16">
@@ -10874,9 +10471,8 @@
       <c r="G64" s="16">
         <v>0.051</v>
       </c>
-      <c r="H64" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B64:G64),B64:G64,0)),"")</f>
-        <v>1 year</v>
+      <c r="H64" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -10886,7 +10482,7 @@
       <c r="B65" s="16">
         <v>0.0447</v>
       </c>
-      <c r="C65" s="16">
+      <c r="C65" s="17">
         <v>0.0431</v>
       </c>
       <c r="D65" s="16">
@@ -10901,9 +10497,8 @@
       <c r="G65" s="16">
         <v>0.05860000000000001</v>
       </c>
-      <c r="H65" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B65:G65),B65:G65,0)),"")</f>
-        <v>1 year</v>
+      <c r="H65" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -10913,7 +10508,7 @@
       <c r="B66" s="16">
         <v>0.0457</v>
       </c>
-      <c r="C66" s="16">
+      <c r="C66" s="17">
         <v>0.0445</v>
       </c>
       <c r="D66" s="16">
@@ -10928,9 +10523,8 @@
       <c r="G66" s="16">
         <v>0.0595</v>
       </c>
-      <c r="H66" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B66:G66),B66:G66,0)),"")</f>
-        <v>1 year</v>
+      <c r="H66" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -10940,7 +10534,7 @@
       <c r="B67" s="16">
         <v>0.0518</v>
       </c>
-      <c r="C67" s="16">
+      <c r="C67" s="17">
         <v>0.05110000000000001</v>
       </c>
       <c r="D67" s="16">
@@ -10955,9 +10549,8 @@
       <c r="G67" s="16">
         <v>0.0629</v>
       </c>
-      <c r="H67" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B67:G67),B67:G67,0)),"")</f>
-        <v>1 year</v>
+      <c r="H67" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -10967,7 +10560,7 @@
       <c r="B68" s="16">
         <v>0.0519</v>
       </c>
-      <c r="C68" s="16">
+      <c r="C68" s="17">
         <v>0.0516</v>
       </c>
       <c r="D68" s="16">
@@ -10982,9 +10575,8 @@
       <c r="G68" s="16">
         <v>0.0629</v>
       </c>
-      <c r="H68" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B68:G68),B68:G68,0)),"")</f>
-        <v>1 year</v>
+      <c r="H68" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -10994,7 +10586,7 @@
       <c r="B69" s="16">
         <v>0.0506</v>
       </c>
-      <c r="C69" s="16">
+      <c r="C69" s="17">
         <v>0.0491</v>
       </c>
       <c r="D69" s="16">
@@ -11009,9 +10601,8 @@
       <c r="G69" s="16">
         <v>0.0601</v>
       </c>
-      <c r="H69" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B69:G69),B69:G69,0)),"")</f>
-        <v>1 year</v>
+      <c r="H69" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -11021,7 +10612,7 @@
       <c r="B70" s="16">
         <v>0.0528</v>
       </c>
-      <c r="C70" s="16">
+      <c r="C70" s="17">
         <v>0.052</v>
       </c>
       <c r="D70" s="16">
@@ -11036,16 +10627,15 @@
       <c r="G70" s="16">
         <v>0.06</v>
       </c>
-      <c r="H70" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B70:G70),B70:G70,0)),"")</f>
-        <v>1 year</v>
+      <c r="H70" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="15">
         <v>44865</v>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="17">
         <v>0.05769999999999999</v>
       </c>
       <c r="C71" s="16">
@@ -11063,9 +10653,8 @@
       <c r="G71" s="16">
         <v>0.0634</v>
       </c>
-      <c r="H71" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B71:G71),B71:G71,0)),"")</f>
-        <v>6 months</v>
+      <c r="H71" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -11075,7 +10664,7 @@
       <c r="B72" s="16">
         <v>0.0612</v>
       </c>
-      <c r="C72" s="16">
+      <c r="C72" s="17">
         <v>0.0601</v>
       </c>
       <c r="D72" s="16">
@@ -11090,9 +10679,8 @@
       <c r="G72" s="16">
         <v>0.063</v>
       </c>
-      <c r="H72" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B72:G72),B72:G72,0)),"")</f>
-        <v>1 year</v>
+      <c r="H72" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -11102,7 +10690,7 @@
       <c r="B73" s="16">
         <v>0.06480000000000001</v>
       </c>
-      <c r="C73" s="16">
+      <c r="C73" s="17">
         <v>0.064</v>
       </c>
       <c r="D73" s="16">
@@ -11117,9 +10705,8 @@
       <c r="G73" s="16">
         <v>0.0675</v>
       </c>
-      <c r="H73" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B73:G73),B73:G73,0)),"")</f>
-        <v>1 year</v>
+      <c r="H73" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -11129,7 +10716,7 @@
       <c r="B74" s="16">
         <v>0.0649</v>
       </c>
-      <c r="C74" s="16">
+      <c r="C74" s="17">
         <v>0.06419999999999999</v>
       </c>
       <c r="D74" s="16">
@@ -11144,9 +10731,8 @@
       <c r="G74" s="16">
         <v>0.067</v>
       </c>
-      <c r="H74" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B74:G74),B74:G74,0)),"")</f>
-        <v>1 year</v>
+      <c r="H74" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -11159,7 +10745,7 @@
       <c r="C75" s="16">
         <v>0.0649</v>
       </c>
-      <c r="D75" s="16">
+      <c r="D75" s="17">
         <v>0.0643</v>
       </c>
       <c r="E75" s="16">
@@ -11171,9 +10757,8 @@
       <c r="G75" s="16">
         <v>0.0654</v>
       </c>
-      <c r="H75" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B75:G75),B75:G75,0)),"")</f>
-        <v>2 years</v>
+      <c r="H75" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -11186,7 +10771,7 @@
       <c r="C76" s="16">
         <v>0.065</v>
       </c>
-      <c r="D76" s="16">
+      <c r="D76" s="17">
         <v>0.06469999999999999</v>
       </c>
       <c r="E76" s="16">
@@ -11198,9 +10783,8 @@
       <c r="G76" s="16">
         <v>0.06559999999999999</v>
       </c>
-      <c r="H76" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B76:G76),B76:G76,0)),"")</f>
-        <v>2 years</v>
+      <c r="H76" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -11216,7 +10800,7 @@
       <c r="D77" s="16">
         <v>0.0654</v>
       </c>
-      <c r="E77" s="16">
+      <c r="E77" s="17">
         <v>0.063</v>
       </c>
       <c r="F77" s="16">
@@ -11225,9 +10809,8 @@
       <c r="G77" s="16">
         <v>0.06320000000000001</v>
       </c>
-      <c r="H77" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B77:G77),B77:G77,0)),"")</f>
-        <v>3 years</v>
+      <c r="H77" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -11243,7 +10826,7 @@
       <c r="D78" s="16">
         <v>0.0649</v>
       </c>
-      <c r="E78" s="16">
+      <c r="E78" s="17">
         <v>0.0622</v>
       </c>
       <c r="F78" s="16">
@@ -11252,9 +10835,8 @@
       <c r="G78" s="16">
         <v>0.0629</v>
       </c>
-      <c r="H78" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B78:G78),B78:G78,0)),"")</f>
-        <v>3 years</v>
+      <c r="H78" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -11270,18 +10852,17 @@
       <c r="D79" s="16">
         <v>0.0654</v>
       </c>
-      <c r="E79" s="16">
+      <c r="E79" s="17">
         <v>0.0629</v>
       </c>
-      <c r="F79" s="16">
+      <c r="F79" s="17">
         <v>0.0629</v>
       </c>
-      <c r="G79" s="16">
+      <c r="G79" s="17">
         <v>0.0629</v>
       </c>
-      <c r="H79" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B79:G79),B79:G79,0)),"")</f>
-        <v>3 years</v>
+      <c r="H79" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -11303,12 +10884,11 @@
       <c r="F80" s="16">
         <v>0.0635</v>
       </c>
-      <c r="G80" s="16">
+      <c r="G80" s="17">
         <v>0.0629</v>
       </c>
-      <c r="H80" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B80:G80),B80:G80,0)),"")</f>
-        <v>5 years</v>
+      <c r="H80" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -11330,12 +10910,11 @@
       <c r="F81" s="16">
         <v>0.0645</v>
       </c>
-      <c r="G81" s="16">
+      <c r="G81" s="17">
         <v>0.0641</v>
       </c>
-      <c r="H81" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B81:G81),B81:G81,0)),"")</f>
-        <v>5 years</v>
+      <c r="H81" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -11357,12 +10936,11 @@
       <c r="F82" s="16">
         <v>0.06519999999999999</v>
       </c>
-      <c r="G82" s="16">
+      <c r="G82" s="17">
         <v>0.0646</v>
       </c>
-      <c r="H82" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B82:G82),B82:G82,0)),"")</f>
-        <v>5 years</v>
+      <c r="H82" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -11384,12 +10962,11 @@
       <c r="F83" s="16">
         <v>0.0668</v>
       </c>
-      <c r="G83" s="16">
+      <c r="G83" s="17">
         <v>0.0665</v>
       </c>
-      <c r="H83" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B83:G83),B83:G83,0)),"")</f>
-        <v>5 years</v>
+      <c r="H83" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -11411,12 +10988,11 @@
       <c r="F84" s="16">
         <v>0.067</v>
       </c>
-      <c r="G84" s="16">
+      <c r="G84" s="17">
         <v>0.06660000000000001</v>
       </c>
-      <c r="H84" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B84:G84),B84:G84,0)),"")</f>
-        <v>5 years</v>
+      <c r="H84" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -11438,12 +11014,11 @@
       <c r="F85" s="16">
         <v>0.067</v>
       </c>
-      <c r="G85" s="16">
+      <c r="G85" s="17">
         <v>0.06660000000000001</v>
       </c>
-      <c r="H85" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B85:G85),B85:G85,0)),"")</f>
-        <v>5 years</v>
+      <c r="H85" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -11465,12 +11040,11 @@
       <c r="F86" s="16">
         <v>0.0667</v>
       </c>
-      <c r="G86" s="16">
+      <c r="G86" s="17">
         <v>0.066</v>
       </c>
-      <c r="H86" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B86:G86),B86:G86,0)),"")</f>
-        <v>5 years</v>
+      <c r="H86" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -11492,12 +11066,11 @@
       <c r="F87" s="16">
         <v>0.0663</v>
       </c>
-      <c r="G87" s="16">
+      <c r="G87" s="17">
         <v>0.06559999999999999</v>
       </c>
-      <c r="H87" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B87:G87),B87:G87,0)),"")</f>
-        <v>5 years</v>
+      <c r="H87" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -11519,12 +11092,11 @@
       <c r="F88" s="16">
         <v>0.06519999999999999</v>
       </c>
-      <c r="G88" s="16">
+      <c r="G88" s="17">
         <v>0.0649</v>
       </c>
-      <c r="H88" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B88:G88),B88:G88,0)),"")</f>
-        <v>5 years</v>
+      <c r="H88" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -11546,12 +11118,11 @@
       <c r="F89" s="16">
         <v>0.06469999999999999</v>
       </c>
-      <c r="G89" s="16">
+      <c r="G89" s="17">
         <v>0.0644</v>
       </c>
-      <c r="H89" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B89:G89),B89:G89,0)),"")</f>
-        <v>5 years</v>
+      <c r="H89" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -11570,15 +11141,14 @@
       <c r="E90" s="16">
         <v>0.065</v>
       </c>
-      <c r="F90" s="16">
+      <c r="F90" s="17">
         <v>0.0644</v>
       </c>
-      <c r="G90" s="16">
+      <c r="G90" s="17">
         <v>0.0644</v>
       </c>
-      <c r="H90" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B90:G90),B90:G90,0)),"")</f>
-        <v>4 years</v>
+      <c r="H90" s="18" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -11597,15 +11167,14 @@
       <c r="E91" s="16">
         <v>0.0654</v>
       </c>
-      <c r="F91" s="16">
+      <c r="F91" s="17">
         <v>0.0644</v>
       </c>
-      <c r="G91" s="16">
+      <c r="G91" s="17">
         <v>0.0644</v>
       </c>
-      <c r="H91" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B91:G91),B91:G91,0)),"")</f>
-        <v>4 years</v>
+      <c r="H91" s="18" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -11627,12 +11196,11 @@
       <c r="F92" s="16">
         <v>0.0633</v>
       </c>
-      <c r="G92" s="16">
+      <c r="G92" s="17">
         <v>0.06309999999999999</v>
       </c>
-      <c r="H92" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B92:G92),B92:G92,0)),"")</f>
-        <v>5 years</v>
+      <c r="H92" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -11648,7 +11216,7 @@
       <c r="D93" s="16">
         <v>0.0594</v>
       </c>
-      <c r="E93" s="16">
+      <c r="E93" s="17">
         <v>0.05860000000000001</v>
       </c>
       <c r="F93" s="16">
@@ -11657,9 +11225,8 @@
       <c r="G93" s="16">
         <v>0.059</v>
       </c>
-      <c r="H93" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B93:G93),B93:G93,0)),"")</f>
-        <v>3 years</v>
+      <c r="H93" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -11678,15 +11245,14 @@
       <c r="E94" s="16">
         <v>0.058</v>
       </c>
-      <c r="F94" s="16">
+      <c r="F94" s="17">
         <v>0.0579</v>
       </c>
-      <c r="G94" s="16">
+      <c r="G94" s="17">
         <v>0.0579</v>
       </c>
-      <c r="H94" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B94:G94),B94:G94,0)),"")</f>
-        <v>4 years</v>
+      <c r="H94" s="18" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -11702,7 +11268,7 @@
       <c r="D95" s="16">
         <v>0.05690000000000001</v>
       </c>
-      <c r="E95" s="16">
+      <c r="E95" s="17">
         <v>0.0567</v>
       </c>
       <c r="F95" s="16">
@@ -11711,9 +11277,8 @@
       <c r="G95" s="16">
         <v>0.0573</v>
       </c>
-      <c r="H95" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B95:G95),B95:G95,0)),"")</f>
-        <v>3 years</v>
+      <c r="H95" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -11726,10 +11291,10 @@
       <c r="C96" s="16">
         <v>0.05860000000000001</v>
       </c>
-      <c r="D96" s="16">
+      <c r="D96" s="17">
         <v>0.0565</v>
       </c>
-      <c r="E96" s="16">
+      <c r="E96" s="17">
         <v>0.0565</v>
       </c>
       <c r="F96" s="16">
@@ -11738,9 +11303,8 @@
       <c r="G96" s="16">
         <v>0.0576</v>
       </c>
-      <c r="H96" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B96:G96),B96:G96,0)),"")</f>
-        <v>2 years</v>
+      <c r="H96" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -11753,7 +11317,7 @@
       <c r="C97" s="16">
         <v>0.0578</v>
       </c>
-      <c r="D97" s="16">
+      <c r="D97" s="17">
         <v>0.0555</v>
       </c>
       <c r="E97" s="16">
@@ -11765,9 +11329,8 @@
       <c r="G97" s="16">
         <v>0.0579</v>
       </c>
-      <c r="H97" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B97:G97),B97:G97,0)),"")</f>
-        <v>2 years</v>
+      <c r="H97" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -11780,7 +11343,7 @@
       <c r="C98" s="16">
         <v>0.0559</v>
       </c>
-      <c r="D98" s="16">
+      <c r="D98" s="17">
         <v>0.0544</v>
       </c>
       <c r="E98" s="16">
@@ -11792,9 +11355,8 @@
       <c r="G98" s="16">
         <v>0.0584</v>
       </c>
-      <c r="H98" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B98:G98),B98:G98,0)),"")</f>
-        <v>2 years</v>
+      <c r="H98" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -11807,7 +11369,7 @@
       <c r="C99" s="16">
         <v>0.0528</v>
       </c>
-      <c r="D99" s="16">
+      <c r="D99" s="17">
         <v>0.0513</v>
       </c>
       <c r="E99" s="16">
@@ -11819,9 +11381,8 @@
       <c r="G99" s="16">
         <v>0.057</v>
       </c>
-      <c r="H99" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B99:G99),B99:G99,0)),"")</f>
-        <v>2 years</v>
+      <c r="H99" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -11834,7 +11395,7 @@
       <c r="C100" s="16">
         <v>0.0522</v>
       </c>
-      <c r="D100" s="16">
+      <c r="D100" s="17">
         <v>0.0506</v>
       </c>
       <c r="E100" s="16">
@@ -11846,9 +11407,8 @@
       <c r="G100" s="16">
         <v>0.057</v>
       </c>
-      <c r="H100" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B100:G100),B100:G100,0)),"")</f>
-        <v>2 years</v>
+      <c r="H100" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -11858,7 +11418,7 @@
       <c r="B101" s="16">
         <v>0.0556</v>
       </c>
-      <c r="C101" s="16">
+      <c r="C101" s="17">
         <v>0.05019999999999999</v>
       </c>
       <c r="D101" s="16">
@@ -11873,9 +11433,8 @@
       <c r="G101" s="16">
         <v>0.057</v>
       </c>
-      <c r="H101" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B101:G101),B101:G101,0)),"")</f>
-        <v>1 year</v>
+      <c r="H101" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -11885,7 +11444,7 @@
       <c r="B102" s="16">
         <v>0.0545</v>
       </c>
-      <c r="C102" s="16">
+      <c r="C102" s="17">
         <v>0.0496</v>
       </c>
       <c r="D102" s="16">
@@ -11900,9 +11459,8 @@
       <c r="G102" s="16">
         <v>0.0568</v>
       </c>
-      <c r="H102" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B102:G102),B102:G102,0)),"")</f>
-        <v>1 year</v>
+      <c r="H102" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -11912,7 +11470,7 @@
       <c r="B103" s="16">
         <v>0.0526</v>
       </c>
-      <c r="C103" s="16">
+      <c r="C103" s="17">
         <v>0.0488</v>
       </c>
       <c r="D103" s="16">
@@ -11927,9 +11485,8 @@
       <c r="G103" s="16">
         <v>0.0563</v>
       </c>
-      <c r="H103" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B103:G103),B103:G103,0)),"")</f>
-        <v>1 year</v>
+      <c r="H103" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -11939,7 +11496,7 @@
       <c r="B104" s="16">
         <v>0.0525</v>
       </c>
-      <c r="C104" s="16">
+      <c r="C104" s="17">
         <v>0.0487</v>
       </c>
       <c r="D104" s="16">
@@ -11954,9 +11511,8 @@
       <c r="G104" s="16">
         <v>0.0563</v>
       </c>
-      <c r="H104" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B104:G104),B104:G104,0)),"")</f>
-        <v>1 year</v>
+      <c r="H104" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -11966,7 +11522,7 @@
       <c r="B105" s="16">
         <v>0.0507</v>
       </c>
-      <c r="C105" s="16">
+      <c r="C105" s="17">
         <v>0.0474</v>
       </c>
       <c r="D105" s="16">
@@ -11981,9 +11537,8 @@
       <c r="G105" s="16">
         <v>0.0553</v>
       </c>
-      <c r="H105" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B105:G105),B105:G105,0)),"")</f>
-        <v>1 year</v>
+      <c r="H105" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -11996,7 +11551,7 @@
       <c r="C106" s="16">
         <v>0.0473</v>
       </c>
-      <c r="D106" s="16">
+      <c r="D106" s="17">
         <v>0.0472</v>
       </c>
       <c r="E106" s="16">
@@ -12008,9 +11563,8 @@
       <c r="G106" s="16">
         <v>0.0553</v>
       </c>
-      <c r="H106" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B106:G106),B106:G106,0)),"")</f>
-        <v>2 years</v>
+      <c r="H106" s="18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -12020,7 +11574,7 @@
       <c r="B107" s="16">
         <v>0.0481</v>
       </c>
-      <c r="C107" s="16">
+      <c r="C107" s="17">
         <v>0.0443</v>
       </c>
       <c r="D107" s="16">
@@ -12035,9 +11589,8 @@
       <c r="G107" s="16">
         <v>0.0512</v>
       </c>
-      <c r="H107" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B107:G107),B107:G107,0)),"")</f>
-        <v>1 year</v>
+      <c r="H107" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -12047,7 +11600,7 @@
       <c r="B108" s="16">
         <v>0.0478</v>
       </c>
-      <c r="C108" s="16">
+      <c r="C108" s="17">
         <v>0.0443</v>
       </c>
       <c r="D108" s="16">
@@ -12062,9 +11615,8 @@
       <c r="G108" s="16">
         <v>0.0512</v>
       </c>
-      <c r="H108" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B108:G108),B108:G108,0)),"")</f>
-        <v>1 year</v>
+      <c r="H108" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -12074,7 +11626,7 @@
       <c r="B109" s="16">
         <v>0.0469</v>
       </c>
-      <c r="C109" s="16">
+      <c r="C109" s="17">
         <v>0.0445</v>
       </c>
       <c r="D109" s="16">
@@ -12089,9 +11641,8 @@
       <c r="G109" s="16">
         <v>0.0527</v>
       </c>
-      <c r="H109" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B109:G109),B109:G109,0)),"")</f>
-        <v>1 year</v>
+      <c r="H109" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -12101,7 +11652,7 @@
       <c r="B110" s="16">
         <v>0.0463</v>
       </c>
-      <c r="C110" s="16">
+      <c r="C110" s="17">
         <v>0.04480000000000001</v>
       </c>
       <c r="D110" s="16">
@@ -12116,9 +11667,8 @@
       <c r="G110" s="16">
         <v>0.0536</v>
       </c>
-      <c r="H110" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B110:G110),B110:G110,0)),"")</f>
-        <v>1 year</v>
+      <c r="H110" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -12128,7 +11678,7 @@
       <c r="B111" s="16">
         <v>0.0455</v>
       </c>
-      <c r="C111" s="16">
+      <c r="C111" s="17">
         <v>0.0446</v>
       </c>
       <c r="D111" s="16">
@@ -12143,16 +11693,15 @@
       <c r="G111" s="16">
         <v>0.0549</v>
       </c>
-      <c r="H111" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B111:G111),B111:G111,0)),"")</f>
-        <v>1 year</v>
+      <c r="H111" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="15">
         <v>46112</v>
       </c>
-      <c r="B112" s="16">
+      <c r="B112" s="17">
         <v>0.0449</v>
       </c>
       <c r="C112" s="16">
@@ -12170,16 +11719,15 @@
       <c r="G112" s="16">
         <v>0.0566</v>
       </c>
-      <c r="H112" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B112:G112),B112:G112,0)),"")</f>
-        <v>6 months</v>
+      <c r="H112" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="15">
         <v>46142</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B113" s="17">
         <v>0.04480000000000001</v>
       </c>
       <c r="C113" s="16">
@@ -12197,16 +11745,15 @@
       <c r="G113" s="16">
         <v>0.0564</v>
       </c>
-      <c r="H113" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B113:G113),B113:G113,0)),"")</f>
-        <v>6 months</v>
+      <c r="H113" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="15">
         <v>46173</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B114" s="17">
         <v>0.045</v>
       </c>
       <c r="C114" s="16">
@@ -12224,16 +11771,15 @@
       <c r="G114" s="16">
         <v>0.0574</v>
       </c>
-      <c r="H114" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B114:G114),B114:G114,0)),"")</f>
-        <v>6 months</v>
+      <c r="H114" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="15">
         <v>46203</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="17">
         <v>0.0457</v>
       </c>
       <c r="C115" s="16">
@@ -12251,16 +11797,15 @@
       <c r="G115" s="16">
         <v>0.0564</v>
       </c>
-      <c r="H115" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B115:G115),B115:G115,0)),"")</f>
-        <v>6 months</v>
+      <c r="H115" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="15">
         <v>46234</v>
       </c>
-      <c r="B116" s="16">
+      <c r="B116" s="17">
         <v>0.046</v>
       </c>
       <c r="C116" s="16">
@@ -12278,16 +11823,15 @@
       <c r="G116" s="16">
         <v>0.0563</v>
       </c>
-      <c r="H116" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B116:G116),B116:G116,0)),"")</f>
-        <v>6 months</v>
+      <c r="H116" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="15">
         <v>46265</v>
       </c>
-      <c r="B117" s="16">
+      <c r="B117" s="17">
         <v>0.0469</v>
       </c>
       <c r="C117" s="16">
@@ -12305,16 +11849,15 @@
       <c r="G117" s="16">
         <v>0.0563</v>
       </c>
-      <c r="H117" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B117:G117),B117:G117,0)),"")</f>
-        <v>6 months</v>
+      <c r="H117" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="15">
         <v>46295</v>
       </c>
-      <c r="B118" s="16">
+      <c r="B118" s="17">
         <v>0.0474</v>
       </c>
       <c r="C118" s="16">
@@ -12332,18 +11875,12 @@
       <c r="G118" s="16">
         <v>0.057</v>
       </c>
-      <c r="H118" s="17" t="str">
-        <f>IFERROR(INDEX($B$1:$G$1,MATCH(MIN(B118:G118),B118:G118,0)),"")</f>
-        <v>6 months</v>
+      <c r="H118" s="18" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H118"/>
-  <conditionalFormatting sqref="B2:G118">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(B2&lt;&gt;"",B2=MIN($B2:$G2))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -12450,899 +11987,692 @@
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="18">
+      <c r="A6" s="19">
         <v>38353</v>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6)</f>
         <v>261</v>
       </c>
       <c r="C6" s="9">
-        <f>AVERAGEIFS('Standard rates'!$B$2:$B$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6)</f>
         <v>0.06794406130268199</v>
       </c>
       <c r="D6" s="9">
-        <f>AVERAGEIFS('Standard rates'!$C$2:$C$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6)</f>
-        <v>0.061274329501915706</v>
+        <v>0.06127432950191571</v>
       </c>
       <c r="E6" s="9">
-        <f>AVERAGEIFS('Standard rates'!$D$2:$D$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6)</f>
         <v>0.05998007662835249</v>
       </c>
       <c r="F6" s="9">
-        <f>AVERAGEIFS('Standard rates'!$E$2:$E$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6)</f>
         <v>0.06155938697318008</v>
       </c>
       <c r="G6" s="9">
-        <f>AVERAGEIFS('Standard rates'!$F$2:$F$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6)</f>
         <v>0.06295632183908045</v>
       </c>
       <c r="H6" s="9">
-        <f>AVERAGEIFS('Standard rates'!$G$2:$G$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6)</f>
         <v>0.06515249042145593</v>
       </c>
       <c r="I6" s="9">
-        <f>AVERAGEIFS('Standard rates'!$H$2:$H$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6)</f>
         <v>0.06661302681992337</v>
       </c>
       <c r="K6" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6,'Standard rates'!$I$2:$I$262,K$5)</f>
         <v>1</v>
       </c>
       <c r="L6" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6,'Standard rates'!$I$2:$I$262,L$5)</f>
         <v>59</v>
       </c>
       <c r="M6" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6,'Standard rates'!$I$2:$I$262,M$5)</f>
         <v>132</v>
       </c>
       <c r="N6" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6,'Standard rates'!$I$2:$I$262,N$5)</f>
         <v>10</v>
       </c>
       <c r="O6" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6,'Standard rates'!$I$2:$I$262,O$5)</f>
         <v>10</v>
       </c>
       <c r="P6" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6,'Standard rates'!$I$2:$I$262,P$5)</f>
         <v>4</v>
       </c>
       <c r="Q6" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A6,'Standard rates'!$I$2:$I$262,Q$5)</f>
         <v>45</v>
       </c>
       <c r="R6" s="11">
-        <f>SUM(K6:Q6)</f>
         <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="18">
+      <c r="A7" s="19">
         <v>38718</v>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7)</f>
         <v>249</v>
       </c>
       <c r="C7" s="9">
-        <f>AVERAGEIFS('Standard rates'!$B$2:$B$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7)</f>
         <v>0.0668991967871486</v>
       </c>
       <c r="D7" s="9">
-        <f>AVERAGEIFS('Standard rates'!$C$2:$C$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7)</f>
         <v>0.06037510040160643</v>
       </c>
       <c r="E7" s="9">
-        <f>AVERAGEIFS('Standard rates'!$D$2:$D$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7)</f>
-        <v>0.059053413654618477</v>
+        <v>0.05905341365461848</v>
       </c>
       <c r="F7" s="9">
-        <f>AVERAGEIFS('Standard rates'!$E$2:$E$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7)</f>
         <v>0.06077028112449799</v>
       </c>
       <c r="G7" s="9">
-        <f>AVERAGEIFS('Standard rates'!$F$2:$F$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7)</f>
         <v>0.06223253012048193</v>
       </c>
       <c r="H7" s="9">
-        <f>AVERAGEIFS('Standard rates'!$G$2:$G$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7)</f>
         <v>0.06454578313253012</v>
       </c>
       <c r="I7" s="9">
-        <f>AVERAGEIFS('Standard rates'!$H$2:$H$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7)</f>
         <v>0.06610160642570281</v>
       </c>
       <c r="K7" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7,'Standard rates'!$I$2:$I$262,K$5)</f>
         <v>1</v>
       </c>
       <c r="L7" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7,'Standard rates'!$I$2:$I$262,L$5)</f>
         <v>59</v>
       </c>
       <c r="M7" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7,'Standard rates'!$I$2:$I$262,M$5)</f>
         <v>129</v>
       </c>
       <c r="N7" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7,'Standard rates'!$I$2:$I$262,N$5)</f>
         <v>8</v>
       </c>
       <c r="O7" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7,'Standard rates'!$I$2:$I$262,O$5)</f>
         <v>10</v>
       </c>
       <c r="P7" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7,'Standard rates'!$I$2:$I$262,P$5)</f>
         <v>3</v>
       </c>
       <c r="Q7" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A7,'Standard rates'!$I$2:$I$262,Q$5)</f>
         <v>39</v>
       </c>
       <c r="R7" s="11">
-        <f>SUM(K7:Q7)</f>
         <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="18">
+      <c r="A8" s="19">
         <v>39083</v>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8)</f>
         <v>237</v>
       </c>
       <c r="C8" s="9">
-        <f>AVERAGEIFS('Standard rates'!$B$2:$B$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8)</f>
         <v>0.06549367088607595</v>
       </c>
       <c r="D8" s="9">
-        <f>AVERAGEIFS('Standard rates'!$C$2:$C$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8)</f>
         <v>0.05917257383966244</v>
       </c>
       <c r="E8" s="9">
-        <f>AVERAGEIFS('Standard rates'!$D$2:$D$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8)</f>
         <v>0.05780590717299578</v>
       </c>
       <c r="F8" s="9">
-        <f>AVERAGEIFS('Standard rates'!$E$2:$E$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8)</f>
-        <v>0.059785232067510546</v>
+        <v>0.05978523206751055</v>
       </c>
       <c r="G8" s="9">
-        <f>AVERAGEIFS('Standard rates'!$F$2:$F$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8)</f>
         <v>0.0613759493670886</v>
       </c>
       <c r="H8" s="9">
-        <f>AVERAGEIFS('Standard rates'!$G$2:$G$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8)</f>
         <v>0.06381814345991561</v>
       </c>
       <c r="I8" s="9">
-        <f>AVERAGEIFS('Standard rates'!$H$2:$H$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8)</f>
         <v>0.06551139240506329</v>
       </c>
       <c r="K8" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8,'Standard rates'!$I$2:$I$262,K$5)</f>
         <v>1</v>
       </c>
       <c r="L8" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8,'Standard rates'!$I$2:$I$262,L$5)</f>
         <v>59</v>
       </c>
       <c r="M8" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8,'Standard rates'!$I$2:$I$262,M$5)</f>
         <v>129</v>
       </c>
       <c r="N8" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8,'Standard rates'!$I$2:$I$262,N$5)</f>
         <v>8</v>
       </c>
       <c r="O8" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8,'Standard rates'!$I$2:$I$262,O$5)</f>
         <v>10</v>
       </c>
       <c r="P8" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8,'Standard rates'!$I$2:$I$262,P$5)</f>
         <v>3</v>
       </c>
       <c r="Q8" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A8,'Standard rates'!$I$2:$I$262,Q$5)</f>
         <v>27</v>
       </c>
       <c r="R8" s="11">
-        <f>SUM(K8:Q8)</f>
         <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="18">
+      <c r="A9" s="19">
         <v>39448</v>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9)</f>
         <v>225</v>
       </c>
       <c r="C9" s="9">
-        <f>AVERAGEIFS('Standard rates'!$B$2:$B$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9)</f>
         <v>0.063628</v>
       </c>
       <c r="D9" s="9">
-        <f>AVERAGEIFS('Standard rates'!$C$2:$C$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9)</f>
         <v>0.05745022222222222</v>
       </c>
       <c r="E9" s="9">
-        <f>AVERAGEIFS('Standard rates'!$D$2:$D$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9)</f>
-        <v>0.056011111111111116</v>
+        <v>0.05601111111111112</v>
       </c>
       <c r="F9" s="9">
-        <f>AVERAGEIFS('Standard rates'!$E$2:$E$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9)</f>
         <v>0.05819777777777778</v>
       </c>
       <c r="G9" s="9">
-        <f>AVERAGEIFS('Standard rates'!$F$2:$F$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9)</f>
         <v>0.05996088888888888</v>
       </c>
       <c r="H9" s="9">
-        <f>AVERAGEIFS('Standard rates'!$G$2:$G$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9)</f>
         <v>0.06255822222222222</v>
       </c>
       <c r="I9" s="9">
-        <f>AVERAGEIFS('Standard rates'!$H$2:$H$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9)</f>
         <v>0.06441022222222223</v>
       </c>
       <c r="K9" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9,'Standard rates'!$I$2:$I$262,K$5)</f>
         <v>1</v>
       </c>
       <c r="L9" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9,'Standard rates'!$I$2:$I$262,L$5)</f>
         <v>59</v>
       </c>
       <c r="M9" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9,'Standard rates'!$I$2:$I$262,M$5)</f>
         <v>129</v>
       </c>
       <c r="N9" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9,'Standard rates'!$I$2:$I$262,N$5)</f>
         <v>8</v>
       </c>
       <c r="O9" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9,'Standard rates'!$I$2:$I$262,O$5)</f>
         <v>10</v>
       </c>
       <c r="P9" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9,'Standard rates'!$I$2:$I$262,P$5)</f>
         <v>3</v>
       </c>
       <c r="Q9" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A9,'Standard rates'!$I$2:$I$262,Q$5)</f>
         <v>15</v>
       </c>
       <c r="R9" s="11">
-        <f>SUM(K9:Q9)</f>
         <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="18">
+      <c r="A10" s="19">
         <v>39814</v>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10)</f>
         <v>213</v>
       </c>
       <c r="C10" s="9">
-        <f>AVERAGEIFS('Standard rates'!$B$2:$B$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10)</f>
         <v>0.06150845070422535</v>
       </c>
       <c r="D10" s="9">
-        <f>AVERAGEIFS('Standard rates'!$C$2:$C$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10)</f>
         <v>0.05550422535211268</v>
       </c>
       <c r="E10" s="9">
-        <f>AVERAGEIFS('Standard rates'!$D$2:$D$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10)</f>
-        <v>0.054084976525821594</v>
+        <v>0.05408497652582159</v>
       </c>
       <c r="F10" s="9">
-        <f>AVERAGEIFS('Standard rates'!$E$2:$E$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10)</f>
         <v>0.05648826291079812</v>
       </c>
       <c r="G10" s="9">
-        <f>AVERAGEIFS('Standard rates'!$F$2:$F$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10)</f>
         <v>0.05834131455399061</v>
       </c>
       <c r="H10" s="9">
-        <f>AVERAGEIFS('Standard rates'!$G$2:$G$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10)</f>
         <v>0.06106197183098591</v>
       </c>
       <c r="I10" s="9">
-        <f>AVERAGEIFS('Standard rates'!$H$2:$H$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10)</f>
         <v>0.06303333333333333</v>
       </c>
       <c r="K10" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10,'Standard rates'!$I$2:$I$262,K$5)</f>
         <v>1</v>
       </c>
       <c r="L10" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10,'Standard rates'!$I$2:$I$262,L$5)</f>
         <v>59</v>
       </c>
       <c r="M10" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10,'Standard rates'!$I$2:$I$262,M$5)</f>
         <v>126</v>
       </c>
       <c r="N10" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10,'Standard rates'!$I$2:$I$262,N$5)</f>
         <v>5</v>
       </c>
       <c r="O10" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10,'Standard rates'!$I$2:$I$262,O$5)</f>
         <v>9</v>
       </c>
       <c r="P10" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10,'Standard rates'!$I$2:$I$262,P$5)</f>
         <v>2</v>
       </c>
       <c r="Q10" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A10,'Standard rates'!$I$2:$I$262,Q$5)</f>
         <v>11</v>
       </c>
       <c r="R10" s="11">
-        <f>SUM(K10:Q10)</f>
         <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" s="18">
+      <c r="A11" s="19">
         <v>40179</v>
       </c>
       <c r="B11" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11)</f>
         <v>201</v>
       </c>
       <c r="C11" s="9">
-        <f>AVERAGEIFS('Standard rates'!$B$2:$B$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11)</f>
         <v>0.06137064676616915</v>
       </c>
       <c r="D11" s="9">
-        <f>AVERAGEIFS('Standard rates'!$C$2:$C$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11)</f>
         <v>0.05541393034825871</v>
       </c>
       <c r="E11" s="9">
-        <f>AVERAGEIFS('Standard rates'!$D$2:$D$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11)</f>
-        <v>0.053836815920398004</v>
+        <v>0.053836815920398</v>
       </c>
       <c r="F11" s="9">
-        <f>AVERAGEIFS('Standard rates'!$E$2:$E$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11)</f>
-        <v>0.055980099502487564</v>
+        <v>0.05598009950248756</v>
       </c>
       <c r="G11" s="9">
-        <f>AVERAGEIFS('Standard rates'!$F$2:$F$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11)</f>
-        <v>0.057578606965174126</v>
+        <v>0.05757860696517413</v>
       </c>
       <c r="H11" s="9">
-        <f>AVERAGEIFS('Standard rates'!$G$2:$G$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11)</f>
         <v>0.06015572139303483</v>
       </c>
       <c r="I11" s="9">
-        <f>AVERAGEIFS('Standard rates'!$H$2:$H$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11)</f>
         <v>0.06208358208955224</v>
       </c>
       <c r="K11" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11,'Standard rates'!$I$2:$I$262,K$5)</f>
         <v>1</v>
       </c>
       <c r="L11" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11,'Standard rates'!$I$2:$I$262,L$5)</f>
         <v>50</v>
       </c>
       <c r="M11" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11,'Standard rates'!$I$2:$I$262,M$5)</f>
         <v>123</v>
       </c>
       <c r="N11" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11,'Standard rates'!$I$2:$I$262,N$5)</f>
         <v>5</v>
       </c>
       <c r="O11" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11,'Standard rates'!$I$2:$I$262,O$5)</f>
         <v>9</v>
       </c>
       <c r="P11" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11,'Standard rates'!$I$2:$I$262,P$5)</f>
         <v>2</v>
       </c>
       <c r="Q11" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A11,'Standard rates'!$I$2:$I$262,Q$5)</f>
         <v>11</v>
       </c>
       <c r="R11" s="11">
-        <f>SUM(K11:Q11)</f>
         <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="18">
+      <c r="A12" s="19">
         <v>40544</v>
       </c>
       <c r="B12" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12)</f>
         <v>189</v>
       </c>
       <c r="C12" s="9">
-        <f>AVERAGEIFS('Standard rates'!$B$2:$B$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12)</f>
-        <v>0.061355026455026454</v>
+        <v>0.06135502645502645</v>
       </c>
       <c r="D12" s="9">
-        <f>AVERAGEIFS('Standard rates'!$C$2:$C$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12)</f>
         <v>0.0551095238095238</v>
       </c>
       <c r="E12" s="9">
-        <f>AVERAGEIFS('Standard rates'!$D$2:$D$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12)</f>
         <v>0.05325291005291005</v>
       </c>
       <c r="F12" s="9">
-        <f>AVERAGEIFS('Standard rates'!$E$2:$E$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12)</f>
         <v>0.05511798941798942</v>
       </c>
       <c r="G12" s="9">
-        <f>AVERAGEIFS('Standard rates'!$F$2:$F$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12)</f>
         <v>0.05651375661375662</v>
       </c>
       <c r="H12" s="9">
-        <f>AVERAGEIFS('Standard rates'!$G$2:$G$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12)</f>
         <v>0.05899206349206349</v>
       </c>
       <c r="I12" s="9">
-        <f>AVERAGEIFS('Standard rates'!$H$2:$H$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12)</f>
         <v>0.06088835978835978</v>
       </c>
       <c r="K12" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12,'Standard rates'!$I$2:$I$262,K$5)</f>
         <v>1</v>
       </c>
       <c r="L12" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12,'Standard rates'!$I$2:$I$262,L$5)</f>
         <v>38</v>
       </c>
       <c r="M12" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12,'Standard rates'!$I$2:$I$262,M$5)</f>
         <v>123</v>
       </c>
       <c r="N12" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12,'Standard rates'!$I$2:$I$262,N$5)</f>
         <v>5</v>
       </c>
       <c r="O12" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12,'Standard rates'!$I$2:$I$262,O$5)</f>
         <v>9</v>
       </c>
       <c r="P12" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12,'Standard rates'!$I$2:$I$262,P$5)</f>
         <v>2</v>
       </c>
       <c r="Q12" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A12,'Standard rates'!$I$2:$I$262,Q$5)</f>
         <v>11</v>
       </c>
       <c r="R12" s="11">
-        <f>SUM(K12:Q12)</f>
         <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="18">
+      <c r="A13" s="19">
         <v>40909</v>
       </c>
       <c r="B13" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13)</f>
         <v>177</v>
       </c>
       <c r="C13" s="9">
-        <f>AVERAGEIFS('Standard rates'!$B$2:$B$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13)</f>
-        <v>0.061481355932203385</v>
+        <v>0.06148135593220339</v>
       </c>
       <c r="D13" s="9">
-        <f>AVERAGEIFS('Standard rates'!$C$2:$C$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13)</f>
-        <v>0.054850847457627125</v>
+        <v>0.05485084745762712</v>
       </c>
       <c r="E13" s="9">
-        <f>AVERAGEIFS('Standard rates'!$D$2:$D$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13)</f>
-        <v>0.052808474576271185</v>
+        <v>0.05280847457627118</v>
       </c>
       <c r="F13" s="9">
-        <f>AVERAGEIFS('Standard rates'!$E$2:$E$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13)</f>
         <v>0.05454745762711864</v>
       </c>
       <c r="G13" s="9">
-        <f>AVERAGEIFS('Standard rates'!$F$2:$F$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13)</f>
-        <v>0.055702824858757057</v>
+        <v>0.05570282485875706</v>
       </c>
       <c r="H13" s="9">
-        <f>AVERAGEIFS('Standard rates'!$G$2:$G$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13)</f>
-        <v>0.058063276836158195</v>
+        <v>0.0580632768361582</v>
       </c>
       <c r="I13" s="9">
-        <f>AVERAGEIFS('Standard rates'!$H$2:$H$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13)</f>
         <v>0.05988135593220339</v>
       </c>
       <c r="K13" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13,'Standard rates'!$I$2:$I$262,K$5)</f>
         <v>0</v>
       </c>
       <c r="L13" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13,'Standard rates'!$I$2:$I$262,L$5)</f>
         <v>27</v>
       </c>
       <c r="M13" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13,'Standard rates'!$I$2:$I$262,M$5)</f>
         <v>123</v>
       </c>
       <c r="N13" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13,'Standard rates'!$I$2:$I$262,N$5)</f>
         <v>5</v>
       </c>
       <c r="O13" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13,'Standard rates'!$I$2:$I$262,O$5)</f>
         <v>9</v>
       </c>
       <c r="P13" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13,'Standard rates'!$I$2:$I$262,P$5)</f>
         <v>2</v>
       </c>
       <c r="Q13" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A13,'Standard rates'!$I$2:$I$262,Q$5)</f>
         <v>11</v>
       </c>
       <c r="R13" s="11">
-        <f>SUM(K13:Q13)</f>
         <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="18">
+      <c r="A14" s="19">
         <v>41275</v>
       </c>
       <c r="B14" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14)</f>
         <v>165</v>
       </c>
       <c r="C14" s="9">
-        <f>AVERAGEIFS('Standard rates'!$B$2:$B$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14)</f>
         <v>0.06172484848484848</v>
       </c>
       <c r="D14" s="9">
-        <f>AVERAGEIFS('Standard rates'!$C$2:$C$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14)</f>
         <v>0.05481575757575758</v>
       </c>
       <c r="E14" s="9">
-        <f>AVERAGEIFS('Standard rates'!$D$2:$D$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14)</f>
-        <v>0.052690303030303025</v>
+        <v>0.05269030303030302</v>
       </c>
       <c r="F14" s="9">
-        <f>AVERAGEIFS('Standard rates'!$E$2:$E$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14)</f>
         <v>0.05443515151515151</v>
       </c>
       <c r="G14" s="9">
-        <f>AVERAGEIFS('Standard rates'!$F$2:$F$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14)</f>
         <v>0.05543818181818182</v>
       </c>
       <c r="H14" s="9">
-        <f>AVERAGEIFS('Standard rates'!$G$2:$G$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14)</f>
-        <v>0.057704848484848484</v>
+        <v>0.05770484848484848</v>
       </c>
       <c r="I14" s="9">
-        <f>AVERAGEIFS('Standard rates'!$H$2:$H$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14)</f>
         <v>0.05938181818181818</v>
       </c>
       <c r="K14" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14,'Standard rates'!$I$2:$I$262,K$5)</f>
         <v>0</v>
       </c>
       <c r="L14" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14,'Standard rates'!$I$2:$I$262,L$5)</f>
         <v>22</v>
       </c>
       <c r="M14" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14,'Standard rates'!$I$2:$I$262,M$5)</f>
         <v>116</v>
       </c>
       <c r="N14" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14,'Standard rates'!$I$2:$I$262,N$5)</f>
         <v>5</v>
       </c>
       <c r="O14" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14,'Standard rates'!$I$2:$I$262,O$5)</f>
         <v>9</v>
       </c>
       <c r="P14" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14,'Standard rates'!$I$2:$I$262,P$5)</f>
         <v>2</v>
       </c>
       <c r="Q14" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A14,'Standard rates'!$I$2:$I$262,Q$5)</f>
         <v>11</v>
       </c>
       <c r="R14" s="11">
-        <f>SUM(K14:Q14)</f>
         <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="18">
+      <c r="A15" s="19">
         <v>41640</v>
       </c>
       <c r="B15" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15)</f>
         <v>153</v>
       </c>
       <c r="C15" s="9">
-        <f>AVERAGEIFS('Standard rates'!$B$2:$B$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15)</f>
         <v>0.06200915032679738</v>
       </c>
       <c r="D15" s="9">
-        <f>AVERAGEIFS('Standard rates'!$C$2:$C$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15)</f>
         <v>0.05487254901960784</v>
       </c>
       <c r="E15" s="9">
-        <f>AVERAGEIFS('Standard rates'!$D$2:$D$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15)</f>
         <v>0.05263660130718954</v>
       </c>
       <c r="F15" s="9">
-        <f>AVERAGEIFS('Standard rates'!$E$2:$E$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15)</f>
         <v>0.05426013071895425</v>
       </c>
       <c r="G15" s="9">
-        <f>AVERAGEIFS('Standard rates'!$F$2:$F$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15)</f>
         <v>0.05500065359477125</v>
       </c>
       <c r="H15" s="9">
-        <f>AVERAGEIFS('Standard rates'!$G$2:$G$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15)</f>
         <v>0.05726143790849673</v>
       </c>
       <c r="I15" s="9">
-        <f>AVERAGEIFS('Standard rates'!$H$2:$H$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15)</f>
-        <v>0.058820915032679735</v>
+        <v>0.05882091503267974</v>
       </c>
       <c r="K15" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15,'Standard rates'!$I$2:$I$262,K$5)</f>
         <v>0</v>
       </c>
       <c r="L15" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15,'Standard rates'!$I$2:$I$262,L$5)</f>
         <v>21</v>
       </c>
       <c r="M15" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15,'Standard rates'!$I$2:$I$262,M$5)</f>
         <v>105</v>
       </c>
       <c r="N15" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15,'Standard rates'!$I$2:$I$262,N$5)</f>
         <v>5</v>
       </c>
       <c r="O15" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15,'Standard rates'!$I$2:$I$262,O$5)</f>
         <v>9</v>
       </c>
       <c r="P15" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15,'Standard rates'!$I$2:$I$262,P$5)</f>
         <v>2</v>
       </c>
       <c r="Q15" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A15,'Standard rates'!$I$2:$I$262,Q$5)</f>
         <v>11</v>
       </c>
       <c r="R15" s="11">
-        <f>SUM(K15:Q15)</f>
         <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="18">
+      <c r="A16" s="19">
         <v>42005</v>
       </c>
       <c r="B16" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16)</f>
         <v>141</v>
       </c>
       <c r="C16" s="9">
-        <f>AVERAGEIFS('Standard rates'!$B$2:$B$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16)</f>
         <v>0.06191985815602837</v>
       </c>
       <c r="D16" s="9">
-        <f>AVERAGEIFS('Standard rates'!$C$2:$C$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16)</f>
         <v>0.05464964539007092</v>
       </c>
       <c r="E16" s="9">
-        <f>AVERAGEIFS('Standard rates'!$D$2:$D$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16)</f>
         <v>0.05216595744680851</v>
       </c>
       <c r="F16" s="9">
-        <f>AVERAGEIFS('Standard rates'!$E$2:$E$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16)</f>
         <v>0.0535950354609929</v>
       </c>
       <c r="G16" s="9">
-        <f>AVERAGEIFS('Standard rates'!$F$2:$F$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16)</f>
-        <v>0.054131914893617024</v>
+        <v>0.05413191489361702</v>
       </c>
       <c r="H16" s="9">
-        <f>AVERAGEIFS('Standard rates'!$G$2:$G$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16)</f>
         <v>0.05631631205673759</v>
       </c>
       <c r="I16" s="9">
-        <f>AVERAGEIFS('Standard rates'!$H$2:$H$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16)</f>
-        <v>0.057773049645390075</v>
+        <v>0.05777304964539007</v>
       </c>
       <c r="K16" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16,'Standard rates'!$I$2:$I$262,K$5)</f>
         <v>0</v>
       </c>
       <c r="L16" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16,'Standard rates'!$I$2:$I$262,L$5)</f>
         <v>11</v>
       </c>
       <c r="M16" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16,'Standard rates'!$I$2:$I$262,M$5)</f>
         <v>103</v>
       </c>
       <c r="N16" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16,'Standard rates'!$I$2:$I$262,N$5)</f>
         <v>5</v>
       </c>
       <c r="O16" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16,'Standard rates'!$I$2:$I$262,O$5)</f>
         <v>9</v>
       </c>
       <c r="P16" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16,'Standard rates'!$I$2:$I$262,P$5)</f>
         <v>2</v>
       </c>
       <c r="Q16" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A16,'Standard rates'!$I$2:$I$262,Q$5)</f>
         <v>11</v>
       </c>
       <c r="R16" s="11">
-        <f>SUM(K16:Q16)</f>
         <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="18">
+      <c r="A17" s="19">
         <v>42370</v>
       </c>
       <c r="B17" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17)</f>
         <v>129</v>
       </c>
       <c r="C17" s="9">
-        <f>AVERAGEIFS('Standard rates'!$B$2:$B$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17)</f>
         <v>0.06184263565891473</v>
       </c>
       <c r="D17" s="9">
-        <f>AVERAGEIFS('Standard rates'!$C$2:$C$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17)</f>
         <v>0.05452868217054264</v>
       </c>
       <c r="E17" s="9">
-        <f>AVERAGEIFS('Standard rates'!$D$2:$D$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17)</f>
-        <v>0.051959689922480616</v>
+        <v>0.05195968992248062</v>
       </c>
       <c r="F17" s="9">
-        <f>AVERAGEIFS('Standard rates'!$E$2:$E$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17)</f>
-        <v>0.053350387596899224</v>
+        <v>0.05335038759689922</v>
       </c>
       <c r="G17" s="9">
-        <f>AVERAGEIFS('Standard rates'!$F$2:$F$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17)</f>
-        <v>0.053787596899224806</v>
+        <v>0.05378759689922481</v>
       </c>
       <c r="H17" s="9">
-        <f>AVERAGEIFS('Standard rates'!$G$2:$G$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17)</f>
         <v>0.05612713178294574</v>
       </c>
       <c r="I17" s="9">
-        <f>AVERAGEIFS('Standard rates'!$H$2:$H$262,'Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17)</f>
         <v>0.05743875968992248</v>
       </c>
       <c r="K17" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17,'Standard rates'!$I$2:$I$262,K$5)</f>
         <v>0</v>
       </c>
       <c r="L17" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17,'Standard rates'!$I$2:$I$262,L$5)</f>
         <v>11</v>
       </c>
       <c r="M17" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17,'Standard rates'!$I$2:$I$262,M$5)</f>
         <v>91</v>
       </c>
       <c r="N17" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17,'Standard rates'!$I$2:$I$262,N$5)</f>
         <v>5</v>
       </c>
       <c r="O17" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17,'Standard rates'!$I$2:$I$262,O$5)</f>
         <v>9</v>
       </c>
       <c r="P17" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17,'Standard rates'!$I$2:$I$262,P$5)</f>
         <v>2</v>
       </c>
       <c r="Q17" s="11">
-        <f>COUNTIFS('Standard rates'!$A$2:$A$262,"&gt;="&amp;$A17,'Standard rates'!$I$2:$I$262,Q$5)</f>
         <v>11</v>
       </c>
       <c r="R17" s="11">
-        <f>SUM(K17:Q17)</f>
         <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="26" customHeight="1">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="19"/>
+      <c r="B19" s="20"/>
       <c r="C19" s="8">
-        <f>AVERAGE(C6:C17)</f>
         <v>0.06309807512167666</v>
       </c>
       <c r="D19" s="8">
-        <f>AVERAGE(D6:D17)</f>
         <v>0.05650144892407568</v>
       </c>
       <c r="E19" s="8">
-        <f>AVERAGE(E6:E17)</f>
         <v>0.05469051977910503</v>
       </c>
       <c r="F19" s="8">
-        <f>AVERAGE(F6:F17)</f>
         <v>0.05650726605777984</v>
       </c>
       <c r="G19" s="8">
-        <f>AVERAGE(G6:G17)</f>
         <v>0.05775171170108443</v>
       </c>
       <c r="H19" s="8">
-        <f>AVERAGE(H6:H17)</f>
         <v>0.06014645025178291</v>
       </c>
       <c r="I19" s="8">
-        <f>AVERAGE(I6:I17)</f>
         <v>0.06182811846384758</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K19" s="11">
-        <f>SUM(K6:K17)</f>
         <v>7</v>
       </c>
       <c r="L19" s="11">
-        <f>SUM(L6:L17)</f>
         <v>475</v>
       </c>
       <c r="M19" s="11">
-        <f>SUM(M6:M17)</f>
         <v>1429</v>
       </c>
       <c r="N19" s="11">
-        <f>SUM(N6:N17)</f>
         <v>74</v>
       </c>
       <c r="O19" s="11">
-        <f>SUM(O6:O17)</f>
         <v>112</v>
       </c>
       <c r="P19" s="11">
-        <f>SUM(P6:P17)</f>
         <v>29</v>
       </c>
       <c r="Q19" s="11">
-        <f>SUM(Q6:Q17)</f>
         <v>214</v>
       </c>
       <c r="R19" s="11">
-        <f>SUM(R6:R17)</f>
         <v>2340</v>
       </c>
     </row>
@@ -13351,31 +12681,24 @@
         <v>17</v>
       </c>
       <c r="K20" s="12">
-        <f>K19/$R$19</f>
-        <v>0.0029914529914529917</v>
+        <v>0.002991452991452992</v>
       </c>
       <c r="L20" s="12">
-        <f>L19/$R$19</f>
         <v>0.202991452991453</v>
       </c>
       <c r="M20" s="12">
-        <f>M19/$R$19</f>
         <v>0.6106837606837607</v>
       </c>
       <c r="N20" s="12">
-        <f>N19/$R$19</f>
         <v>0.03162393162393162</v>
       </c>
       <c r="O20" s="12">
-        <f>O19/$R$19</f>
         <v>0.04786324786324787</v>
       </c>
       <c r="P20" s="12">
-        <f>P19/$R$19</f>
-        <v>0.012393162393162393</v>
+        <v>0.01239316239316239</v>
       </c>
       <c r="Q20" s="12">
-        <f>Q19/$R$19</f>
         <v>0.09145299145299145</v>
       </c>
     </row>
